--- a/fund_api.xlsx
+++ b/fund_api.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lzfdd\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4444AD2D-D568-4632-B346-D5ED0B7C4201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A47BA08-7C83-4B58-82B9-A625FAAF17D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7068C037-8E11-473D-BF09-92FC6201B4E7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>接口</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -905,6 +905,14 @@
   </si>
   <si>
     <t>orderField=5_1_-1&amp;pageIndex=1&amp;pageNum=30&amp;pageType=5&amp;deviceid=Wap&amp;plat=Wap&amp;product=EFund&amp;version=2.0.0&amp;abnormal=3&amp;rankSy=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deviceid=1234567.py.service&amp;version=6.5.5&amp;appVersion=6.5.5&amp;product=EFund&amp;plat=Iphone&amp;FCODE=008142&amp;INDEXCODE=AU9999&amp;RANGE=n&amp;POINTCOUNT=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其中 url 参数 RANGE 表示基金范围: RANGE=n 表示获取近 1 年的基金净值。3n 为三年，y 为月，3y 为 3月。jn 为今年来。ln 为成立以来.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1394,8 +1402,14 @@
       <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="E5" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>26</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">

--- a/fund_api.xlsx
+++ b/fund_api.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lzfdd\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lzfdd\backups\MyProjects\python_test\fundweb\JJBond\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A47BA08-7C83-4B58-82B9-A625FAAF17D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC02931D-A3CD-4E8D-8CB7-B0F176317C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7068C037-8E11-473D-BF09-92FC6201B4E7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>接口</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -913,6 +913,44 @@
   </si>
   <si>
     <t>其中 url 参数 RANGE 表示基金范围: RANGE=n 表示获取近 1 年的基金净值。3n 为三年，y 为月，3y 为 3月。jn 为今年来。ln 为成立以来.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://api.fund.eastmoney.com//ztjj/GetZTJJListNew?callback=jQuery18302985230470397895_1776505785907&amp;tt=0&amp;dt=syl&amp;st=D&amp;_=1776507110492</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jQuery18302985230470397895_1776505785907({
+    "Data": [
+        {
+            "INDEXCODE": "BK000651",
+            "INDEXNAME": "光模块",
+            "D": 4.847572
+        },
+        {
+            "INDEXCODE": "BK000176",
+            "INDEXNAME": "通信设备",
+            "D": 4.705764
+        },
+    ],
+    "ErrCode": 0,
+    "ErrMsg": null,
+    "TotalCount": 0,
+    "Expansion": null,
+    "PageSize": 0,
+    "PageIndex": 0
+})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数说明：
+tt: 板块分类（0为全部，001002为行业板块，001003为概念板块）
+dt: 排序类别（syl 为按涨幅排序，zjlr 为按基金流入分类）
+st: 时间范围（当按涨幅排序时，st可选[D-天，W-近一周，M-近一个月]。当按自己流入排序时，st可选[FLOW为实时，FLOW_W 为近一周，FLOW_M 为近一月]）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取行业板块涨跌情况</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1306,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756FAFE1-58E3-4702-9EE8-9320214AB644}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -1315,7 +1353,8 @@
     <col min="4" max="4" width="8.88671875" style="1"/>
     <col min="5" max="5" width="31.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="70.33203125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="17.109375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1431,6 +1470,26 @@
       <c r="G6" s="1" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="7" spans="1:7" ht="276" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C8" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1440,6 +1499,7 @@
     <hyperlink ref="C4" r:id="rId3" xr:uid="{19C90962-D255-4554-BAB4-CCF1B560A39F}"/>
     <hyperlink ref="C5" r:id="rId4" xr:uid="{65A696E3-DC0D-41D5-BEF2-5F556A0DFD08}"/>
     <hyperlink ref="C6" r:id="rId5" xr:uid="{4CE6E835-A307-4EC6-94A1-7077A14AD1D1}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{F70AB97F-1DF4-41E6-89EB-9DE1813B8336}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/fund_api.xlsx
+++ b/fund_api.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lzfdd\backups\MyProjects\python_test\fundweb\JJBond\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC02931D-A3CD-4E8D-8CB7-B0F176317C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FBFA8B-72D1-4F87-B0AE-1AD1AEE2ACFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7068C037-8E11-473D-BF09-92FC6201B4E7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
   <si>
     <t>接口</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -953,6 +953,676 @@
     <t>获取行业板块涨跌情况</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>https://push2.eastmoney.com/api/qt/clist/get?np=1&amp;fltt=1&amp;invt=2&amp;cb=jQuery37103879588047371354_1776568216882&amp;fs=b%3AMK0010&amp;fields=f12%2Cf13%2Cf14%2Cf1%2Cf2%2Cf4%2Cf3%2Cf152%2Cf5%2Cf6%2Cf18%2Cf17%2Cf15%2Cf16&amp;fid=&amp;pn=1&amp;pz=50&amp;po=1&amp;ut=fa5fd1943c7b386f172d6893dbfba10b&amp;dect=1&amp;wbp2u=%7C0%7C0%7C0%7Cweb&amp;_=1776568216883</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jQuery37103879588047371354_1776568216882({
+    "rc": 0,
+    "rt": 6,
+    "svr": 180606380,
+    "lt": 1,
+    "full": 1,
+    "dlmkts": "",
+    "data": {
+        "total": 43,
+        "diff": [{
+            "f1": 2,
+            "f2": 405143,
+            "f3": -10,
+            "f4": -412,
+            "f5": 548791406,
+            "f6": 1013520660231.1,
+            "f12": "000001",
+            "f13": 1,
+            "f14": "上证指数",
+            "f15": 405860,
+            "f16": 403843,
+            "f17": 404338,
+            "f18": 405555,
+            "f152": 2
+        }, {
+            "f1": 2,
+            "f2": 1488542,
+            "f3": 60,
+            "f4": 8909,
+            "f5": 695914499,
+            "f6": 1412063032872.2705,
+            "f12": "399001",
+            "f13": 0,
+            "f14": "深证成指",
+            "f15": 1491639,
+            "f16": 1478787,
+            "f17": 1480628,
+            "f18": 1479633,
+            "f152": 2
+        }]
+    }
+});</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f2: 最新价（百分位）
+f3:涨跌幅（百分位）
+f4:涨跌额（百分位）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取A股市场行情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取美股道琼斯指数行情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>miniquotechart_jp152({
+    "rc": 0,
+    "rt": 10,
+    "svr": 180606311,
+    "lt": 1,
+    "full": 1,
+    "dlmkts": "",
+    "data": {
+        "code": "DJIA",
+        "market": 100,
+        "type": 0,
+        "status": 0,
+        "name": "道琼斯",
+        "decimal": 2,
+        "preSettlement": 48578.72,
+        "preClose": 48578.72,
+        "beticks": "77400|77400|100800|77400|100800",
+        "trendsTotal": 391,
+        "time": 1776456000,
+        "kind": 2,
+        "prePrice": 48578.72,
+        "tradePeriods": {
+            "pre": null,
+            "after": null,
+            "periods": [{
+                "b": 202604172130,
+                "e": 202604180400
+            }]
+        },
+        "hisPrePrices": [{
+            "date": 20260417,
+            "prePrice": 48578.72
+        }],
+        "trends": ["2026-04-17 21:30,48788.81,48788.81,48788.81,48788.81,48788.810", "2026-04-17 21:31,48788.81,49077.21,49089.67,49066.56,48933.010", "2026-04-17 21:32,49083.88,49141.14,49141.89,49083.88,49002.386", "2026-04-17 21:33,49177.50,49224.41,49224.41,49177.50,49057.892", "2026-04-17 21:34,49198.21,49210.62,49216.10,49198.21,49088.437", "2026-04-17 21:35,49212.82,49259.67,49261.11,49212.82,49116.975", "2026-04-17 21:36,49232.96,49261.98,49265.65,49232.96,49137.690", "2026-04-17 21:37,49284.03,49285.49,49295.30,49280.40,49156.165", "2026-04-17 21:38,49283.76,49247.49,49283.76,49239.01,49166.312", "2026-04-17 21:39,49243.50,49221.12,49243.50,49217.07,49171.792", "2026-04-17 21:40,49231.78,49187.47,49231.78,49183.71,49173.217", "2026-04-17 21:41,49182.82,49166.06,49182.82,49163.30,49172.620", "2026-04-17 21:42,49153.19,49143.01,49153.19,49134.79,49170.342", "2026-04-17 21:43,49151.61,49153.12,49154.54,49151.61,49169.111", "2026-04-17 21:44,49141.07,49135.92,49141.07,49126.42,49166.898", "2026-04-17 21:45,49129.73,49140.03,49140.03,49129.73,49165.218", "2026-04-17 21:46,49136.99,49107.75,49136.99,49107.75,49161.837", "2026-04-17 21:47,49156.16,49149.46,49156.16,49143.95,49161.149", "2026-04-17 21:48,49086.88,49097.43,49101.12,49085.09,49157.795", "2026-04-17 21:49,49089.81,49109.22,49109.22,49080.40,49155.366", "2026-04-17 21:50,49116.73,49114.01,49131.80,49112.96,49153.396", "2026-04-17 21:51,49133.24,49161.41,49161.41,49132.26,49153.760", "2026-04-17 21:52,49147.15,49186.26,49186.26,49147.15,49155.173", "2026-04-17 21:53,49181.48,49196.58,49204.55,49181.48,49156.898", "2026-04-17 21:54,49199.50,49219.67,49219.67,49199.50,49159.408", "2026-04-17 21:55,49225.48,49234.82,49234.82,49223.51,49162.308", "2026-04-17 21:56,49249.75,49263.11,49263.11,49249.75,49166.041", "2026-04-17 21:57,49265.43,49286.25,49286.25,49265.43,49170.334", "2026-04-17 21:58,49313.84,49339.62,49339.62,49313.84,49176.171", "2026-04-17 21:59,49322.47,49294.58,49322.47,49294.58,49180.117", "2026-04-17 22:00,49313.49,49326.79,49326.79,49313.49,49184.848", "2026-04-17 22:01,49296.44,49316.94,49316.94,49296.44,49188.975", "2026-04-17 22:02,49329.88,49328.45,49329.88,49327.95,49193.201", "2026-04-17 22:03,49328.73,49349.01,49349.01,49328.73,49197.783", "2026-04-17 22:04,49341.70,49358.85,49358.85,49341.70,49202.384", "2026-04-17 22:05,49356.24,49369.66,49369.66,49356.24,49207.030", "2026-04-17 22:06,49376.62,49392.84,49393.54,49376.62,49212.051", "2026-04-17 22:07,49380.37,49384.45,49402.65,49380.37,49216.587", "2026-04-17 22:08,49391.15,49406.68,49407.17,49391.15,49221.461", "2026-04-17 22:09,49407.74,49412.42,49412.42,49407.74,49226.234", "2026-04-17 22:10,49404.76,49411.69,49411.69,49404.76,49230.757", "2026-04-17 22:11,49417.50,49429.11,49432.19,49417.50,49235.479", "2026-04-17 22:12,49422.21,49395.14,49422.21,49395.14,49239.192", "2026-04-17 22:13,49397.45,49390.00,49397.73,49387.61,49242.619", "2026-04-17 22:14,49395.28,49391.44,49402.60,49391.17,49245.926", "2026-04-17 22:15,49392.98,49398.34,49400.47,49392.98,49249.239", "2026-04-17 22:16,49405.41,49414.58,49414.58,49397.45,49252.756", "2026-04-17 22:17,49425.20,49430.08,49430.08,49421.85,49256.450", "2026-04-17 22:18,49433.78,49420.99,49433.78,49420.99,49259.807", "2026-04-17 22:19,49418.50,49441.24,49441.24,49418.50,49263.435", "2026-04-17 22:20,49438.62,49447.52,49447.52,49438.48,49267.044", "2026-04-17 22:21,49445.16,49468.76,49469.59,49445.16,49270.923", "2026-04-17 22:22,49479.99,49473.19,49479.99,49473.19,49274.739", "2026-04-17 22:23,49488.86,49487.66,49493.08,49487.66,49278.681", "2026-04-17 22:24,49485.07,49507.16,49507.16,49485.07,49282.835", "2026-04-17 22:25,49507.10,49514.02,49514.02,49507.10,49286.963", "2026-04-17 22:26,49517.18,49521.24,49521.24,49515.09,49291.073", "2026-04-17 22:27,49534.49,49528.23,49534.49,49528.23,49295.161", "2026-04-17 22:28,49527.11,49520.97,49527.11,49510.01,49298.988", "2026-04-17 22:29,49515.99,49522.00,49522.18,49515.99,49302.704", "2026-04-17 22:30,49511.27,49516.02,49516.02,49506.03,49306.200", "2026-04-17 22:31,49512.90,49508.73,49513.52,49507.55,49309.466", "2026-04-17 22:32,49494.60,49508.53,49508.53,49494.60,49312.625", "2026-04-17 22:33,49523.43,49522.16,49523.43,49522.16,49315.898", "2026-04-17 22:34,49517.71,49558.37,49558.37,49517.71,49319.628", "2026-04-17 22:35,49570.69,49567.25,49570.69,49567.25,49323.379", "2026-04-17 22:36,49565.22,49538.41,49565.22,49537.60,49326.588", "2026-04-17 22:37,49552.34,49567.22,49567.22,49552.34,49330.126", "2026-04-17 22:38,49567.29,49566.52,49574.50,49566.52,49333.552", "2026-04-17 22:39,49571.02,49572.65,49572.65,49569.86,49336.967", "2026-04-17 22:40,49567.08,49558.62,49567.08,49556.74,49340.088", "2026-04-17 22:41,49562.08,49572.04,49574.81,49562.08,49343.309", "2026-04-17 22:42,49583.39,49587.46,49587.46,49581.08,49346.653", "2026-04-17 22:43,49586.00,49598.11,49599.05,49586.00,49350.051", "2026-04-17 22:44,49604.17,49589.80,49605.33,49589.80,49353.247", "2026-04-17 22:45,49595.79,49600.93,49600.93,49595.26,49356.505", "2026-04-17 22:46,49595.65,49592.79,49595.65,49592.79,49359.573", "2026-04-17 22:47,49597.41,49597.77,49597.77,49594.64,49362.626", "2026-04-17 22:48,49596.02,49600.97,49601.53,49596.02,49365.643", "2026-04-17 22:49,49601.47,49607.63,49607.63,49601.47,49368.667", "2026-04-17 22:50,49615.87,49626.40,49626.40,49615.87,49371.848", "2026-04-17 22:51,49628.99,49617.39,49628.99,49617.39,49374.842", "2026-04-17 22:52,49613.14,49643.13,49643.13,49613.14,49378.074", "2026-04-17 22:53,49638.31,49645.09,49645.09,49638.12,49381.252", "2026-04-17 22:54,49634.60,49631.37,49634.60,49628.83,49384.194", "2026-04-17 22:55,49629.88,49618.91,49629.88,49615.81,49386.923", "2026-04-17 22:56,49619.79,49594.84,49619.79,49594.84,49389.312", "2026-04-17 22:57,49581.86,49597.10,49597.10,49581.48,49391.673", "2026-04-17 22:58,49600.48,49594.01,49600.48,49594.01,49393.946", "2026-04-17 22:59,49593.97,49581.10,49593.97,49580.91,49396.025", "2026-04-17 23:00,49586.11,49561.54,49586.11,49561.54,49397.843", "2026-04-17 23:01,49559.51,49550.09,49559.51,49550.09,49399.497", "2026-04-17 23:02,49559.08,49570.62,49570.62,49559.08,49401.337", "2026-04-17 23:03,49575.55,49583.77,49591.37,49574.87,49403.277", "2026-04-17 23:04,49583.93,49602.18,49602.18,49583.93,49405.370", "2026-04-17 23:05,49570.96,49601.69,49601.69,49570.96,49407.415", "2026-04-17 23:06,49596.66,49600.25,49601.23,49596.66,49409.402", "2026-04-17 23:07,49598.32,49599.27,49599.27,49596.56,49411.339", "2026-04-17 23:08,49608.62,49611.16,49611.86,49607.81,49413.357", "2026-04-17 23:09,49608.68,49599.58,49608.68,49599.58,49415.219", "2026-04-17 23:10,49605.78,49590.56,49609.26,49590.56,49416.955", "2026-04-17 23:11,49591.50,49594.16,49594.16,49585.55,49418.692", "2026-04-17 23:12,49569.67,49559.20,49569.67,49559.20,49420.056", "2026-04-17 23:13,49562.35,49555.56,49568.32,49555.26,49421.358", "2026-04-17 23:14,49552.53,49559.85,49559.85,49552.53,49422.676", "2026-04-17 23:15,49558.93,49538.08,49558.93,49538.08,49423.764", "2026-04-17 23:16,49539.11,49553.37,49553.37,49539.11,49424.975", "2026-04-17 23:17,49543.49,49562.19,49562.19,49543.49,49426.245", "2026-04-17 23:18,49560.32,49557.66,49560.32,49557.20,49427.450", "2026-04-17 23:19,49561.43,49547.10,49561.43,49547.10,49428.537", "2026-04-17 23:20,49540.07,49512.44,49540.07,49508.26,49429.292", "2026-04-17 23:21,49531.49,49527.62,49535.76,49527.62,49430.169", "2026-04-17 23:22,49518.20,49541.01,49541.01,49518.20,49431.149", "2026-04-17 23:23,49539.92,49526.97,49539.92,49526.97,49431.989", "2026-04-17 23:24,49530.94,49535.80,49535.80,49530.94,49432.891", "2026-04-17 23:25,49533.41,49524.00,49533.41,49523.68,49433.676", "2026-04-17 23:26,49526.16,49520.21,49526.16,49520.21,49434.415", "2026-04-17 23:27,49514.39,49518.59,49518.59,49512.72,49435.128", "2026-04-17 23:28,49527.43,49514.94,49527.43,49514.89,49435.798", "2026-04-17 23:29,49500.04,49521.86,49521.86,49500.04,49436.515", "2026-04-17 23:30,49518.23,49518.90,49521.90,49518.23,49437.195", "2026-04-17 23:31,49528.11,49533.16,49535.55,49528.11,49437.981", "2026-04-17 23:32,49528.23,49554.77,49556.16,49528.23,49438.930", "2026-04-17 23:33,49556.78,49540.10,49556.78,49539.36,49439.745", "2026-04-17 23:34,49545.16,49552.94,49552.94,49543.20,49440.650", "2026-04-17 23:35,49550.76,49552.59,49552.59,49548.64,49441.538", "2026-04-17 23:36,49556.78,49556.34,49556.79,49553.78,49442.441", "2026-04-17 23:37,49560.57,49559.23,49563.67,49559.23,49443.353", "2026-04-17 23:38,49557.28,49558.29,49558.86,49557.28,49444.243", "2026-04-17 23:39,49546.67,49567.61,49567.61,49546.67,49445.191", "2026-04-17 23:40,49572.56,49564.20,49572.56,49564.20,49446.099", "2026-04-17 23:41,49564.34,49563.77,49564.34,49561.73,49446.990", "2026-04-17 23:42,49564.11,49564.97,49564.97,49560.77,49447.877", "2026-04-17 23:43,49563.36,49552.44,49563.36,49552.44,49448.657", "2026-04-17 23:44,49550.58,49551.58,49551.58,49549.91,49449.419", "2026-04-17 23:45,49548.94,49535.91,49548.94,49535.91,49450.054", "2026-04-17 23:46,49537.76,49552.89,49552.89,49537.76,49450.804", "2026-04-17 23:47,49557.63,49551.11,49557.63,49550.34,49451.530", "2026-04-17 23:48,49550.66,49556.62,49556.62,49550.66,49452.286", "2026-04-17 23:49,49557.31,49566.48,49566.48,49557.31,49453.101", "2026-04-17 23:50,49562.37,49583.44,49583.44,49559.71,49454.025", "2026-04-17 23:51,49584.47,49609.04,49609.04,49584.47,49455.116", "2026-04-17 23:52,49618.88,49635.83,49635.83,49618.88,49456.379", "2026-04-17 23:53,49628.06,49627.48,49629.84,49627.20,49457.567", "2026-04-17 23:54,49619.94,49628.92,49628.92,49619.94,49458.748", "2026-04-17 23:55,49636.78,49636.91,49636.91,49632.79,49459.968", "2026-04-17 23:56,49631.88,49645.36,49645.36,49631.88,49461.229", "2026-04-17 23:57,49640.98,49647.72,49647.72,49640.98,49462.489", "2026-04-17 23:58,49658.57,49661.92,49662.13,49658.57,49463.827", "2026-04-17 23:59,49661.44,49648.03,49661.44,49648.03,49465.055", "2026-04-18 00:00,49650.76,49659.25,49659.25,49647.08,49466.341", "2026-04-18 00:01,49657.11,49653.07,49657.11,49647.46,49467.569", "2026-04-18 00:02,49650.04,49669.53,49669.53,49650.04,49468.889", "2026-04-18 00:03,49673.64,49684.03,49684.03,49673.64,49470.286", "2026-04-18 00:04,49686.39,49694.38,49694.59,49686.39,49471.731", "2026-04-18 00:05,49686.01,49683.07,49686.01,49682.26,49473.085", "2026-04-18 00:06,49677.35,49672.39,49677.35,49670.76,49474.354", "2026-04-18 00:07,49668.76,49660.43,49669.31,49660.43,49475.531", "2026-04-18 00:08,49656.39,49660.12,49660.12,49656.39,49476.691", "2026-04-18 00:09,49656.03,49661.45,49663.90,49656.03,49477.845", "2026-04-18 00:10,49661.22,49636.90,49661.22,49636.90,49478.832", "2026-04-18 00:11,49635.14,49632.53,49639.98,49632.53,49479.780", "2026-04-18 00:12,49637.18,49642.03,49642.03,49637.18,49480.775", "2026-04-18 00:13,49651.01,49655.25,49655.25,49651.01,49481.838", "2026-04-18 00:14,49652.43,49647.95,49652.43,49645.65,49482.844", "2026-04-18 00:15,49642.47,49639.93,49642.47,49639.50,49483.790", "2026-04-18 00:16,49640.48,49641.74,49643.26,49640.48,49484.735", "2026-04-18 00:17,49639.67,49635.18,49639.67,49632.75,49485.630", "2026-04-18 00:18,49630.18,49622.94,49630.18,49617.07,49486.442", "2026-04-18 00:19,49621.14,49624.66,49628.19,49621.14,49487.255", "2026-04-18 00:20,49638.93,49643.29,49643.29,49638.93,49488.167", "2026-04-18 00:21,49644.51,49646.34,49646.34,49641.55,49489.086", "2026-04-18 00:22,49643.39,49648.44,49648.44,49642.27,49490.007", "2026-04-18 00:23,49647.74,49645.92,49647.74,49643.88,49490.903", "2026-04-18 00:24,49644.08,49641.29,49645.12,49641.29,49491.762", "2026-04-18 00:25,49649.16,49644.75,49649.16,49644.75,49492.631", "2026-04-18 00:26,49646.57,49649.71,49651.98,49646.57,49493.518", "2026-04-18 00:27,49649.40,49650.96,49650.96,49647.98,49494.402", "2026-04-18 00:28,49646.72,49652.59,49652.62,49646.72,49495.285", "2026-04-18 00:29,49646.01,49647.09,49647.09,49644.33,49496.128", "2026-04-18 00:30,49643.25,49647.16,49647.16,49640.87,49496.962", "2026-04-18 00:31,49644.29,49653.47,49653.47,49644.29,49497.821", "2026-04-18 00:32,49659.66,49658.29,49659.66,49653.00,49498.697", "2026-04-18 00:33,49667.00,49680.78,49680.78,49667.00,49499.686", "2026-04-18 00:34,49685.42,49689.60,49689.60,49684.35,49500.712", "2026-04-18 00:35,49688.74,49685.57,49688.74,49685.57,49501.705", "2026-04-18 00:36,49685.35,49688.42,49688.42,49682.17,49502.703", "2026-04-18 00:37,49684.61,49690.26,49690.26,49680.21,49503.700", "2026-04-18 00:38,49691.46,49687.23,49691.46,49687.23,49504.671", "2026-04-18 00:39,49688.06,49689.13,49689.13,49683.58,49505.641", "2026-04-18 00:40,49686.89,49690.55,49690.55,49684.37,49506.609", "2026-04-18 00:41,49688.38,49695.10,49695.10,49687.12,49507.590", "2026-04-18 00:42,49693.63,49687.97,49693.63,49687.97,49508.524", "2026-04-18 00:43,49686.84,49701.38,49706.94,49686.84,49509.518", "2026-04-18 00:44,49699.79,49696.85,49699.79,49696.85,49510.478", "2026-04-18 00:45,49697.69,49706.51,49706.51,49697.69,49511.478", "2026-04-18 00:46,49705.05,49708.76,49709.21,49705.05,49512.479", "2026-04-18 00:47,49710.53,49712.19,49712.19,49707.55,49513.487", "2026-04-18 00:48,49710.65,49707.78,49710.65,49707.44,49514.463", "2026-04-18 00:49,49708.09,49711.49,49711.49,49707.84,49515.448", "2026-04-18 00:50,49707.98,49705.77,49707.98,49703.61,49516.394", "2026-04-18 00:51,49705.11,49702.19,49705.11,49700.87,49517.313", "2026-04-18 00:52,49705.90,49707.92,49707.92,49705.90,49518.251", "2026-04-18 00:53,49709.72,49706.81,49709.72,49705.52,49519.175", "2026-04-18 00:54,49713.64,49707.49,49713.64,49705.72,49520.093", "2026-04-18 00:55,49709.82,49705.68,49711.42,49705.68,49520.993", "2026-04-18 00:56,49706.28,49703.50,49706.28,49703.08,49521.874", "2026-04-18 00:57,49701.80,49699.29,49701.80,49699.29,49522.726", "2026-04-18 00:58,49698.20,49701.53,49701.53,49698.20,49523.581", "2026-04-18 00:59,49703.82,49699.30,49704.22,49698.88,49524.417", "2026-04-18 01:00,49691.47,49690.74,49691.47,49689.22,49525.205", "2026-04-18 01:01,49694.45,49695.04,49697.51,49694.45,49526.006", "2026-04-18 01:02,49686.73,49691.61,49691.61,49686.39,49526.783", "2026-04-18 01:03,49686.77,49677.78,49686.77,49677.78,49527.488", "2026-04-18 01:04,49675.59,49672.49,49679.38,49672.49,49528.162", "2026-04-18 01:05,49671.53,49680.07,49680.07,49671.53,49528.865", "2026-04-18 01:06,49677.99,49673.25,49677.99,49672.86,49529.530", "2026-04-18 01:07,49672.60,49669.40,49672.60,49669.40,49530.171", "2026-04-18 01:08,49668.76,49655.27,49668.76,49655.27,49530.742", "2026-04-18 01:09,49652.29,49640.38,49652.29,49640.38,49531.240", "2026-04-18 01:10,49595.31,49622.64,49622.64,49595.31,49531.653", "2026-04-18 01:11,49623.50,49608.33,49623.50,49608.33,49531.998", "2026-04-18 01:12,49599.19,49594.42,49599.19,49592.50,49532.277", "2026-04-18 01:13,49593.34,49601.64,49601.64,49589.23,49532.586", "2026-04-18 01:14,49600.21,49603.04,49603.04,49600.21,49532.899", "2026-04-18 01:15,49604.18,49599.56,49604.18,49599.33,49533.193", "2026-04-18 01:16,49593.31,49595.27,49598.93,49593.31,49533.466", "2026-04-18 01:17,49584.12,49593.78,49593.78,49584.12,49533.730", "2026-04-18 01:18,49601.63,49593.08,49602.65,49593.08,49533.989", "2026-04-18 01:19,49592.03,49596.06,49596.06,49592.03,49534.258", "2026-04-18 01:20,49602.59,49593.12,49602.59,49593.12,49534.512", "2026-04-18 01:21,49586.26,49576.71,49586.26,49576.71,49534.693", "2026-04-18 01:22,49560.33,49546.48,49560.33,49546.48,49534.743", "2026-04-18 01:23,49550.61,49554.87,49554.87,49550.61,49534.829", "2026-04-18 01:24,49553.93,49572.62,49572.62,49553.93,49534.989", "2026-04-18 01:25,49587.23,49498.51,49587.23,49498.51,49534.834", "2026-04-18 01:26,49502.55,49508.02,49514.23,49502.55,49534.720", "2026-04-18 01:27,49510.76,49502.13,49510.76,49482.21,49534.583", "2026-04-18 01:28,49512.55,49518.88,49518.88,49512.55,49534.517", "2026-04-18 01:29,49531.53,49515.83,49531.53,49515.83,49534.439", "2026-04-18 01:30,49504.83,49514.12,49516.06,49504.83,49534.354", "2026-04-18 01:31,49513.66,49511.52,49515.18,49511.49,49534.259", "2026-04-18 01:32,49513.34,49506.83,49513.34,49506.83,49534.146", "2026-04-18 01:33,49505.24,49512.25,49512.25,49499.20,49534.056", "2026-04-18 01:34,49516.07,49508.70,49516.07,49505.59,49533.952", "2026-04-18 01:35,49513.56,49523.54,49523.54,49513.56,49533.909", "2026-04-18 01:36,49523.02,49504.54,49523.02,49504.54,49533.790", "2026-04-18 01:37,49498.34,49494.83,49499.39,49494.83,49533.632", "2026-04-18 01:38,49496.13,49512.79,49516.50,49496.13,49533.548", "2026-04-18 01:39,49514.97,49515.63,49526.75,49514.97,49533.476", "2026-04-18 01:40,49519.31,49498.32,49519.31,49498.32,49533.335", "2026-04-18 01:41,49499.76,49500.32,49505.72,49499.76,49533.203", "2026-04-18 01:42,49494.12,49494.14,49495.53,49494.12,49533.048", "2026-04-18 01:43,49501.48,49505.22,49505.22,49500.26,49532.938", "2026-04-18 01:44,49506.87,49497.50,49506.87,49497.50,49532.799", "2026-04-18 01:45,49492.01,49488.08,49492.01,49488.08,49532.624", "2026-04-18 01:46,49493.19,49504.75,49507.67,49493.19,49532.515", "2026-04-18 01:47,49500.98,49516.83,49516.83,49500.98,49532.454", "2026-04-18 01:48,49533.53,49541.29,49541.29,49533.53,49532.488", "2026-04-18 01:49,49545.07,49542.74,49545.07,49538.21,49532.527", "2026-04-18 01:50,49537.47,49535.77,49538.79,49535.77,49532.539", "2026-04-18 01:51,49537.16,49533.41,49537.16,49533.41,49532.542", "2026-04-18 01:52,49536.00,49547.31,49547.31,49536.00,49532.598", "2026-04-18 01:53,49548.21,49548.61,49548.61,49546.21,49532.658", "2026-04-18 01:54,49545.66,49546.70,49546.70,49545.42,49532.710", "2026-04-18 01:55,49551.11,49553.38,49553.57,49551.11,49532.787", "2026-04-18 01:56,49553.51,49555.59,49555.59,49553.51,49532.872", "2026-04-18 01:57,49552.18,49553.87,49553.87,49548.03,49532.950", "2026-04-18 01:58,49563.61,49558.89,49565.11,49558.89,49533.046", "2026-04-18 01:59,49559.11,49544.52,49559.11,49544.52,49533.088", "2026-04-18 02:00,49539.07,49539.29,49541.58,49539.07,49533.110", "2026-04-18 02:01,49533.97,49532.60,49533.97,49532.55,49533.108", "2026-04-18 02:02,49528.90,49540.50,49540.50,49528.90,49533.135", "2026-04-18 02:03,49543.89,49529.41,49543.89,49529.41,49533.121", "2026-04-18 02:04,49520.94,49521.49,49529.57,49520.94,49533.078", "2026-04-18 02:05,49517.74,49526.47,49526.57,49517.74,49533.054", "2026-04-18 02:06,49521.89,49515.02,49521.89,49515.02,49532.988", "2026-04-18 02:07,49513.88,49508.80,49513.88,49499.79,49532.900", "2026-04-18 02:08,49516.35,49498.27,49516.35,49498.27,49532.775", "2026-04-18 02:09,49498.21,49494.76,49498.21,49494.76,49532.639", "2026-04-18 02:10,49488.65,49486.28,49488.65,49485.61,49532.474", "2026-04-18 02:11,49489.44,49485.19,49497.17,49485.19,49532.306", "2026-04-18 02:12,49480.12,49490.11,49490.11,49480.12,49532.156", "2026-04-18 02:13,49490.23,49485.55,49490.23,49485.41,49531.991", "2026-04-18 02:14,49491.62,49485.28,49491.62,49485.28,49531.827", "2026-04-18 02:15,49477.94,49472.08,49477.94,49472.08,49531.618", "2026-04-18 02:16,49475.22,49487.75,49487.75,49475.22,49531.465", "2026-04-18 02:17,49487.45,49481.64,49487.45,49481.64,49531.291", "2026-04-18 02:18,49480.87,49475.69,49484.73,49475.69,49531.098", "2026-04-18 02:19,49478.70,49489.24,49489.24,49478.70,49530.953", "2026-04-18 02:20,49489.14,49483.12,49492.94,49483.12,49530.788", "2026-04-18 02:21,49480.99,49471.99,49480.99,49471.99,49530.586", "2026-04-18 02:22,49466.63,49465.83,49468.25,49465.83,49530.364", "2026-04-18 02:23,49465.05,49461.67,49465.05,49461.67,49530.130", "2026-04-18 02:24,49468.16,49475.81,49475.81,49466.15,49529.945", "2026-04-18 02:25,49484.52,49496.60,49501.54,49484.47,49529.832", "2026-04-18 02:26,49493.84,49511.13,49516.79,49493.84,49529.769", "2026-04-18 02:27,49514.58,49519.28,49519.28,49514.58,49529.733", "2026-04-18 02:28,49511.11,49511.70,49511.70,49509.56,49529.672", "2026-04-18 02:29,49504.80,49485.58,49504.80,49485.58,49529.525", "2026-04-18 02:30,49489.98,49479.81,49489.98,49479.81,49529.359", "2026-04-18 02:31,49485.04,49495.35,49495.35,49485.04,49529.246", "2026-04-18 02:32,49500.43,49497.77,49500.98,49497.77,49529.142", "2026-04-18 02:33,49499.66,49506.09,49506.09,49499.66,49529.066", "2026-04-18 02:34,49503.00,49503.48,49503.48,49500.83,49528.982", "2026-04-18 02:35,49507.53,49507.03,49508.98,49507.03,49528.910", "2026-04-18 02:36,49500.35,49495.86,49500.35,49495.86,49528.802", "2026-04-18 02:37,49499.03,49504.54,49505.64,49499.03,49528.723", "2026-04-18 02:38,49503.77,49500.34,49503.77,49495.80,49528.631", "2026-04-18 02:39,49496.65,49487.59,49496.65,49487.59,49528.498", "2026-04-18 02:40,49491.36,49482.36,49493.23,49482.36,49528.349", "2026-04-18 02:41,49482.30,49482.63,49482.63,49480.45,49528.202", "2026-04-18 02:42,49478.52,49478.09,49478.52,49475.22,49528.041", "2026-04-18 02:43,49476.40,49463.79,49476.40,49463.79,49527.836", "2026-04-18 02:44,49462.21,49470.12,49470.12,49462.21,49527.652", "2026-04-18 02:45,49473.85,49477.60,49477.60,49473.85,49527.493", "2026-04-18 02:46,49487.63,49484.28,49489.02,49484.28,49527.356", "2026-04-18 02:47,49484.74,49485.63,49485.63,49480.53,49527.224", "2026-04-18 02:48,49482.70,49482.21,49490.69,49482.21,49527.082", "2026-04-18 02:49,49480.88,49482.34,49482.83,49480.88,49526.942", "2026-04-18 02:50,49480.80,49476.53,49483.59,49476.53,49526.784", "2026-04-18 02:51,49476.74,49463.21,49476.74,49463.21,49526.586", "2026-04-18 02:52,49460.97,49465.83,49465.96,49460.97,49526.397", "2026-04-18 02:53,49457.39,49444.67,49457.67,49444.67,49526.144", "2026-04-18 02:54,49454.97,49452.03,49454.97,49451.74,49525.915", "2026-04-18 02:55,49455.07,49452.44,49455.07,49451.31,49525.689", "2026-04-18 02:56,49457.01,49466.33,49466.36,49457.01,49525.507", "2026-04-18 02:57,49468.19,49459.94,49469.91,49459.94,49525.307", "2026-04-18 02:58,49458.58,49458.37,49458.58,49457.06,49525.103", "2026-04-18 02:59,49456.14,49456.59,49456.59,49455.05,49524.895", "2026-04-18 03:00,49456.58,49458.09,49458.09,49456.39,49524.693", "2026-04-18 03:01,49451.75,49451.31,49453.85,49451.15,49524.471", "2026-04-18 03:02,49451.39,49461.50,49461.50,49451.39,49524.281", "2026-04-18 03:03,49465.11,49457.86,49465.11,49456.42,49524.082", "2026-04-18 03:04,49454.86,49450.88,49454.86,49450.33,49523.863", "2026-04-18 03:05,49449.94,49444.81,49449.94,49444.81,49523.627", "2026-04-18 03:06,49448.52,49452.27,49452.27,49448.18,49523.415", "2026-04-18 03:07,49450.60,49443.15,49450.60,49438.40,49523.177", "2026-04-18 03:08,49445.59,49454.63,49457.62,49445.59,49522.974", "2026-04-18 03:09,49450.57,49449.97,49450.57,49448.24,49522.759", "2026-04-18 03:10,49450.95,49439.41,49453.27,49439.41,49522.514", "2026-04-18 03:11,49446.52,49436.35,49446.52,49436.35,49522.262", "2026-04-18 03:12,49432.90,49432.11,49434.82,49432.11,49521.999", "2026-04-18 03:13,49431.08,49428.84,49431.08,49427.48,49521.728", "2026-04-18 03:14,49428.81,49422.32,49428.81,49422.32,49521.439", "2026-04-18 03:15,49413.44,49412.07,49415.75,49412.07,49521.122", "2026-04-18 03:16,49410.84,49431.85,49432.31,49410.84,49520.864", "2026-04-18 03:17,49433.42,49437.52,49437.52,49433.42,49520.624", "2026-04-18 03:18,49435.14,49434.32,49435.14,49432.54,49520.376", "2026-04-18 03:19,49434.20,49435.67,49440.17,49434.20,49520.133", "2026-04-18 03:20,49432.17,49423.04,49432.17,49422.12,49519.856", "2026-04-18 03:21,49427.51,49422.55,49434.62,49422.55,49519.579", "2026-04-18 03:22,49426.48,49433.41,49433.41,49426.40,49519.334", "2026-04-18 03:23,49435.46,49423.76,49435.46,49423.76,49519.064", "2026-04-18 03:24,49418.80,49417.10,49419.51,49416.14,49518.776", "2026-04-18 03:25,49417.69,49416.17,49417.69,49414.06,49518.487", "2026-04-18 03:26,49420.31,49423.26,49425.79,49420.31,49518.220", "2026-04-18 03:27,49422.52,49422.45,49422.52,49415.94,49517.952", "2026-04-18 03:28,49423.12,49413.39,49423.12,49413.39,49517.660", "2026-04-18 03:29,49414.47,49409.67,49414.47,49409.67,49517.360", "2026-04-18 03:30,49405.82,49405.82,49405.82,49402.40,49517.051", "2026-04-18 03:31,49399.65,49412.13,49412.45,49399.65,49516.761", "2026-04-18 03:32,49414.39,49426.91,49427.28,49414.39,49516.513", "2026-04-18 03:33,49421.75,49434.07,49436.04,49421.75,49516.286", "2026-04-18 03:34,49429.15,49434.87,49434.87,49428.49,49516.062", "2026-04-18 03:35,49439.37,49447.21,49447.29,49439.32,49515.873", "2026-04-18 03:36,49442.46,49444.46,49444.99,49442.09,49515.678", "2026-04-18 03:37,49440.41,49447.73,49447.73,49439.61,49515.493", "2026-04-18 03:38,49448.92,49450.59,49451.03,49448.92,49515.317", "2026-04-18 03:39,49453.62,49479.97,49479.97,49453.62,49515.221", "2026-04-18 03:40,49475.46,49485.02,49485.02,49474.00,49515.139", "2026-04-18 03:41,49475.58,49470.83,49475.58,49462.03,49515.019", "2026-04-18 03:42,49473.32,49464.85,49473.32,49464.85,49514.884", "2026-04-18 03:43,49470.27,49483.17,49483.17,49470.27,49514.799", "2026-04-18 03:44,49482.04,49488.45,49488.45,49482.04,49514.728", "2026-04-18 03:45,49490.25,49483.18,49490.59,49483.18,49514.644", "2026-04-18 03:46,49487.52,49465.83,49487.52,49465.83,49514.514", "2026-04-18 03:47,49459.30,49454.60,49459.45,49454.60,49514.355", "2026-04-18 03:48,49455.29,49440.27,49455.29,49440.27,49514.159", "2026-04-18 03:49,49442.42,49442.27,49442.42,49440.49,49513.969", "2026-04-18 03:50,49433.47,49431.33,49433.47,49424.37,49513.752", "2026-04-18 03:51,49430.53,49430.62,49455.54,49430.53,49513.534", "2026-04-18 03:52,49441.09,49439.41,49441.09,49430.09,49513.340", "2026-04-18 03:53,49448.90,49452.00,49452.00,49446.20,49513.180", "2026-04-18 03:54,49439.45,49454.78,49454.78,49439.45,49513.028", "2026-04-18 03:55,49457.12,49477.67,49477.67,49457.12,49512.936", "2026-04-18 03:56,49468.94,49462.69,49468.94,49462.69,49512.806", "2026-04-18 03:57,49460.67,49457.37,49475.58,49457.37,49512.663", "2026-04-18 03:58,49453.52,49445.07,49453.52,49445.07,49512.489", "2026-04-18 03:59,49447.40,49444.63,49448.47,49444.63,49512.315", "2026-04-18 04:00,49452.97,49447.43,49458.62,49434.16,49512.149"]
+    }
+});</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=100.DJIA&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp152</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>miniquotechart_jp154({
+    "rc": 0,
+    "rt": 10,
+    "svr": 177617709,
+    "lt": 1,
+    "full": 1,
+    "dlmkts": "",
+    "data": {
+        "code": "NDX",
+        "market": 100,
+        "type": 0,
+        "status": 0,
+        "name": "纳斯达克",
+        "decimal": 2,
+        "preSettlement": 24102.7,
+        "preClose": 24102.7,
+        "beticks": "77400|77400|100800|77400|100800",
+        "trendsTotal": 391,
+        "time": 1776456000,
+        "kind": 2,
+        "prePrice": 24102.7,
+        "tradePeriods": {
+            "pre": null,
+            "after": null,
+            "periods": [{
+                "b": 202604172130,
+                "e": 202604180400
+            }]
+        },
+        "hisPrePrices": [{
+            "date": 20260417,
+            "prePrice": 24102.7
+        }],
+        "trends": ["2026-04-17 21:30,24338.01,24338.01,24338.01,24338.01,24338.010", "2026-04-17 21:31,24338.01,24316.23,24351.97,24307.41,24327.120", "2026-04-17 21:32,24317.46,24328.82,24351.11,24314.80,24327.686", "2026-04-17 21:33,24329.98,24323.00,24337.27,24304.99,24326.514", "2026-04-17 21:34,24323.16,24290.14,24323.16,24286.47,24319.239", "2026-04-17 21:35,24291.36,24323.18,24325.32,24290.44,24319.895", "2026-04-17 21:36,24322.93,24340.33,24343.95,24321.77,24322.814", "2026-04-17 21:37,24338.35,24339.81,24343.94,24330.02,24324.938", "2026-04-17 21:38,24343.20,24365.23,24367.59,24338.68,24329.414", "2026-04-17 21:39,24365.11,24360.02,24365.11,24342.34,24332.474", "2026-04-17 21:40,24359.75,24350.73,24365.64,24349.77,24334.133", "2026-04-17 21:41,24350.29,24340.15,24351.45,24337.33,24334.634", "2026-04-17 21:42,24340.89,24341.24,24347.26,24336.83,24335.142", "2026-04-17 21:43,24341.83,24348.40,24355.66,24335.60,24336.089", "2026-04-17 21:44,24349.77,24342.55,24353.68,24335.92,24336.519", "2026-04-17 21:45,24343.93,24352.07,24361.66,24340.28,24337.490", "2026-04-17 21:46,24352.52,24358.85,24358.85,24347.66,24338.746", "2026-04-17 21:47,24361.33,24334.40,24372.97,24328.28,24338.504", "2026-04-17 21:48,24334.20,24313.21,24334.25,24307.44,24337.172", "2026-04-17 21:49,24314.50,24332.03,24332.83,24296.17,24336.914", "2026-04-17 21:50,24332.74,24348.43,24349.56,24332.74,24337.462", "2026-04-17 21:51,24349.68,24350.22,24365.81,24346.24,24338.041", "2026-04-17 21:52,24351.27,24378.17,24380.74,24349.81,24339.785", "2026-04-17 21:53,24377.32,24367.43,24379.49,24360.91,24340.936", "2026-04-17 21:54,24367.52,24365.59,24371.12,24362.14,24341.922", "2026-04-17 21:55,24365.29,24357.68,24365.93,24343.66,24342.528", "2026-04-17 21:56,24358.02,24349.16,24360.13,24349.16,24342.773", "2026-04-17 21:57,24349.43,24347.87,24352.62,24340.66,24342.955", "2026-04-17 21:58,24346.68,24356.80,24358.05,24343.85,24343.432", "2026-04-17 21:59,24356.47,24354.54,24360.65,24344.65,24343.802", "2026-04-17 22:00,24355.12,24371.77,24371.77,24355.12,24344.704", "2026-04-17 22:01,24373.23,24388.07,24388.07,24368.65,24346.059", "2026-04-17 22:02,24387.92,24390.83,24391.95,24384.74,24347.415", "2026-04-17 22:03,24389.98,24384.43,24390.15,24378.09,24348.503", "2026-04-17 22:04,24383.96,24383.44,24387.29,24379.06,24349.501", "2026-04-17 22:05,24382.71,24388.02,24391.91,24381.95,24350.570", "2026-04-17 22:06,24388.19,24388.26,24398.98,24383.98,24351.588", "2026-04-17 22:07,24388.45,24390.32,24395.07,24386.59,24352.607", "2026-04-17 22:08,24388.76,24389.92,24393.34,24383.67,24353.563", "2026-04-17 22:09,24389.92,24391.88,24397.06,24386.01,24354.520", "2026-04-17 22:10,24392.14,24395.87,24397.41,24391.13,24355.528", "2026-04-17 22:11,24396.13,24408.35,24409.10,24394.23,24356.785", "2026-04-17 22:12,24407.11,24401.43,24409.19,24398.23,24357.823", "2026-04-17 22:13,24401.98,24393.48,24404.11,24389.23,24358.633", "2026-04-17 22:14,24393.80,24403.14,24408.06,24393.28,24359.622", "2026-04-17 22:15,24401.96,24409.33,24409.53,24401.43,24360.702", "2026-04-17 22:16,24411.82,24408.09,24412.16,24403.23,24361.710", "2026-04-17 22:17,24409.04,24411.94,24411.94,24405.73,24362.756", "2026-04-17 22:18,24411.94,24396.04,24412.06,24393.70,24363.435", "2026-04-17 22:19,24396.48,24397.15,24402.14,24392.50,24364.109", "2026-04-17 22:20,24397.01,24398.43,24400.67,24393.12,24364.781", "2026-04-17 22:21,24396.02,24389.65,24396.02,24373.62,24365.259", "2026-04-17 22:22,24389.18,24390.51,24390.61,24379.21,24365.735", "2026-04-17 22:23,24390.69,24383.53,24395.55,24383.47,24366.064", "2026-04-17 22:24,24383.97,24376.92,24383.97,24371.07,24366.261", "2026-04-17 22:25,24376.62,24383.61,24384.64,24374.08,24366.570", "2026-04-17 22:26,24382.62,24380.60,24384.39,24378.42,24366.816", "2026-04-17 22:27,24380.69,24379.85,24389.26,24377.61,24367.040", "2026-04-17 22:28,24380.41,24381.65,24383.87,24372.95,24367.287", "2026-04-17 22:29,24381.37,24391.02,24392.40,24380.59,24367.682", "2026-04-17 22:30,24391.30,24386.73,24393.22,24385.71,24367.994", "2026-04-17 22:31,24388.32,24403.20,24404.45,24388.32,24368.561", "2026-04-17 22:32,24403.49,24413.89,24413.89,24403.49,24369.280", "2026-04-17 22:33,24414.17,24414.78,24420.34,24412.90,24369.990", "2026-04-17 22:34,24414.89,24437.08,24437.33,24414.22,24371.022", "2026-04-17 22:35,24437.24,24438.07,24438.21,24431.99,24372.037", "2026-04-17 22:36,24438.03,24425.79,24438.03,24418.27,24372.839", "2026-04-17 22:37,24424.98,24431.95,24431.95,24422.68,24373.708", "2026-04-17 22:38,24432.26,24437.50,24437.66,24431.77,24374.632", "2026-04-17 22:39,24437.41,24441.48,24441.48,24436.45,24375.586", "2026-04-17 22:40,24441.30,24451.18,24451.18,24438.51,24376.650", "2026-04-17 22:41,24450.42,24457.38,24467.01,24450.42,24377.771", "2026-04-17 22:42,24457.36,24465.95,24465.95,24457.36,24378.978", "2026-04-17 22:43,24465.21,24473.72,24474.85,24465.21,24380.258", "2026-04-17 22:44,24474.63,24466.64,24475.40,24464.92,24381.409", "2026-04-17 22:45,24466.91,24472.03,24474.29,24466.72,24382.601", "2026-04-17 22:46,24472.08,24476.88,24476.88,24469.49,24383.825", "2026-04-17 22:47,24477.17,24473.12,24479.13,24470.14,24384.969", "2026-04-17 22:48,24473.48,24477.54,24478.73,24472.95,24386.140", "2026-04-17 22:49,24476.68,24484.43,24486.92,24472.33,24387.368", "2026-04-17 22:50,24484.83,24489.35,24490.41,24484.83,24388.627", "2026-04-17 22:51,24488.81,24472.41,24490.89,24471.74,24389.648", "2026-04-17 22:52,24472.57,24481.05,24481.05,24470.80,24390.749", "2026-04-17 22:53,24481.27,24485.62,24489.19,24481.27,24391.878", "2026-04-17 22:54,24485.63,24481.96,24486.36,24480.39,24392.937", "2026-04-17 22:55,24482.75,24477.74,24483.10,24476.77,24393.923", "2026-04-17 22:56,24478.03,24447.77,24478.03,24446.91,24394.541", "2026-04-17 22:57,24447.23,24469.69,24470.75,24447.23,24395.394", "2026-04-17 22:58,24469.74,24477.68,24478.82,24469.74,24396.318", "2026-04-17 22:59,24479.17,24479.92,24481.45,24474.01,24397.246", "2026-04-17 23:00,24480.33,24466.57,24480.33,24462.56,24398.007", "2026-04-17 23:01,24468.20,24463.16,24468.41,24457.57,24398.715", "2026-04-17 23:02,24464.00,24469.26,24470.00,24460.92,24399.473", "2026-04-17 23:03,24468.21,24481.93,24482.17,24467.00,24400.350", "2026-04-17 23:04,24482.08,24463.66,24486.56,24461.86,24401.016", "2026-04-17 23:05,24464.64,24468.27,24470.66,24459.64,24401.716", "2026-04-17 23:06,24468.64,24474.53,24476.03,24466.75,24402.466", "2026-04-17 23:07,24475.04,24487.35,24487.35,24474.46,24403.332", "2026-04-17 23:08,24486.75,24487.39,24490.07,24482.06,24404.181", "2026-04-17 23:09,24487.21,24482.85,24487.21,24480.93,24404.967", "2026-04-17 23:10,24482.96,24484.45,24485.53,24480.78,24405.753", "2026-04-17 23:11,24484.08,24480.70,24490.54,24480.70,24406.487", "2026-04-17 23:12,24481.37,24468.92,24481.37,24468.92,24407.093", "2026-04-17 23:13,24469.72,24466.38,24476.94,24465.67,24407.663", "2026-04-17 23:14,24466.62,24461.41,24469.59,24458.59,24408.174", "2026-04-17 23:15,24461.25,24462.21,24469.33,24458.73,24408.683", "2026-04-17 23:16,24462.05,24475.48,24475.71,24461.98,24409.307", "2026-04-17 23:17,24475.43,24483.30,24485.00,24475.43,24409.992", "2026-04-17 23:18,24483.30,24485.39,24487.16,24483.07,24410.683", "2026-04-17 23:19,24485.24,24473.96,24485.27,24473.96,24411.258", "2026-04-17 23:20,24473.47,24462.11,24473.47,24455.08,24411.716", "2026-04-17 23:21,24462.11,24457.13,24462.33,24452.69,24412.121", "2026-04-17 23:22,24457.49,24467.81,24470.94,24454.07,24412.613", "2026-04-17 23:23,24467.41,24469.62,24470.22,24464.94,24413.113", "2026-04-17 23:24,24470.18,24482.21,24484.64,24470.18,24413.713", "2026-04-17 23:25,24482.40,24480.60,24482.72,24476.29,24414.289", "2026-04-17 23:26,24481.11,24477.95,24486.43,24477.95,24414.833", "2026-04-17 23:27,24478.05,24488.58,24488.58,24477.66,24415.457", "2026-04-17 23:28,24488.44,24483.34,24488.44,24481.95,24416.027", "2026-04-17 23:29,24483.59,24489.57,24493.70,24483.59,24416.639", "2026-04-17 23:30,24488.06,24485.53,24490.27,24482.22,24417.208", "2026-04-17 23:31,24485.81,24490.00,24496.25,24484.64,24417.804", "2026-04-17 23:32,24490.44,24506.92,24507.23,24489.79,24418.528", "2026-04-17 23:33,24507.29,24497.84,24509.55,24494.89,24419.167", "2026-04-17 23:34,24497.93,24507.17,24507.17,24497.93,24419.871", "2026-04-17 23:35,24507.63,24511.70,24512.13,24499.87,24420.599", "2026-04-17 23:36,24511.97,24510.32,24512.76,24508.60,24421.305", "2026-04-17 23:37,24510.48,24513.94,24518.65,24510.48,24422.028", "2026-04-17 23:38,24514.42,24503.07,24515.39,24500.03,24422.656", "2026-04-17 23:39,24502.86,24508.48,24509.96,24501.14,24423.316", "2026-04-17 23:40,24509.13,24510.94,24511.10,24505.69,24423.984", "2026-04-17 23:41,24511.20,24502.09,24511.54,24501.76,24424.575", "2026-04-17 23:42,24502.03,24496.59,24502.24,24493.84,24425.116", "2026-04-17 23:43,24497.15,24477.94,24497.15,24477.94,24425.510", "2026-04-17 23:44,24478.30,24468.66,24480.33,24468.59,24425.829", "2026-04-17 23:45,24468.57,24464.36,24470.90,24464.25,24426.112", "2026-04-17 23:46,24464.32,24478.44,24478.45,24464.32,24426.493", "2026-04-17 23:47,24478.92,24468.92,24479.40,24468.26,24426.800", "2026-04-17 23:48,24468.90,24470.67,24474.42,24467.25,24427.115", "2026-04-17 23:49,24470.20,24466.75,24470.20,24466.15,24427.398", "2026-04-17 23:50,24467.43,24475.70,24485.68,24463.49,24427.740", "2026-04-17 23:51,24476.20,24487.18,24488.91,24474.61,24428.158", "2026-04-17 23:52,24486.88,24491.32,24492.99,24485.05,24428.599", "2026-04-17 23:53,24491.13,24478.55,24491.13,24478.55,24428.945", "2026-04-17 23:54,24478.85,24480.80,24481.41,24474.60,24429.302", "2026-04-17 23:55,24480.99,24481.25,24485.91,24480.99,24429.657", "2026-04-17 23:56,24480.91,24478.11,24483.98,24478.11,24429.986", "2026-04-17 23:57,24478.10,24477.83,24479.69,24473.37,24430.309", "2026-04-17 23:58,24477.60,24477.87,24481.14,24475.58,24430.628", "2026-04-17 23:59,24477.79,24464.77,24477.91,24463.84,24430.855", "2026-04-18 00:00,24465.00,24453.55,24465.00,24452.18,24431.005", "2026-04-18 00:01,24453.87,24447.13,24453.87,24445.06,24431.111", "2026-04-18 00:02,24447.00,24461.19,24461.60,24447.00,24431.307", "2026-04-18 00:03,24461.58,24473.54,24473.65,24461.58,24431.581", "2026-04-18 00:04,24473.42,24481.46,24482.93,24472.30,24431.902", "2026-04-18 00:05,24481.32,24481.60,24482.70,24477.36,24432.220", "2026-04-18 00:06,24481.06,24487.42,24487.42,24479.76,24432.571", "2026-04-18 00:07,24487.63,24488.69,24488.69,24484.62,24432.926", "2026-04-18 00:08,24488.74,24492.21,24493.05,24486.88,24433.298", "2026-04-18 00:09,24492.50,24497.90,24502.32,24492.50,24433.701", "2026-04-18 00:10,24497.71,24486.80,24497.71,24486.20,24434.030", "2026-04-18 00:11,24486.52,24491.41,24493.14,24483.85,24434.384", "2026-04-18 00:12,24490.78,24496.53,24496.96,24489.18,24434.765", "2026-04-18 00:13,24496.59,24499.85,24500.80,24496.59,24435.161", "2026-04-18 00:14,24500.07,24492.90,24500.07,24492.31,24435.510", "2026-04-18 00:15,24492.87,24494.08,24497.43,24492.85,24435.862", "2026-04-18 00:16,24493.48,24494.38,24500.48,24492.08,24436.212", "2026-04-18 00:17,24495.17,24484.82,24496.32,24484.82,24436.501", "2026-04-18 00:18,24484.67,24475.52,24484.67,24474.08,24436.731", "2026-04-18 00:19,24474.36,24486.25,24488.85,24472.18,24437.022", "2026-04-18 00:20,24485.80,24483.90,24487.04,24482.25,24437.296", "2026-04-18 00:21,24483.91,24483.18,24485.81,24478.50,24437.562", "2026-04-18 00:22,24483.05,24485.39,24485.45,24482.50,24437.838", "2026-04-18 00:23,24485.45,24487.42,24489.83,24485.01,24438.122", "2026-04-18 00:24,24487.36,24490.58,24490.76,24487.36,24438.421", "2026-04-18 00:25,24491.45,24495.44,24495.44,24490.88,24438.744", "2026-04-18 00:26,24495.07,24497.26,24498.85,24492.97,24439.074", "2026-04-18 00:27,24497.21,24498.64,24498.79,24494.12,24439.408", "2026-04-18 00:28,24498.87,24496.82,24498.99,24495.69,24439.728", "2026-04-18 00:29,24496.75,24495.42,24499.86,24495.21,24440.037", "2026-04-18 00:30,24495.19,24497.64,24498.60,24492.74,24440.355", "2026-04-18 00:31,24497.79,24509.88,24509.88,24497.79,24440.737", "2026-04-18 00:32,24509.46,24513.59,24513.59,24508.73,24441.135", "2026-04-18 00:33,24513.72,24511.17,24513.74,24508.96,24441.515", "2026-04-18 00:34,24511.35,24505.53,24514.29,24505.53,24441.861", "2026-04-18 00:35,24505.57,24508.13,24508.20,24505.06,24442.217", "2026-04-18 00:36,24508.61,24509.57,24513.01,24508.25,24442.577", "2026-04-18 00:37,24509.15,24516.32,24517.25,24508.11,24442.969", "2026-04-18 00:38,24516.18,24515.84,24519.01,24515.54,24443.354", "2026-04-18 00:39,24515.44,24517.44,24518.37,24512.50,24443.743", "2026-04-18 00:40,24517.52,24513.27,24518.16,24513.27,24444.107", "2026-04-18 00:41,24513.45,24512.97,24514.40,24510.07,24444.465", "2026-04-18 00:42,24513.24,24504.75,24513.24,24504.75,24444.777", "2026-04-18 00:43,24504.39,24503.91,24504.39,24501.06,24445.081", "2026-04-18 00:44,24503.92,24504.35,24506.32,24503.92,24445.384", "2026-04-18 00:45,24504.46,24510.90,24510.90,24504.46,24445.718", "2026-04-18 00:46,24511.19,24516.54,24517.12,24509.65,24446.077", "2026-04-18 00:47,24516.63,24517.67,24518.72,24515.99,24446.438", "2026-04-18 00:48,24517.63,24514.62,24519.51,24514.62,24446.780", "2026-04-18 00:49,24514.42,24518.06,24518.98,24512.94,24447.136", "2026-04-18 00:50,24517.65,24512.62,24518.06,24510.97,24447.461", "2026-04-18 00:51,24512.75,24512.08,24513.83,24510.62,24447.780", "2026-04-18 00:52,24512.05,24514.38,24514.57,24510.43,24448.108", "2026-04-18 00:53,24514.43,24508.87,24514.82,24508.87,24448.405", "2026-04-18 00:54,24509.11,24510.20,24510.58,24504.36,24448.706", "2026-04-18 00:55,24510.03,24505.06,24510.03,24502.97,24448.979", "2026-04-18 00:56,24504.69,24500.51,24505.81,24500.34,24449.227", "2026-04-18 00:57,24500.47,24498.08,24501.70,24498.08,24449.461", "2026-04-18 00:58,24497.68,24498.00,24498.37,24495.66,24449.693", "2026-04-18 00:59,24497.85,24501.37,24503.25,24497.85,24449.939", "2026-04-18 01:00,24501.68,24498.21,24502.22,24495.77,24450.167", "2026-04-18 01:01,24498.13,24498.40,24502.40,24496.81,24450.394", "2026-04-18 01:02,24498.38,24504.04,24504.30,24497.80,24450.645", "2026-04-18 01:03,24504.35,24505.46,24506.17,24501.53,24450.901", "2026-04-18 01:04,24505.85,24508.73,24511.41,24505.85,24451.169", "2026-04-18 01:05,24508.85,24511.19,24511.96,24508.09,24451.446", "2026-04-18 01:06,24511.20,24507.71,24511.37,24505.07,24451.705", "2026-04-18 01:07,24508.20,24509.82,24512.33,24508.20,24451.971", "2026-04-18 01:08,24509.50,24505.78,24511.17,24505.78,24452.216", "2026-04-18 01:09,24505.98,24463.98,24505.98,24463.51,24452.269", "2026-04-18 01:10,24467.55,24480.84,24482.67,24467.55,24452.398", "2026-04-18 01:11,24482.17,24479.75,24484.10,24479.75,24452.521", "2026-04-18 01:12,24479.65,24472.36,24479.65,24470.54,24452.609", "2026-04-18 01:13,24472.35,24472.60,24475.00,24468.25,24452.698", "2026-04-18 01:14,24473.14,24476.52,24478.41,24470.46,24452.803", "2026-04-18 01:15,24476.29,24479.87,24481.75,24474.65,24452.922", "2026-04-18 01:16,24480.08,24474.60,24484.08,24474.34,24453.017", "2026-04-18 01:17,24475.00,24479.89,24480.27,24474.95,24453.134", "2026-04-18 01:18,24479.71,24466.36,24480.86,24466.36,24453.191", "2026-04-18 01:19,24466.42,24469.18,24469.18,24461.77,24453.260", "2026-04-18 01:20,24469.30,24462.28,24469.77,24459.39,24453.299", "2026-04-18 01:21,24461.78,24441.34,24461.78,24441.22,24453.247", "2026-04-18 01:22,24442.13,24435.46,24442.75,24429.69,24453.170", "2026-04-18 01:23,24435.86,24445.62,24445.78,24435.54,24453.137", "2026-04-18 01:24,24445.60,24461.10,24462.16,24445.01,24453.170", "2026-04-18 01:25,24460.38,24406.99,24460.38,24390.96,24452.974", "2026-04-18 01:26,24407.81,24412.61,24420.58,24407.81,24452.803", "2026-04-18 01:27,24412.83,24410.07,24412.83,24393.01,24452.623", "2026-04-18 01:28,24409.52,24421.39,24422.85,24404.87,24452.492", "2026-04-18 01:29,24420.68,24410.57,24421.65,24410.03,24452.317", "2026-04-18 01:30,24410.69,24419.74,24421.16,24410.69,24452.181", "2026-04-18 01:31,24418.86,24433.13,24433.95,24417.07,24452.102", "2026-04-18 01:32,24433.00,24426.10,24436.88,24426.00,24451.994", "2026-04-18 01:33,24426.11,24424.94,24426.11,24416.77,24451.883", "2026-04-18 01:34,24425.15,24417.71,24425.15,24415.77,24451.743", "2026-04-18 01:35,24417.95,24420.57,24426.95,24417.95,24451.616", "2026-04-18 01:36,24420.57,24413.65,24421.50,24413.43,24451.462", "2026-04-18 01:37,24413.62,24413.72,24416.39,24413.08,24451.309", "2026-04-18 01:38,24413.92,24440.26,24440.89,24413.92,24451.264", "2026-04-18 01:39,24441.10,24438.83,24444.13,24435.65,24451.214", "2026-04-18 01:40,24439.14,24434.41,24439.23,24431.87,24451.147", "2026-04-18 01:41,24434.86,24436.64,24440.21,24434.64,24451.089", "2026-04-18 01:42,24436.05,24435.87,24438.58,24431.54,24451.028", "2026-04-18 01:43,24434.30,24440.31,24440.52,24432.93,24450.985", "2026-04-18 01:44,24439.05,24433.61,24439.13,24433.12,24450.916", "2026-04-18 01:45,24432.50,24436.45,24438.01,24431.15,24450.859", "2026-04-18 01:46,24436.90,24447.81,24448.37,24436.53,24450.847", "2026-04-18 01:47,24448.12,24462.38,24462.38,24448.12,24450.891", "2026-04-18 01:48,24461.73,24467.13,24467.44,24461.27,24450.953", "2026-04-18 01:49,24466.93,24462.45,24466.93,24462.22,24450.997", "2026-04-18 01:50,24462.35,24457.05,24463.01,24456.06,24451.020", "2026-04-18 01:51,24455.94,24461.60,24461.69,24454.14,24451.060", "2026-04-18 01:52,24461.66,24459.59,24461.72,24455.03,24451.092", "2026-04-18 01:53,24458.84,24456.77,24460.59,24456.77,24451.113", "2026-04-18 01:54,24456.80,24461.50,24461.57,24456.17,24451.152", "2026-04-18 01:55,24461.09,24457.26,24461.09,24457.26,24451.174", "2026-04-18 01:56,24457.16,24459.13,24461.58,24456.81,24451.203", "2026-04-18 01:57,24459.38,24462.73,24462.85,24456.99,24451.246", "2026-04-18 01:58,24463.14,24460.04,24464.07,24459.60,24451.278", "2026-04-18 01:59,24460.04,24452.17,24460.73,24452.11,24451.281", "2026-04-18 02:00,24452.24,24449.76,24452.24,24448.96,24451.275", "2026-04-18 02:01,24449.89,24451.04,24457.12,24449.89,24451.274", "2026-04-18 02:02,24451.02,24458.29,24458.42,24449.07,24451.299", "2026-04-18 02:03,24458.61,24452.73,24460.51,24452.73,24451.304", "2026-04-18 02:04,24452.46,24440.75,24455.86,24438.62,24451.265", "2026-04-18 02:05,24440.93,24440.53,24442.77,24437.08,24451.226", "2026-04-18 02:06,24440.67,24436.62,24442.06,24434.77,24451.173", "2026-04-18 02:07,24436.97,24441.21,24441.21,24430.62,24451.137", "2026-04-18 02:08,24440.60,24433.66,24440.60,24431.49,24451.074", "2026-04-18 02:09,24433.95,24424.75,24434.55,24424.75,24450.979", "2026-04-18 02:10,24425.15,24421.24,24426.13,24420.81,24450.873", "2026-04-18 02:11,24420.69,24418.06,24428.66,24418.06,24450.756", "2026-04-18 02:12,24418.70,24420.48,24423.57,24416.01,24450.649", "2026-04-18 02:13,24420.37,24425.38,24425.85,24418.83,24450.560", "2026-04-18 02:14,24425.24,24412.79,24425.51,24412.79,24450.427", "2026-04-18 02:15,24412.42,24411.02,24412.42,24406.83,24450.289", "2026-04-18 02:16,24410.95,24421.59,24423.45,24410.95,24450.189", "2026-04-18 02:17,24421.44,24420.05,24422.32,24417.88,24450.084", "2026-04-18 02:18,24420.43,24425.83,24426.16,24419.18,24450.000", "2026-04-18 02:19,24427.39,24426.24,24429.65,24426.16,24449.918", "2026-04-18 02:20,24426.37,24417.94,24427.87,24416.18,24449.808", "2026-04-18 02:21,24419.31,24410.14,24420.32,24410.14,24449.672", "2026-04-18 02:22,24409.73,24403.79,24411.73,24402.58,24449.515", "2026-04-18 02:23,24403.66,24404.09,24405.68,24397.81,24449.360", "2026-04-18 02:24,24404.29,24416.21,24416.88,24398.53,24449.247", "2026-04-18 02:25,24416.28,24424.58,24425.04,24416.28,24449.163", "2026-04-18 02:26,24424.36,24442.81,24444.12,24423.25,24449.141", "2026-04-18 02:27,24441.88,24441.99,24445.27,24438.42,24449.117", "2026-04-18 02:28,24441.10,24439.80,24442.27,24438.36,24449.085", "2026-04-18 02:29,24439.66,24430.38,24439.66,24426.04,24449.022", "2026-04-18 02:30,24429.15,24423.95,24429.15,24420.65,24448.938", "2026-04-18 02:31,24424.02,24434.57,24435.98,24424.02,24448.890", "2026-04-18 02:32,24434.23,24433.78,24434.76,24427.31,24448.840", "2026-04-18 02:33,24433.73,24436.85,24439.66,24433.73,24448.800", "2026-04-18 02:34,24436.85,24444.87,24446.54,24436.62,24448.787", "2026-04-18 02:35,24444.89,24444.62,24446.33,24443.16,24448.773", "2026-04-18 02:36,24444.79,24444.63,24445.77,24440.88,24448.759", "2026-04-18 02:37,24444.69,24449.19,24449.83,24444.69,24448.760", "2026-04-18 02:38,24449.23,24448.61,24450.59,24447.94,24448.759", "2026-04-18 02:39,24448.17,24451.37,24452.19,24448.17,24448.767", "2026-04-18 02:40,24451.72,24446.06,24451.72,24443.55,24448.758", "2026-04-18 02:41,24446.00,24448.34,24450.97,24445.07,24448.756", "2026-04-18 02:42,24448.27,24442.31,24448.27,24442.15,24448.735", "2026-04-18 02:43,24442.31,24432.49,24442.73,24431.50,24448.683", "2026-04-18 02:44,24432.54,24435.79,24435.94,24430.01,24448.642", "2026-04-18 02:45,24435.83,24442.33,24442.33,24435.33,24448.622", "2026-04-18 02:46,24442.07,24442.53,24444.93,24441.44,24448.602", "2026-04-18 02:47,24442.92,24443.46,24443.46,24439.73,24448.585", "2026-04-18 02:48,24443.79,24442.18,24449.15,24441.81,24448.564", "2026-04-18 02:49,24442.24,24443.88,24447.32,24442.24,24448.549", "2026-04-18 02:50,24443.77,24439.52,24445.06,24439.10,24448.520", "2026-04-18 02:51,24440.04,24435.47,24440.54,24435.22,24448.479", "2026-04-18 02:52,24434.54,24428.83,24437.20,24428.58,24448.418", "2026-04-18 02:53,24428.79,24423.64,24428.92,24418.32,24448.341", "2026-04-18 02:54,24423.87,24423.07,24423.92,24417.41,24448.263", "2026-04-18 02:55,24423.20,24420.59,24424.88,24411.18,24448.178", "2026-04-18 02:56,24420.74,24429.33,24429.33,24419.21,24448.120", "2026-04-18 02:57,24429.05,24430.45,24437.12,24429.05,24448.066", "2026-04-18 02:58,24430.44,24432.35,24433.71,24427.37,24448.018", "2026-04-18 02:59,24431.66,24427.50,24434.70,24426.82,24447.955", "2026-04-18 03:00,24427.56,24426.71,24432.15,24426.11,24447.890", "2026-04-18 03:01,24427.30,24427.89,24430.92,24425.49,24447.829", "2026-04-18 03:02,24427.87,24432.09,24432.09,24426.46,24447.781", "2026-04-18 03:03,24431.98,24431.76,24434.35,24429.38,24447.733", "2026-04-18 03:04,24429.84,24425.07,24429.84,24424.67,24447.665", "2026-04-18 03:05,24425.27,24424.31,24426.55,24421.90,24447.595", "2026-04-18 03:06,24424.19,24416.47,24424.19,24416.24,24447.502", "2026-04-18 03:07,24416.15,24416.87,24417.21,24410.09,24447.411", "2026-04-18 03:08,24417.19,24416.56,24422.55,24415.57,24447.319", "2026-04-18 03:09,24416.55,24418.51,24418.51,24412.48,24447.234", "2026-04-18 03:10,24418.30,24415.64,24418.49,24412.10,24447.141", "2026-04-18 03:11,24415.95,24407.49,24417.38,24407.49,24447.025", "2026-04-18 03:12,24407.47,24405.67,24410.34,24405.64,24446.904", "2026-04-18 03:13,24405.57,24404.96,24405.57,24400.58,24446.782", "2026-04-18 03:14,24405.54,24400.80,24407.33,24400.80,24446.648", "2026-04-18 03:15,24400.36,24404.38,24407.20,24398.82,24446.525", "2026-04-18 03:16,24404.55,24414.63,24414.63,24403.49,24446.433", "2026-04-18 03:17,24414.41,24421.26,24421.69,24414.35,24446.360", "2026-04-18 03:18,24422.18,24413.62,24422.94,24412.73,24446.266", "2026-04-18 03:19,24413.86,24421.26,24421.26,24413.01,24446.194", "2026-04-18 03:20,24421.36,24419.78,24423.73,24416.40,24446.118", "2026-04-18 03:21,24420.48,24420.26,24425.88,24419.25,24446.044", "2026-04-18 03:22,24420.32,24422.79,24424.48,24417.17,24445.978", "2026-04-18 03:23,24422.84,24421.21,24424.36,24419.76,24445.908", "2026-04-18 03:24,24421.61,24420.32,24422.14,24419.69,24445.835", "2026-04-18 03:25,24420.37,24425.93,24425.96,24417.59,24445.779", "2026-04-18 03:26,24425.91,24428.69,24432.36,24425.58,24445.731", "2026-04-18 03:27,24427.85,24426.67,24428.52,24425.06,24445.677", "2026-04-18 03:28,24426.52,24423.68,24426.52,24421.75,24445.615", "2026-04-18 03:29,24423.85,24419.02,24426.81,24419.02,24445.541", "2026-04-18 03:30,24417.98,24420.26,24421.14,24417.90,24445.470", "2026-04-18 03:31,24420.06,24425.91,24426.15,24420.06,24445.415", "2026-04-18 03:32,24426.26,24427.69,24431.79,24426.26,24445.366", "2026-04-18 03:33,24427.68,24437.49,24437.56,24427.68,24445.344", "2026-04-18 03:34,24438.06,24446.18,24446.29,24437.72,24445.346", "2026-04-18 03:35,24445.76,24444.40,24447.01,24443.17,24445.343", "2026-04-18 03:36,24444.04,24441.43,24446.88,24440.61,24445.332", "2026-04-18 03:37,24441.33,24437.81,24441.33,24434.97,24445.311", "2026-04-18 03:38,24437.79,24440.17,24440.18,24434.08,24445.297", "2026-04-18 03:39,24440.63,24450.80,24451.59,24440.58,24445.311", "2026-04-18 03:40,24449.74,24452.88,24455.28,24449.22,24445.331", "2026-04-18 03:41,24452.99,24460.88,24464.94,24446.86,24445.372", "2026-04-18 03:42,24460.52,24455.56,24460.52,24453.48,24445.399", "2026-04-18 03:43,24455.42,24466.17,24468.72,24455.20,24445.454", "2026-04-18 03:44,24466.27,24466.46,24468.25,24463.22,24445.510", "2026-04-18 03:45,24466.28,24465.32,24466.91,24461.22,24445.562", "2026-04-18 03:46,24464.93,24455.97,24464.93,24455.92,24445.589", "2026-04-18 03:47,24455.95,24458.76,24459.58,24455.00,24445.623", "2026-04-18 03:48,24459.17,24448.48,24459.88,24448.47,24445.630", "2026-04-18 03:49,24448.48,24450.02,24452.76,24448.23,24445.641", "2026-04-18 03:50,24450.64,24451.94,24452.40,24449.17,24445.657", "2026-04-18 03:51,24458.68,24450.46,24459.42,24447.49,24445.669", "2026-04-18 03:52,24450.06,24450.90,24452.14,24443.23,24445.682", "2026-04-18 03:53,24450.57,24442.57,24453.18,24442.04,24445.673", "2026-04-18 03:54,24441.73,24449.02,24451.81,24438.27,24445.681", "2026-04-18 03:55,24448.52,24459.36,24459.36,24448.20,24445.716", "2026-04-18 03:56,24464.08,24460.45,24468.22,24457.56,24445.754", "2026-04-18 03:57,24460.25,24457.59,24467.69,24457.55,24445.784", "2026-04-18 03:58,24457.99,24463.54,24463.54,24450.66,24445.829", "2026-04-18 03:59,24463.34,24468.41,24468.72,24462.53,24445.886", "2026-04-18 04:00,24468.89,24468.48,24471.08,24461.04,24445.943"]
+    }
+});</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=100.NDX&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp154</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取美股纳斯达克指数行情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>miniquotechart_jp156({
+    "rc": 0,
+    "rt": 10,
+    "svr": 180606310,
+    "lt": 1,
+    "full": 1,
+    "dlmkts": "",
+    "data": {
+        "code": "SPX",
+        "market": 100,
+        "type": 0,
+        "status": 0,
+        "name": "标普500",
+        "decimal": 2,
+        "preSettlement": 7041.28,
+        "preClose": 7041.28,
+        "beticks": "77400|77400|100800|77400|100800",
+        "trendsTotal": 391,
+        "time": 1776455989,
+        "kind": 2,
+        "prePrice": 7041.28,
+        "tradePeriods": {
+            "pre": null,
+            "after": null,
+            "periods": [{
+                "b": 202604172130,
+                "e": 202604180400
+            }]
+        },
+        "hisPrePrices": [{
+            "date": 20260417,
+            "prePrice": 7041.28
+        }],
+        "trends": ["2026-04-17 21:30,7074.55,7074.55,7074.55,7074.55,7074.550", "2026-04-17 21:31,7074.55,7084.99,7088.45,7084.99,7079.770", "2026-04-17 21:32,7085.56,7092.94,7092.94,7085.56,7084.160", "2026-04-17 21:33,7090.89,7091.54,7092.54,7090.89,7086.005", "2026-04-17 21:34,7092.98,7088.20,7092.98,7088.20,7086.444", "2026-04-17 21:35,7088.52,7095.37,7095.37,7088.52,7087.931", "2026-04-17 21:36,7093.65,7096.86,7096.90,7093.65,7089.206", "2026-04-17 21:37,7097.21,7097.66,7098.19,7097.19,7090.262", "2026-04-17 21:38,7098.11,7098.30,7099.07,7098.11,7091.155", "2026-04-17 21:39,7099.17,7097.37,7099.17,7094.86,7091.776", "2026-04-17 21:40,7098.82,7096.14,7098.82,7095.79,7092.172", "2026-04-17 21:41,7095.15,7092.92,7095.15,7092.78,7092.234", "2026-04-17 21:42,7092.98,7092.44,7093.07,7092.44,7092.249", "2026-04-17 21:43,7093.09,7095.14,7095.14,7092.89,7092.455", "2026-04-17 21:44,7094.55,7093.95,7094.55,7091.96,7092.554", "2026-04-17 21:45,7092.48,7096.47,7096.47,7092.48,7092.798", "2026-04-17 21:46,7095.82,7093.91,7095.82,7093.91,7092.863", "2026-04-17 21:47,7097.14,7097.08,7097.19,7097.08,7093.097", "2026-04-17 21:48,7089.82,7088.35,7089.89,7088.35,7092.847", "2026-04-17 21:49,7086.86,7088.97,7088.97,7083.53,7092.653", "2026-04-17 21:50,7091.50,7092.79,7093.06,7091.42,7092.659", "2026-04-17 21:51,7094.79,7098.51,7098.51,7094.79,7092.924", "2026-04-17 21:52,7095.37,7101.46,7101.46,7095.37,7093.295", "2026-04-17 21:53,7100.86,7100.44,7101.77,7100.44,7093.592", "2026-04-17 21:54,7100.94,7102.01,7102.01,7100.68,7093.928", "2026-04-17 21:55,7102.09,7099.99,7102.09,7099.73,7094.161", "2026-04-17 21:56,7101.44,7101.95,7101.95,7101.44,7094.449", "2026-04-17 21:57,7100.63,7101.59,7101.59,7100.63,7094.704", "2026-04-17 21:58,7102.52,7105.64,7105.64,7102.52,7095.081", "2026-04-17 21:59,7105.14,7103.51,7105.14,7103.51,7095.361", "2026-04-17 22:00,7104.96,7107.74,7107.74,7104.96,7095.760", "2026-04-17 22:01,7106.19,7108.81,7108.81,7106.19,7096.167", "2026-04-17 22:02,7110.57,7110.02,7110.63,7110.02,7096.586", "2026-04-17 22:03,7111.23,7109.85,7111.23,7109.85,7096.976", "2026-04-17 22:04,7110.06,7109.82,7110.08,7109.82,7097.342", "2026-04-17 22:05,7110.12,7112.28,7112.38,7110.12,7097.756", "2026-04-17 22:06,7112.35,7114.92,7114.97,7112.35,7098.219", "2026-04-17 22:07,7113.14,7113.28,7114.87,7113.14,7098.615", "2026-04-17 22:08,7113.89,7114.64,7114.70,7113.89,7099.025", "2026-04-17 22:09,7114.13,7114.82,7114.82,7114.09,7099.419", "2026-04-17 22:10,7113.84,7114.83,7114.83,7113.84,7099.794", "2026-04-17 22:11,7115.20,7117.13,7117.19,7115.20,7100.206", "2026-04-17 22:12,7117.32,7114.71,7117.32,7114.71,7100.543", "2026-04-17 22:13,7114.64,7111.93,7114.64,7111.77,7100.801", "2026-04-17 22:14,7113.34,7115.33,7115.35,7113.34,7101.123", "2026-04-17 22:15,7114.57,7115.15,7115.75,7114.57,7101.427", "2026-04-17 22:16,7115.92,7115.64,7115.92,7114.94,7101.729", "2026-04-17 22:17,7116.51,7116.86,7116.86,7115.53,7102.044", "2026-04-17 22:18,7117.09,7115.54,7117.09,7115.54,7102.319", "2026-04-17 22:19,7113.84,7115.13,7115.13,7113.84,7102.575", "2026-04-17 22:20,7114.43,7114.27,7114.52,7114.27,7102.804", "2026-04-17 22:21,7114.14,7114.18,7114.18,7113.27,7103.022", "2026-04-17 22:22,7115.05,7114.80,7115.05,7114.07,7103.244", "2026-04-17 22:23,7116.31,7116.23,7117.17,7116.23,7103.484", "2026-04-17 22:24,7115.15,7114.65,7115.15,7113.42,7103.687", "2026-04-17 22:25,7114.60,7116.38,7116.38,7114.54,7103.913", "2026-04-17 22:26,7116.28,7116.00,7116.34,7116.00,7104.125", "2026-04-17 22:27,7116.25,7115.53,7116.30,7115.53,7104.321", "2026-04-17 22:28,7115.76,7116.07,7116.07,7115.54,7104.520", "2026-04-17 22:29,7115.55,7116.62,7116.62,7115.55,7104.721", "2026-04-17 22:30,7117.25,7117.29,7117.29,7116.71,7104.927", "2026-04-17 22:31,7116.27,7118.14,7118.49,7116.27,7105.140", "2026-04-17 22:32,7117.36,7118.48,7118.48,7117.36,7105.351", "2026-04-17 22:33,7119.97,7120.36,7121.08,7119.97,7105.585", "2026-04-17 22:34,7120.19,7124.97,7124.97,7120.19,7105.883", "2026-04-17 22:35,7126.17,7125.22,7126.17,7125.22,7106.175", "2026-04-17 22:36,7125.35,7121.90,7125.35,7121.82,7106.409", "2026-04-17 22:37,7122.77,7124.07,7124.33,7122.77,7106.668", "2026-04-17 22:38,7125.20,7124.45,7125.20,7124.45,7106.925", "2026-04-17 22:39,7125.46,7126.05,7126.30,7125.46,7107.198", "2026-04-17 22:40,7125.87,7126.18,7126.23,7125.87,7107.465", "2026-04-17 22:41,7127.06,7128.55,7129.88,7127.06,7107.757", "2026-04-17 22:42,7129.26,7130.59,7130.59,7129.26,7108.069", "2026-04-17 22:43,7131.44,7133.36,7133.36,7131.44,7108.410", "2026-04-17 22:44,7133.50,7131.75,7133.60,7131.75,7108.721", "2026-04-17 22:45,7131.78,7132.36,7132.36,7131.78,7109.032", "2026-04-17 22:46,7133.04,7132.72,7133.04,7132.45,7109.339", "2026-04-17 22:47,7133.68,7132.67,7133.68,7132.67,7109.638", "2026-04-17 22:48,7133.11,7133.09,7133.35,7133.09,7109.934", "2026-04-17 22:49,7133.54,7134.91,7134.91,7133.54,7110.246", "2026-04-17 22:50,7134.76,7136.53,7136.53,7134.76,7110.570", "2026-04-17 22:51,7136.35,7134.71,7136.35,7134.71,7110.864", "2026-04-17 22:52,7132.90,7135.43,7135.43,7132.90,7111.159", "2026-04-17 22:53,7135.28,7136.34,7136.34,7135.28,7111.458", "2026-04-17 22:54,7135.41,7134.15,7135.41,7134.15,7111.724", "2026-04-17 22:55,7134.44,7133.27,7134.44,7132.95,7111.974", "2026-04-17 22:56,7133.33,7129.23,7133.33,7129.23,7112.172", "2026-04-17 22:57,7126.54,7129.87,7129.87,7126.49,7112.373", "2026-04-17 22:58,7131.05,7131.68,7131.68,7131.05,7112.589", "2026-04-17 22:59,7132.05,7131.28,7132.10,7131.28,7112.796", "2026-04-17 23:00,7132.03,7128.88,7132.03,7128.88,7112.972", "2026-04-17 23:01,7129.16,7127.15,7129.16,7127.15,7113.126", "2026-04-17 23:02,7128.27,7128.56,7129.28,7128.27,7113.291", "2026-04-17 23:03,7129.98,7131.69,7131.69,7129.90,7113.486", "2026-04-17 23:04,7132.41,7133.30,7133.70,7132.41,7113.694", "2026-04-17 23:05,7129.08,7131.38,7131.72,7129.08,7113.878", "2026-04-17 23:06,7130.91,7132.23,7132.23,7130.91,7114.067", "2026-04-17 23:07,7132.21,7133.42,7133.42,7132.21,7114.264", "2026-04-17 23:08,7135.11,7134.95,7135.11,7134.82,7114.472", "2026-04-17 23:09,7134.59,7133.02,7134.59,7133.02,7114.657", "2026-04-17 23:10,7133.62,7132.81,7134.28,7132.81,7114.836", "2026-04-17 23:11,7133.13,7134.15,7134.15,7132.82,7115.025", "2026-04-17 23:12,7131.46,7128.83,7131.46,7128.83,7115.159", "2026-04-17 23:13,7128.40,7127.99,7128.94,7127.99,7115.282", "2026-04-17 23:14,7127.45,7126.49,7127.99,7126.49,7115.388", "2026-04-17 23:15,7126.74,7125.92,7127.68,7125.92,7115.487", "2026-04-17 23:16,7126.27,7129.08,7129.08,7126.27,7115.614", "2026-04-17 23:17,7128.48,7130.81,7130.81,7128.48,7115.754", "2026-04-17 23:18,7130.61,7130.73,7130.73,7130.61,7115.891", "2026-04-17 23:19,7130.85,7128.83,7130.85,7128.83,7116.008", "2026-04-17 23:20,7128.15,7123.62,7128.15,7123.62,7116.076", "2026-04-17 23:21,7125.88,7124.21,7125.94,7124.21,7116.148", "2026-04-17 23:22,7124.73,7127.18,7127.18,7124.51,7116.245", "2026-04-17 23:23,7126.98,7126.68,7126.98,7126.68,7116.336", "2026-04-17 23:24,7126.93,7129.42,7129.42,7126.93,7116.449", "2026-04-17 23:25,7129.37,7128.46,7129.37,7127.97,7116.552", "2026-04-17 23:26,7128.80,7129.04,7129.09,7128.80,7116.658", "2026-04-17 23:27,7127.67,7128.94,7128.94,7127.67,7116.762", "2026-04-17 23:28,7129.80,7128.64,7129.80,7128.64,7116.861", "2026-04-17 23:29,7128.19,7130.57,7130.57,7128.19,7116.975", "2026-04-17 23:30,7129.96,7129.10,7130.29,7129.10,7117.075", "2026-04-17 23:31,7130.00,7131.41,7131.71,7130.00,7117.192", "2026-04-17 23:32,7130.68,7134.06,7134.06,7130.68,7117.329", "2026-04-17 23:33,7134.72,7132.26,7134.72,7132.26,7117.449", "2026-04-17 23:34,7133.21,7134.67,7134.67,7133.17,7117.586", "2026-04-17 23:35,7135.09,7134.99,7135.09,7133.85,7117.724", "2026-04-17 23:36,7136.41,7135.71,7136.41,7135.67,7117.865", "2026-04-17 23:37,7135.95,7136.26,7137.12,7135.95,7118.008", "2026-04-17 23:38,7136.53,7135.20,7136.53,7135.20,7118.141", "2026-04-17 23:39,7134.11,7136.01,7136.01,7134.11,7118.278", "2026-04-17 23:40,7136.47,7136.19,7136.47,7136.19,7118.414", "2026-04-17 23:41,7136.70,7135.77,7136.70,7135.77,7118.545", "2026-04-17 23:42,7135.29,7134.73,7135.29,7134.38,7118.666", "2026-04-17 23:43,7134.00,7131.10,7134.00,7131.10,7118.758", "2026-04-17 23:44,7130.76,7129.66,7131.05,7129.66,7118.838", "2026-04-17 23:45,7128.99,7128.36,7129.02,7128.36,7118.908", "2026-04-17 23:46,7128.10,7130.76,7130.76,7128.10,7118.994", "2026-04-17 23:47,7131.43,7129.88,7131.43,7129.88,7119.072", "2026-04-17 23:48,7129.12,7130.38,7130.38,7129.12,7119.153", "2026-04-17 23:49,7129.95,7130.24,7130.24,7129.95,7119.232", "2026-04-17 23:50,7129.86,7132.75,7132.75,7129.36,7119.327", "2026-04-17 23:51,7132.33,7135.46,7135.46,7132.33,7119.440", "2026-04-17 23:52,7135.71,7136.87,7136.87,7135.71,7119.561", "2026-04-17 23:53,7136.71,7135.57,7136.71,7135.56,7119.672", "2026-04-17 23:54,7134.17,7134.36,7134.64,7134.17,7119.773", "2026-04-17 23:55,7135.10,7135.75,7135.75,7135.10,7119.882", "2026-04-17 23:56,7134.78,7135.70,7135.71,7134.78,7119.989", "2026-04-17 23:57,7134.54,7134.86,7134.88,7134.54,7120.089", "2026-04-17 23:58,7135.13,7135.51,7135.65,7135.13,7120.192", "2026-04-17 23:59,7135.08,7132.42,7135.08,7132.42,7120.273", "2026-04-18 00:00,7132.63,7132.05,7132.63,7132.05,7120.350", "2026-04-18 00:01,7131.01,7130.76,7131.01,7130.26,7120.418", "2026-04-18 00:02,7130.15,7133.15,7133.15,7130.15,7120.501", "2026-04-18 00:03,7133.59,7136.24,7136.24,7133.59,7120.603", "2026-04-18 00:04,7136.20,7137.81,7137.81,7136.20,7120.714", "2026-04-18 00:05,7137.22,7137.16,7137.22,7136.85,7120.819", "2026-04-18 00:06,7136.73,7137.26,7137.26,7136.73,7120.923", "2026-04-18 00:07,7137.21,7137.07,7137.27,7137.07,7121.025", "2026-04-18 00:08,7137.23,7137.65,7137.65,7137.23,7121.129", "2026-04-18 00:09,7137.57,7139.00,7139.47,7137.57,7121.240", "2026-04-18 00:10,7138.91,7136.01,7138.91,7136.01,7121.331", "2026-04-18 00:11,7135.85,7137.00,7137.31,7135.85,7121.427", "2026-04-18 00:12,7137.37,7138.23,7138.23,7137.37,7121.530", "2026-04-18 00:13,7139.06,7139.77,7139.77,7139.06,7121.641", "2026-04-18 00:14,7139.60,7138.45,7139.60,7138.11,7121.742", "2026-04-18 00:15,7138.09,7137.92,7138.63,7137.85,7121.839", "2026-04-18 00:16,7137.69,7138.41,7138.66,7137.69,7121.938", "2026-04-18 00:17,7138.01,7136.77,7138.01,7136.77,7122.026", "2026-04-18 00:18,7135.87,7134.14,7135.87,7134.14,7122.097", "2026-04-18 00:19,7133.86,7134.68,7134.68,7133.86,7122.171", "2026-04-18 00:20,7136.76,7136.74,7136.84,7136.74,7122.256", "2026-04-18 00:21,7136.54,7135.76,7136.54,7135.66,7122.334", "2026-04-18 00:22,7136.17,7136.81,7136.81,7136.17,7122.417", "2026-04-18 00:23,7137.23,7137.47,7137.47,7136.74,7122.503", "2026-04-18 00:24,7137.07,7137.55,7137.66,7137.07,7122.588", "2026-04-18 00:25,7138.40,7138.79,7138.79,7138.40,7122.680", "2026-04-18 00:26,7138.75,7138.88,7138.88,7138.75,7122.771", "2026-04-18 00:27,7138.84,7138.97,7138.97,7138.37,7122.862", "2026-04-18 00:28,7139.05,7139.10,7139.16,7138.78,7122.952", "2026-04-18 00:29,7138.53,7138.71,7138.89,7138.53,7123.039", "2026-04-18 00:30,7138.42,7138.84,7138.84,7138.29,7123.126", "2026-04-18 00:31,7138.89,7140.98,7140.98,7138.89,7123.224", "2026-04-18 00:32,7141.72,7141.55,7141.72,7141.33,7123.324", "2026-04-18 00:33,7142.67,7142.82,7142.82,7142.19,7123.429", "2026-04-18 00:34,7142.96,7143.09,7143.09,7142.83,7123.535", "2026-04-18 00:35,7142.29,7142.54,7142.54,7142.19,7123.637", "2026-04-18 00:36,7142.79,7143.66,7143.66,7142.79,7123.744", "2026-04-18 00:37,7143.07,7144.12,7144.12,7143.07,7123.852", "2026-04-18 00:38,7144.93,7145.11,7145.11,7144.90,7123.964", "2026-04-18 00:39,7145.09,7144.77,7145.09,7143.98,7124.073", "2026-04-18 00:40,7144.93,7145.16,7145.16,7144.79,7124.183", "2026-04-18 00:41,7144.39,7144.10,7144.39,7144.10,7124.286", "2026-04-18 00:42,7144.35,7143.92,7144.35,7143.70,7124.387", "2026-04-18 00:43,7142.77,7143.62,7143.71,7142.77,7124.486", "2026-04-18 00:44,7143.85,7144.28,7144.28,7143.67,7124.587", "2026-04-18 00:45,7144.26,7145.23,7145.23,7144.26,7124.692", "2026-04-18 00:46,7145.74,7146.40,7146.40,7145.74,7124.802", "2026-04-18 00:47,7146.91,7147.07,7147.07,7146.91,7124.914", "2026-04-18 00:48,7147.40,7146.54,7147.40,7146.54,7125.022", "2026-04-18 00:49,7146.42,7146.97,7146.97,7146.27,7125.131", "2026-04-18 00:50,7146.88,7146.09,7146.88,7146.09,7125.235", "2026-04-18 00:51,7145.99,7146.40,7146.40,7145.78,7125.339", "2026-04-18 00:52,7146.19,7146.41,7146.41,7146.16,7125.442", "2026-04-18 00:53,7147.06,7146.12,7147.06,7146.12,7125.543", "2026-04-18 00:54,7145.70,7145.57,7145.70,7145.10,7125.640", "2026-04-18 00:55,7146.10,7144.78,7146.10,7144.78,7125.732", "2026-04-18 00:56,7145.06,7144.66,7145.06,7144.42,7125.823", "2026-04-18 00:57,7144.34,7144.20,7144.43,7144.20,7125.911", "2026-04-18 00:58,7143.59,7143.78,7143.78,7143.45,7125.996", "2026-04-18 00:59,7143.83,7144.43,7144.43,7143.83,7126.083", "2026-04-18 01:00,7143.76,7142.75,7143.76,7142.75,7126.161", "2026-04-18 01:01,7143.26,7143.59,7144.01,7143.26,7126.243", "2026-04-18 01:02,7143.03,7144.27,7144.27,7143.01,7126.327", "2026-04-18 01:03,7144.49,7143.99,7144.49,7143.68,7126.409", "2026-04-18 01:04,7144.39,7145.18,7145.38,7144.39,7126.496", "2026-04-18 01:05,7144.76,7145.43,7145.43,7144.76,7126.583", "2026-04-18 01:06,7145.09,7143.91,7145.09,7143.83,7126.662", "2026-04-18 01:07,7144.35,7144.73,7144.73,7144.35,7126.744", "2026-04-18 01:08,7143.95,7143.09,7144.01,7143.09,7126.818", "2026-04-18 01:09,7142.69,7140.34,7142.69,7140.34,7126.879", "2026-04-18 01:10,7133.14,7137.42,7137.42,7133.14,7126.926", "2026-04-18 01:11,7137.66,7136.86,7137.66,7136.86,7126.970", "2026-04-18 01:12,7135.92,7134.17,7135.92,7134.17,7127.002", "2026-04-18 01:13,7134.58,7134.18,7134.58,7133.94,7127.034", "2026-04-18 01:14,7134.89,7136.00,7136.00,7134.58,7127.073", "2026-04-18 01:15,7135.68,7136.44,7136.44,7135.43,7127.114", "2026-04-18 01:16,7136.27,7136.51,7137.40,7136.27,7127.155", "2026-04-18 01:17,7135.26,7135.65,7136.42,7135.26,7127.192", "2026-04-18 01:18,7136.33,7135.11,7136.42,7135.11,7127.226", "2026-04-18 01:19,7133.41,7133.60,7133.64,7133.41,7127.253", "2026-04-18 01:20,7134.78,7133.19,7134.78,7133.19,7127.278", "2026-04-18 01:21,7133.02,7131.17,7133.02,7131.17,7127.294", "2026-04-18 01:22,7128.61,7126.16,7128.61,7126.16,7127.289", "2026-04-18 01:23,7126.96,7128.08,7128.08,7126.96,7127.292", "2026-04-18 01:24,7129.92,7130.71,7130.71,7129.92,7127.306", "2026-04-18 01:25,7133.54,7120.68,7133.54,7120.68,7127.277", "2026-04-18 01:26,7119.88,7121.98,7122.12,7119.88,7127.254", "2026-04-18 01:27,7121.67,7120.95,7121.67,7116.80,7127.227", "2026-04-18 01:28,7120.87,7121.54,7121.54,7120.87,7127.203", "2026-04-18 01:29,7124.01,7122.68,7124.01,7122.68,7127.184", "2026-04-18 01:30,7120.84,7122.90,7122.90,7120.84,7127.166", "2026-04-18 01:31,7122.77,7124.74,7125.04,7122.77,7127.155", "2026-04-18 01:32,7125.25,7124.98,7125.36,7124.98,7127.146", "2026-04-18 01:33,7123.31,7122.54,7123.31,7121.65,7127.127", "2026-04-18 01:34,7123.19,7121.49,7123.19,7121.49,7127.103", "2026-04-18 01:35,7121.46,7123.09,7123.42,7121.46,7127.086", "2026-04-18 01:36,7122.90,7120.93,7122.90,7120.93,7127.061", "2026-04-18 01:37,7120.49,7120.46,7120.66,7120.46,7127.034", "2026-04-18 01:38,7120.30,7124.44,7125.30,7120.30,7127.023", "2026-04-18 01:39,7124.85,7125.47,7126.87,7124.85,7127.016", "2026-04-18 01:40,7126.01,7124.03,7126.01,7124.03,7127.004", "2026-04-18 01:41,7124.05,7124.76,7124.77,7124.05,7126.995", "2026-04-18 01:42,7123.55,7122.67,7124.34,7122.67,7126.977", "2026-04-18 01:43,7123.04,7124.26,7124.26,7123.04,7126.966", "2026-04-18 01:44,7124.19,7123.02,7124.19,7123.02,7126.950", "2026-04-18 01:45,7122.36,7122.28,7122.36,7122.26,7126.931", "2026-04-18 01:46,7123.08,7125.51,7125.80,7123.08,7126.925", "2026-04-18 01:47,7125.84,7126.78,7126.78,7125.84,7126.924", "2026-04-18 01:48,7128.99,7130.07,7130.11,7128.99,7126.936", "2026-04-18 01:49,7130.46,7130.00,7130.46,7129.43,7126.947", "2026-04-18 01:50,7129.15,7128.46,7129.46,7128.46,7126.952", "2026-04-18 01:51,7128.37,7128.91,7129.38,7128.37,7126.959", "2026-04-18 01:52,7129.34,7129.31,7129.34,7128.62,7126.967", "2026-04-18 01:53,7129.28,7129.19,7129.65,7129.19,7126.975", "2026-04-18 01:54,7129.17,7129.26,7129.26,7129.04,7126.983", "2026-04-18 01:55,7130.00,7130.12,7130.12,7129.99,7126.994", "2026-04-18 01:56,7129.39,7129.31,7129.83,7129.31,7127.002", "2026-04-18 01:57,7129.25,7129.24,7129.25,7128.49,7127.010", "2026-04-18 01:58,7130.13,7129.39,7130.30,7129.39,7127.018", "2026-04-18 01:59,7129.30,7128.35,7129.30,7128.35,7127.022", "2026-04-18 02:00,7127.33,7126.91,7127.33,7126.91,7127.021", "2026-04-18 02:01,7127.51,7127.55,7127.55,7127.33,7127.022", "2026-04-18 02:02,7126.09,7127.69,7127.69,7126.09,7127.024", "2026-04-18 02:03,7128.14,7127.00,7128.18,7127.00,7127.023", "2026-04-18 02:04,7125.97,7124.21,7127.11,7124.21,7127.012", "2026-04-18 02:05,7124.13,7124.88,7124.89,7123.67,7127.004", "2026-04-18 02:06,7124.07,7123.02,7124.20,7123.02,7126.989", "2026-04-18 02:07,7123.34,7123.17,7123.34,7121.67,7126.975", "2026-04-18 02:08,7123.79,7121.91,7123.79,7121.91,7126.956", "2026-04-18 02:09,7122.11,7121.36,7122.11,7121.36,7126.936", "2026-04-18 02:10,7120.12,7119.57,7120.12,7119.57,7126.909", "2026-04-18 02:11,7119.49,7119.83,7121.60,7119.49,7126.883", "2026-04-18 02:12,7118.94,7120.32,7120.32,7118.94,7126.859", "2026-04-18 02:13,7120.41,7119.62,7120.41,7119.62,7126.833", "2026-04-18 02:14,7120.97,7120.37,7120.97,7120.37,7126.810", "2026-04-18 02:15,7118.59,7117.57,7118.59,7117.57,7126.777", "2026-04-18 02:16,7117.96,7120.09,7120.09,7117.96,7126.753", "2026-04-18 02:17,7120.48,7119.95,7120.48,7119.93,7126.729", "2026-04-18 02:18,7119.70,7120.18,7120.25,7119.70,7126.706", "2026-04-18 02:19,7121.10,7121.74,7121.74,7121.07,7126.688", "2026-04-18 02:20,7121.31,7120.06,7121.51,7120.06,7126.665", "2026-04-18 02:21,7120.12,7118.63,7120.12,7118.63,7126.637", "2026-04-18 02:22,7117.71,7116.78,7118.03,7116.78,7126.603", "2026-04-18 02:23,7116.59,7115.90,7116.59,7115.90,7126.566", "2026-04-18 02:24,7117.27,7118.12,7118.12,7116.69,7126.537", "2026-04-18 02:25,7119.95,7121.86,7122.35,7119.95,7126.521", "2026-04-18 02:26,7121.75,7124.76,7125.82,7121.75,7126.515", "2026-04-18 02:27,7125.43,7125.91,7125.91,7125.43,7126.512", "2026-04-18 02:28,7125.41,7125.19,7125.42,7125.16,7126.507", "2026-04-18 02:29,7124.93,7122.60,7124.93,7122.60,7126.493", "2026-04-18 02:30,7123.06,7121.47,7123.06,7121.14,7126.476", "2026-04-18 02:31,7121.99,7124.14,7124.14,7121.99,7126.468", "2026-04-18 02:32,7124.94,7124.25,7124.94,7124.09,7126.460", "2026-04-18 02:33,7125.02,7125.87,7125.87,7125.02,7126.458", "2026-04-18 02:34,7125.50,7126.49,7126.49,7125.50,7126.458", "2026-04-18 02:35,7126.90,7127.13,7127.13,7126.90,7126.460", "2026-04-18 02:36,7126.88,7126.13,7126.88,7126.13,7126.458", "2026-04-18 02:37,7126.70,7127.18,7127.46,7126.70,7126.460", "2026-04-18 02:38,7127.16,7127.04,7127.16,7126.78,7126.461", "2026-04-18 02:39,7126.30,7126.07,7126.55,7126.07,7126.459", "2026-04-18 02:40,7126.64,7125.19,7126.64,7125.19,7126.454", "2026-04-18 02:41,7125.22,7125.70,7125.70,7125.06,7126.451", "2026-04-18 02:42,7125.14,7124.28,7125.14,7124.22,7126.444", "2026-04-18 02:43,7124.00,7121.80,7124.00,7121.80,7126.429", "2026-04-18 02:44,7122.48,7123.17,7123.17,7121.83,7126.418", "2026-04-18 02:45,7123.32,7123.37,7123.37,7123.32,7126.408", "2026-04-18 02:46,7124.82,7124.48,7125.36,7124.48,7126.401", "2026-04-18 02:47,7124.63,7124.35,7124.63,7124.04,7126.394", "2026-04-18 02:48,7124.56,7124.12,7125.59,7124.12,7126.386", "2026-04-18 02:49,7123.68,7123.94,7124.16,7123.68,7126.378", "2026-04-18 02:50,7123.79,7123.09,7124.08,7123.09,7126.367", "2026-04-18 02:51,7123.12,7121.91,7123.12,7121.91,7126.353", "2026-04-18 02:52,7121.45,7121.63,7122.13,7121.45,7126.338", "2026-04-18 02:53,7120.51,7118.37,7120.51,7118.37,7126.313", "2026-04-18 02:54,7119.67,7118.86,7119.67,7118.42,7126.290", "2026-04-18 02:55,7119.53,7118.89,7119.53,7118.84,7126.267", "2026-04-18 02:56,7118.97,7120.33,7120.33,7118.97,7126.248", "2026-04-18 02:57,7121.37,7121.50,7122.65,7121.37,7126.233", "2026-04-18 02:58,7121.40,7121.85,7121.85,7121.40,7126.219", "2026-04-18 02:59,7121.64,7121.36,7121.67,7121.36,7126.204", "2026-04-18 03:00,7120.91,7121.77,7121.77,7120.84,7126.190", "2026-04-18 03:01,7120.58,7120.54,7120.84,7120.54,7126.172", "2026-04-18 03:02,7120.81,7122.13,7122.13,7120.81,7126.159", "2026-04-18 03:03,7122.19,7122.20,7122.20,7121.30,7126.147", "2026-04-18 03:04,7121.66,7120.96,7121.66,7120.70,7126.131", "2026-04-18 03:05,7120.64,7119.93,7120.64,7119.93,7126.112", "2026-04-18 03:06,7120.38,7119.86,7120.38,7119.67,7126.093", "2026-04-18 03:07,7118.89,7117.63,7118.89,7117.58,7126.067", "2026-04-18 03:08,7118.89,7119.39,7120.37,7118.89,7126.047", "2026-04-18 03:09,7119.12,7118.75,7119.12,7118.27,7126.025", "2026-04-18 03:10,7119.23,7117.42,7119.23,7117.42,7125.999", "2026-04-18 03:11,7118.40,7117.27,7118.40,7117.27,7125.973", "2026-04-18 03:12,7116.50,7116.42,7116.59,7116.42,7125.945", "2026-04-18 03:13,7116.20,7115.95,7116.20,7115.59,7125.915", "2026-04-18 03:14,7115.90,7115.45,7115.90,7115.21,7125.884", "2026-04-18 03:15,7114.38,7115.62,7115.63,7114.38,7125.854", "2026-04-18 03:16,7115.40,7117.80,7117.92,7115.40,7125.830", "2026-04-18 03:17,7118.23,7119.27,7119.36,7118.23,7125.811", "2026-04-18 03:18,7119.38,7118.27,7119.38,7118.27,7125.789", "2026-04-18 03:19,7117.89,7118.40,7118.47,7117.89,7125.767", "2026-04-18 03:20,7118.72,7117.30,7118.77,7117.30,7125.742", "2026-04-18 03:21,7118.24,7117.17,7118.79,7117.17,7125.717", "2026-04-18 03:22,7117.59,7118.06,7118.06,7117.14,7125.695", "2026-04-18 03:23,7118.28,7117.62,7118.33,7117.62,7125.672", "2026-04-18 03:24,7117.18,7116.81,7117.24,7116.81,7125.647", "2026-04-18 03:25,7116.79,7116.91,7116.91,7116.00,7125.622", "2026-04-18 03:26,7117.47,7118.34,7118.85,7117.47,7125.601", "2026-04-18 03:27,7118.03,7118.40,7118.40,7117.87,7125.580", "2026-04-18 03:28,7118.20,7117.24,7118.20,7117.24,7125.556", "2026-04-18 03:29,7117.65,7117.03,7117.84,7117.03,7125.532", "2026-04-18 03:30,7116.48,7116.77,7116.77,7116.28,7125.507", "2026-04-18 03:31,7116.51,7117.98,7118.11,7116.51,7125.486", "2026-04-18 03:32,7118.32,7119.61,7119.73,7118.32,7125.469", "2026-04-18 03:33,7118.62,7120.36,7120.65,7118.62,7125.454", "2026-04-18 03:34,7120.99,7121.79,7121.79,7120.99,7125.443", "2026-04-18 03:35,7122.49,7122.72,7122.72,7121.92,7125.435", "2026-04-18 03:36,7121.79,7121.66,7121.90,7121.66,7125.424", "2026-04-18 03:37,7121.08,7120.82,7121.08,7120.25,7125.411", "2026-04-18 03:38,7120.78,7121.30,7121.30,7120.78,7125.399", "2026-04-18 03:39,7121.28,7124.15,7124.15,7121.28,7125.395", "2026-04-18 03:40,7123.95,7124.98,7124.98,7123.41,7125.393", "2026-04-18 03:41,7123.98,7124.73,7124.90,7122.95,7125.391", "2026-04-18 03:42,7125.14,7123.65,7125.14,7123.65,7125.386", "2026-04-18 03:43,7124.26,7126.39,7126.39,7124.26,7125.388", "2026-04-18 03:44,7126.72,7126.80,7126.99,7126.70,7125.391", "2026-04-18 03:45,7127.02,7126.01,7127.02,7126.01,7125.392", "2026-04-18 03:46,7126.69,7124.83,7126.69,7124.83,7125.390", "2026-04-18 03:47,7123.73,7123.81,7123.95,7123.73,7125.385", "2026-04-18 03:48,7124.13,7122.02,7124.13,7122.02,7125.376", "2026-04-18 03:49,7122.76,7122.59,7122.76,7122.59,7125.368", "2026-04-18 03:50,7121.98,7122.02,7122.05,7121.38,7125.359", "2026-04-18 03:51,7122.34,7122.09,7125.24,7122.09,7125.350", "2026-04-18 03:52,7122.90,7122.75,7122.90,7121.27,7125.343", "2026-04-18 03:53,7123.54,7123.40,7123.54,7123.37,7125.337", "2026-04-18 03:54,7121.83,7124.20,7124.20,7121.83,7125.334", "2026-04-18 03:55,7123.87,7125.86,7125.86,7123.87,7125.335", "2026-04-18 03:56,7125.77,7124.68,7125.77,7124.68,7125.333", "2026-04-18 03:57,7124.66,7124.79,7126.69,7124.66,7125.331", "2026-04-18 03:58,7124.00,7123.48,7124.00,7122.93,7125.326", "2026-04-18 03:59,7125.49,7125.75,7125.75,7125.40,7125.327", "2026-04-18 04:00,7126.20,7126.06,7126.98,7124.12,7125.328"]
+    }
+});</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=100.DJIA&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp152</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取美股标普500指数行情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取港股恒生指数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>miniquotechart_jp246({
+    "rc": 0,
+    "rt": 10,
+    "svr": 183124088,
+    "lt": 1,
+    "full": 1,
+    "dlmkts": "",
+    "data": {
+        "code": "HSI",
+        "market": 100,
+        "type": 0,
+        "status": 0,
+        "name": "恒生指数",
+        "decimal": 2,
+        "preSettlement": 26394.26,
+        "preClose": 26394.26,
+        "beticks": "32400|34200|57600|34200|43200|46800|57600",
+        "trendsTotal": 331,
+        "time": 1776413320,
+        "kind": 2,
+        "prePrice": 26394.26,
+        "tradePeriods": {
+            "pre": null,
+            "after": null,
+            "periods": [{
+                "b": 202604170930,
+                "e": 202604171200
+            }, {
+                "b": 202604171300,
+                "e": 202604171600
+            }]
+        },
+        "hisPrePrices": [{
+            "date": 20260417,
+            "prePrice": 26394.26
+        }],
+        "trends": ["2026-04-17 09:30,26210.97,26210.97,26210.97,26210.97,0.000", "2026-04-17 09:31,26240.01,26269.79,26280.96,26228.63,26269.790", "2026-04-17 09:32,26264.97,26252.13,26266.39,26251.18,26263.903", "2026-04-17 09:33,26249.62,26266.36,26266.36,26239.21,26264.517", "2026-04-17 09:34,26263.28,26237.49,26274.77,26237.10,26259.111", "2026-04-17 09:35,26234.02,26233.08,26238.64,26229.07,26254.772", "2026-04-17 09:36,26233.58,26246.72,26248.55,26227.67,26253.621", "2026-04-17 09:37,26244.56,26259.11,26259.35,26244.56,26254.307", "2026-04-17 09:38,26257.88,26239.95,26260.93,26234.81,26252.711", "2026-04-17 09:39,26240.34,26229.76,26241.11,26229.00,26250.415", "2026-04-17 09:40,26229.16,26196.54,26229.79,26196.54,26245.517", "2026-04-17 09:41,26198.45,26215.04,26218.32,26198.45,26242.977", "2026-04-17 09:42,26216.63,26197.46,26216.63,26196.37,26239.475", "2026-04-17 09:43,26195.86,26199.68,26205.96,26192.74,26236.632", "2026-04-17 09:44,26201.36,26186.46,26202.38,26186.46,26233.287", "2026-04-17 09:45,26184.73,26200.20,26203.43,26180.81,26231.219", "2026-04-17 09:46,26197.39,26186.21,26201.49,26183.88,26228.571", "2026-04-17 09:47,26183.90,26177.23,26187.55,26168.33,26225.718", "2026-04-17 09:48,26177.84,26204.28,26208.57,26177.84,26224.589", "2026-04-17 09:49,26201.87,26199.00,26203.24,26190.70,26223.309", "2026-04-17 09:50,26198.49,26206.62,26208.15,26196.69,26222.514", "2026-04-17 09:51,26208.35,26177.52,26208.94,26177.52,26220.468", "2026-04-17 09:52,26177.45,26167.41,26187.70,26167.41,26218.161", "2026-04-17 09:53,26166.69,26179.25,26181.70,26166.69,26216.539", "2026-04-17 09:54,26180.35,26184.38,26191.02,26174.42,26215.252", "2026-04-17 09:55,26185.86,26184.56,26190.80,26179.64,26214.071", "2026-04-17 09:56,26184.46,26191.15,26196.56,26184.46,26213.222", "2026-04-17 09:57,26189.93,26169.02,26189.93,26165.30,26211.643", "2026-04-17 09:58,26166.72,26169.53,26172.35,26162.91,26210.190", "2026-04-17 09:59,26167.73,26152.13,26171.94,26152.13,26208.254", "2026-04-17 10:00,26146.30,26166.99,26168.72,26146.30,26206.922", "2026-04-17 10:01,26165.01,26156.85,26169.92,26154.81,26205.357", "2026-04-17 10:02,26155.74,26165.45,26167.86,26155.74,26204.147", "2026-04-17 10:03,26165.46,26158.86,26166.68,26154.31,26202.815", "2026-04-17 10:04,26157.98,26162.94,26166.75,26156.56,26201.675", "2026-04-17 10:05,26165.78,26155.35,26168.44,26151.65,26200.388", "2026-04-17 10:06,26154.65,26162.43,26167.23,26154.65,26199.362", "2026-04-17 10:07,26158.24,26161.47,26161.85,26153.64,26198.364", "2026-04-17 10:08,26160.25,26155.89,26165.02,26154.50,26197.274", "2026-04-17 10:09,26156.76,26154.96,26158.51,26152.50,26196.216", "2026-04-17 10:10,26150.34,26140.82,26155.27,26140.82,26194.864", "2026-04-17 10:11,26138.41,26136.38,26143.87,26132.39,26193.471", "2026-04-17 10:12,26136.85,26129.53,26136.85,26125.72,26191.984", "2026-04-17 10:13,26126.13,26141.65,26144.41,26126.13,26190.840", "2026-04-17 10:14,26145.10,26142.84,26148.67,26140.93,26189.773", "2026-04-17 10:15,26145.27,26130.64,26145.27,26129.63,26188.487", "2026-04-17 10:16,26130.81,26140.15,26140.29,26130.81,26187.458", "2026-04-17 10:17,26138.32,26143.40,26147.16,26138.32,26186.540", "2026-04-17 10:18,26142.81,26139.68,26145.17,26133.05,26185.583", "2026-04-17 10:19,26139.59,26144.89,26147.59,26137.99,26184.769", "2026-04-17 10:20,26144.81,26136.41,26144.81,26136.41,26183.820", "2026-04-17 10:21,26135.64,26150.52,26153.33,26129.90,26183.179", "2026-04-17 10:22,26154.22,26164.79,26166.55,26151.18,26182.832", "2026-04-17 10:23,26164.21,26166.79,26172.08,26161.55,26182.534", "2026-04-17 10:24,26167.61,26161.58,26169.66,26159.05,26182.153", "2026-04-17 10:25,26160.43,26152.58,26164.64,26152.58,26181.624", "2026-04-17 10:26,26153.25,26159.96,26161.13,26149.49,26181.243", "2026-04-17 10:27,26160.27,26155.62,26164.01,26154.19,26180.801", "2026-04-17 10:28,26156.63,26152.47,26160.75,26150.87,26180.320", "2026-04-17 10:29,26150.35,26143.30,26150.91,26140.91,26179.703", "2026-04-17 10:30,26148.94,26148.71,26153.36,26143.02,26179.194", "2026-04-17 10:31,26146.28,26142.28,26149.80,26138.84,26178.598", "2026-04-17 10:32,26141.56,26148.72,26150.39,26136.81,26178.123", "2026-04-17 10:33,26148.75,26157.96,26158.56,26148.75,26177.807", "2026-04-17 10:34,26159.34,26151.76,26163.29,26151.76,26177.406", "2026-04-17 10:35,26153.14,26152.96,26158.17,26148.28,26177.035", "2026-04-17 10:36,26153.05,26123.09,26153.05,26121.71,26176.229", "2026-04-17 10:37,26122.51,26130.06,26133.42,26122.11,26175.550", "2026-04-17 10:38,26128.89,26138.31,26141.38,26128.28,26175.010", "2026-04-17 10:39,26139.32,26133.91,26143.41,26133.91,26174.422", "2026-04-17 10:40,26134.42,26134.23,26138.59,26132.46,26173.855", "2026-04-17 10:41,26131.68,26129.27,26137.25,26128.33,26173.235", "2026-04-17 10:42,26131.37,26129.67,26137.31,26128.97,26172.638", "2026-04-17 10:43,26130.08,26130.17,26135.56,26129.33,26172.064", "2026-04-17 10:44,26129.25,26133.48,26137.89,26129.25,26171.549", "2026-04-17 10:45,26133.81,26129.20,26137.01,26126.23,26170.991", "2026-04-17 10:46,26129.34,26143.50,26143.50,26122.60,26170.633", "2026-04-17 10:47,26145.09,26141.78,26146.09,26139.98,26170.263", "2026-04-17 10:48,26141.73,26141.04,26144.28,26136.20,26169.893", "2026-04-17 10:49,26141.82,26120.80,26141.82,26119.80,26169.279", "2026-04-17 10:50,26122.36,26118.87,26123.89,26117.30,26168.656", "2026-04-17 10:51,26123.12,26102.03,26123.12,26099.58,26167.843", "2026-04-17 10:52,26102.28,26100.34,26107.69,26099.65,26167.029", "2026-04-17 10:53,26098.87,26097.59,26101.99,26088.47,26166.202", "2026-04-17 10:54,26097.64,26096.34,26103.55,26094.18,26165.380", "2026-04-17 10:55,26097.78,26094.37,26101.79,26092.92,26164.554", "2026-04-17 10:56,26093.24,26085.73,26094.80,26083.26,26163.647", "2026-04-17 10:57,26084.29,26078.80,26085.12,26078.51,26162.682", "2026-04-17 10:58,26078.37,26081.17,26082.21,26075.36,26161.766", "2026-04-17 10:59,26081.84,26078.25,26083.89,26077.19,26160.838", "2026-04-17 11:00,26078.41,26063.11,26081.57,26063.11,26159.764", "2026-04-17 11:01,26062.52,26066.05,26071.64,26062.33,26158.745", "2026-04-17 11:02,26066.43,26059.55,26067.52,26057.67,26157.678", "2026-04-17 11:03,26062.98,26056.97,26062.98,26054.43,26156.606", "2026-04-17 11:04,26056.70,26059.91,26064.24,26055.25,26155.588", "2026-04-17 11:05,26058.84,26053.04,26061.73,26052.18,26154.519", "2026-04-17 11:06,26053.74,26053.71,26060.48,26050.39,26153.479", "2026-04-17 11:07,26048.04,26048.33,26052.99,26043.21,26152.406", "2026-04-17 11:08,26048.58,26042.77,26048.58,26040.20,26151.298", "2026-04-17 11:09,26041.37,26048.06,26052.85,26041.08,26150.265", "2026-04-17 11:10,26050.64,26041.64,26050.64,26041.64,26149.189", "2026-04-17 11:11,26039.24,26044.66,26044.66,26035.71,26148.164", "2026-04-17 11:12,26046.08,26041.04,26047.36,26038.84,26147.123", "2026-04-17 11:13,26036.21,26045.50,26045.50,26036.21,26146.145", "2026-04-17 11:14,26041.25,26034.07,26047.20,26034.07,26145.077", "2026-04-17 11:15,26037.74,26043.48,26044.55,26036.16,26144.118", "2026-04-17 11:16,26040.37,26044.02,26049.08,26038.23,26143.182", "2026-04-17 11:17,26040.47,26045.23,26046.42,26034.30,26142.275", "2026-04-17 11:18,26046.21,26050.10,26054.71,26045.63,26141.429", "2026-04-17 11:19,26046.85,26048.10,26052.34,26042.77,26140.580", "2026-04-17 11:20,26045.20,26046.27,26054.01,26045.20,26139.730", "2026-04-17 11:21,26047.73,26042.06,26050.26,26038.28,26138.857", "2026-04-17 11:22,26043.69,26043.65,26049.82,26042.09,26138.014", "2026-04-17 11:23,26042.41,26042.84,26045.16,26036.65,26137.179", "2026-04-17 11:24,26044.45,26037.77,26044.45,26036.26,26136.314", "2026-04-17 11:25,26040.73,26041.07,26045.16,26038.12,26135.492", "2026-04-17 11:26,26037.19,26040.39,26043.80,26036.05,26134.679", "2026-04-17 11:27,26041.72,26035.03,26042.01,26033.67,26133.834", "2026-04-17 11:28,26034.26,26035.88,26036.86,26029.60,26133.010", "2026-04-17 11:29,26031.17,26035.60,26041.81,26029.48,26132.198", "2026-04-17 11:30,26035.18,26046.01,26046.24,26034.96,26131.485", "2026-04-17 11:31,26044.16,26043.29,26049.43,26040.79,26130.762", "2026-04-17 11:32,26043.44,26044.60,26047.64,26038.29,26130.061", "2026-04-17 11:33,26043.96,26041.12,26045.67,26040.53,26129.343", "2026-04-17 11:34,26042.97,26045.61,26045.61,26037.04,26128.673", "2026-04-17 11:35,26044.73,26036.88,26046.65,26034.83,26127.944", "2026-04-17 11:36,26038.87,26034.29,26040.57,26031.74,26127.206", "2026-04-17 11:37,26031.76,26029.44,26033.18,26023.56,26126.442", "2026-04-17 11:38,26027.73,26028.75,26031.36,26024.12,26125.684", "2026-04-17 11:39,26032.58,26032.38,26032.58,26025.14,26124.966", "2026-04-17 11:40,26031.97,26025.83,26034.38,26025.16,26124.209", "2026-04-17 11:41,26026.38,26022.47,26026.52,26017.32,26123.438", "2026-04-17 11:42,26021.91,26022.04,26023.73,26015.44,26122.675", "2026-04-17 11:43,26020.97,26022.75,26024.44,26019.08,26121.929", "2026-04-17 11:44,26025.04,26024.35,26025.93,26020.32,26121.206", "2026-04-17 11:45,26023.23,26020.47,26026.03,26020.47,26120.465", "2026-04-17 11:46,26019.62,26030.42,26030.42,26019.61,26119.807", "2026-04-17 11:47,26029.63,26035.81,26037.40,26029.63,26119.198", "2026-04-17 11:48,26035.99,26030.09,26038.40,26029.03,26118.556", "2026-04-17 11:49,26033.46,26029.80,26033.51,26027.85,26117.922", "2026-04-17 11:50,26033.36,26030.05,26034.17,26027.02,26117.298", "2026-04-17 11:51,26030.68,26029.64,26033.81,26028.50,26116.680", "2026-04-17 11:52,26030.54,26027.80,26033.73,26027.14,26116.058", "2026-04-17 11:53,26027.84,26031.02,26032.23,26025.46,26115.467", "2026-04-17 11:54,26027.21,26031.27,26033.41,26026.96,26114.886", "2026-04-17 11:55,26029.32,26034.10,26036.10,26028.05,26114.332", "2026-04-17 11:56,26035.33,26034.77,26040.65,26034.30,26113.790", "2026-04-17 11:57,26038.61,26043.71,26044.80,26037.51,26113.316", "2026-04-17 11:58,26042.08,26045.62,26046.50,26038.38,26112.861", "2026-04-17 11:59,26045.40,26040.56,26046.13,26038.40,26112.378", "2026-04-17 12:00,26043.15,26046.70,26048.78,26039.66,26111.943", "2026-04-17 13:01,26048.04,26061.35,26065.26,26048.04,26111.610", "2026-04-17 13:02,26061.20,26061.45,26069.74,26057.91,26111.282", "2026-04-17 13:03,26062.91,26057.96,26064.13,26055.40,26110.935", "2026-04-17 13:04,26055.26,26050.06,26055.26,26048.00,26110.542", "2026-04-17 13:05,26051.01,26051.51,26053.31,26048.54,26110.163", "2026-04-17 13:06,26049.67,26060.11,26060.11,26047.63,26109.844", "2026-04-17 13:07,26057.39,26054.93,26060.41,26051.68,26109.496", "2026-04-17 13:08,26055.56,26048.42,26056.89,26047.83,26109.111", "2026-04-17 13:09,26049.40,26058.59,26058.59,26047.48,26108.795", "2026-04-17 13:10,26057.22,26055.26,26057.22,26051.30,26108.462", "2026-04-17 13:11,26055.32,26058.14,26060.42,26053.68,26108.151", "2026-04-17 13:12,26056.99,26052.97,26057.95,26050.20,26107.812", "2026-04-17 13:13,26053.32,26052.45,26056.99,26048.18,26107.474", "2026-04-17 13:14,26053.52,26056.70,26059.08,26053.52,26107.166", "2026-04-17 13:15,26056.83,26058.49,26061.26,26053.21,26106.872", "2026-04-17 13:16,26055.24,26058.02,26059.11,26052.66,26106.579", "2026-04-17 13:17,26059.11,26060.94,26062.62,26056.96,26106.307", "2026-04-17 13:18,26062.05,26061.35,26062.49,26054.81,26106.040", "2026-04-17 13:19,26057.96,26045.10,26059.56,26042.64,26105.681", "2026-04-17 13:20,26045.93,26048.04,26048.59,26043.11,26105.343", "2026-04-17 13:21,26048.59,26049.25,26050.68,26045.27,26105.016", "2026-04-17 13:22,26048.13,26044.71,26050.11,26044.71,26104.667", "2026-04-17 13:23,26044.50,26050.56,26054.69,26043.07,26104.356", "2026-04-17 13:24,26052.53,26049.95,26056.28,26049.53,26104.045", "2026-04-17 13:25,26049.94,26060.46,26064.30,26049.10,26103.797", "2026-04-17 13:26,26059.06,26058.64,26061.47,26056.90,26103.541", "2026-04-17 13:27,26057.40,26058.72,26061.00,26052.65,26103.289", "2026-04-17 13:28,26057.73,26056.16,26060.53,26053.07,26103.025", "2026-04-17 13:29,26055.95,26056.43,26061.28,26054.54,26102.766", "2026-04-17 13:30,26056.08,26060.12,26060.34,26056.08,26102.530", "2026-04-17 13:31,26059.12,26061.91,26063.11,26058.64,26102.306", "2026-04-17 13:32,26059.39,26043.31,26061.02,26041.62,26101.983", "2026-04-17 13:33,26043.71,26044.72,26048.73,26040.37,26101.671", "2026-04-17 13:34,26044.47,26039.53,26044.47,26035.87,26101.335", "2026-04-17 13:35,26039.45,26042.65,26042.65,26037.31,26101.019", "2026-04-17 13:36,26042.71,26044.05,26045.53,26037.33,26100.714", "2026-04-17 13:37,26045.61,26048.74,26049.85,26042.72,26100.437", "2026-04-17 13:38,26048.52,26063.67,26063.67,26046.82,26100.242", "2026-04-17 13:39,26061.31,26066.71,26069.82,26061.31,26100.065", "2026-04-17 13:40,26062.23,26058.42,26064.83,26057.96,26099.846", "2026-04-17 13:41,26059.15,26059.06,26061.29,26054.41,26099.633", "2026-04-17 13:42,26058.90,26063.00,26066.25,26058.90,26099.443", "2026-04-17 13:43,26063.33,26062.03,26066.23,26059.96,26099.250", "2026-04-17 13:44,26059.45,26059.64,26064.99,26058.33,26099.046", "2026-04-17 13:45,26061.76,26065.03,26067.88,26058.76,26098.872", "2026-04-17 13:46,26064.24,26068.81,26071.95,26060.84,26098.719", "2026-04-17 13:47,26067.76,26074.10,26079.05,26066.37,26098.594", "2026-04-17 13:48,26072.91,26076.16,26078.94,26071.13,26098.481", "2026-04-17 13:49,26076.06,26083.35,26084.19,26076.06,26098.405", "2026-04-17 13:50,26083.68,26082.37,26088.81,26082.37,26098.325", "2026-04-17 13:51,26083.43,26087.73,26087.73,26080.64,26098.272", "2026-04-17 13:52,26087.21,26087.36,26091.48,26086.35,26098.218", "2026-04-17 13:53,26089.28,26095.67,26099.55,26086.78,26098.205", "2026-04-17 13:54,26102.52,26101.26,26103.45,26095.32,26098.219", "2026-04-17 13:55,26103.40,26111.67,26113.32,26101.63,26098.284", "2026-04-17 13:56,26112.78,26130.37,26130.37,26112.78,26098.439", "2026-04-17 13:57,26131.63,26125.94,26134.13,26124.56,26098.571", "2026-04-17 13:58,26125.88,26116.47,26125.88,26114.94,26098.656", "2026-04-17 13:59,26116.55,26107.49,26116.55,26106.70,26098.698", "2026-04-17 14:00,26110.04,26104.93,26110.04,26101.18,26098.727", "2026-04-17 14:01,26105.09,26107.16,26110.88,26102.34,26098.766", "2026-04-17 14:02,26107.71,26105.98,26110.14,26103.66,26098.799", "2026-04-17 14:03,26108.98,26108.83,26112.61,26106.77,26098.845", "2026-04-17 14:04,26106.83,26112.77,26116.09,26106.83,26098.909", "2026-04-17 14:05,26116.16,26110.77,26116.16,26109.66,26098.963", "2026-04-17 14:06,26109.79,26119.32,26119.74,26109.79,26099.056", "2026-04-17 14:07,26117.22,26118.35,26125.58,26115.85,26099.144", "2026-04-17 14:08,26120.31,26123.11,26123.98,26118.73,26099.253", "2026-04-17 14:09,26124.72,26111.74,26124.72,26108.03,26099.309", "2026-04-17 14:10,26109.96,26091.82,26109.96,26089.84,26099.275", "2026-04-17 14:11,26091.13,26092.06,26095.55,26088.70,26099.242", "2026-04-17 14:12,26095.29,26085.75,26095.70,26085.50,26099.181", "2026-04-17 14:13,26085.17,26087.63,26093.24,26085.17,26099.129", "2026-04-17 14:14,26086.72,26087.48,26096.07,26086.57,26099.077", "2026-04-17 14:15,26090.50,26089.65,26092.48,26085.70,26099.035", "2026-04-17 14:16,26088.68,26090.67,26095.21,26086.20,26098.998", "2026-04-17 14:17,26088.27,26090.62,26094.71,26087.87,26098.961", "2026-04-17 14:18,26089.39,26091.62,26097.07,26089.39,26098.928", "2026-04-17 14:19,26092.18,26090.38,26092.18,26084.69,26098.890", "2026-04-17 14:20,26090.10,26085.06,26090.10,26083.07,26098.830", "2026-04-17 14:21,26083.30,26081.95,26085.30,26081.28,26098.757", "2026-04-17 14:22,26080.24,26069.50,26082.64,26066.94,26098.631", "2026-04-17 14:23,26069.12,26068.96,26073.66,26066.56,26098.504", "2026-04-17 14:24,26069.10,26070.29,26076.62,26068.12,26098.383", "2026-04-17 14:25,26072.41,26079.22,26082.71,26071.79,26098.301", "2026-04-17 14:26,26082.07,26078.55,26082.91,26076.65,26098.217", "2026-04-17 14:27,26080.93,26076.19,26081.37,26071.56,26098.124", "2026-04-17 14:28,26076.82,26075.50,26077.62,26072.06,26098.029", "2026-04-17 14:29,26078.07,26074.43,26083.17,26073.13,26097.930", "2026-04-17 14:30,26073.01,26067.14,26074.61,26065.88,26097.802", "2026-04-17 14:31,26065.92,26062.04,26070.17,26058.93,26097.654", "2026-04-17 14:32,26064.67,26068.41,26068.41,26059.73,26097.533", "2026-04-17 14:33,26065.87,26066.33,26069.57,26062.29,26097.405", "2026-04-17 14:34,26064.42,26071.08,26073.24,26064.42,26097.297", "2026-04-17 14:35,26070.71,26071.92,26077.54,26070.71,26097.193", "2026-04-17 14:36,26074.60,26076.43,26077.29,26070.63,26097.108", "2026-04-17 14:37,26077.43,26076.60,26080.48,26073.10,26097.025", "2026-04-17 14:38,26075.09,26079.06,26081.93,26072.63,26096.952", "2026-04-17 14:39,26079.42,26080.62,26084.56,26074.98,26096.886", "2026-04-17 14:40,26076.07,26077.14,26082.67,26072.99,26096.807", "2026-04-17 14:41,26077.02,26080.84,26085.97,26077.02,26096.743", "2026-04-17 14:42,26082.40,26080.82,26085.54,26079.58,26096.680", "2026-04-17 14:43,26077.79,26081.57,26084.88,26076.49,26096.620", "2026-04-17 14:44,26080.68,26081.44,26083.99,26076.08,26096.560", "2026-04-17 14:45,26080.05,26084.22,26084.39,26076.90,26096.511", "2026-04-17 14:46,26085.06,26089.20,26096.04,26080.91,26096.482", "2026-04-17 14:47,26088.70,26091.88,26096.55,26088.70,26096.464", "2026-04-17 14:48,26091.85,26090.51,26095.06,26089.91,26096.441", "2026-04-17 14:49,26092.51,26091.08,26093.13,26085.07,26096.420", "2026-04-17 14:50,26093.29,26092.76,26097.01,26089.06,26096.405", "2026-04-17 14:51,26092.69,26097.15,26098.96,26091.80,26096.407", "2026-04-17 14:52,26098.59,26094.21,26104.40,26093.88,26096.398", "2026-04-17 14:53,26096.69,26097.49,26100.39,26093.75,26096.402", "2026-04-17 14:54,26099.13,26089.79,26100.51,26087.37,26096.377", "2026-04-17 14:55,26089.04,26084.60,26089.26,26082.84,26096.332", "2026-04-17 14:56,26083.76,26080.07,26087.22,26075.89,26096.271", "2026-04-17 14:57,26078.26,26078.61,26080.00,26073.91,26096.205", "2026-04-17 14:58,26079.15,26083.27,26088.70,26078.94,26096.156", "2026-04-17 14:59,26084.63,26086.17,26090.00,26083.01,26096.119", "2026-04-17 15:00,26087.23,26087.29,26088.70,26081.01,26096.086", "2026-04-17 15:01,26086.53,26101.23,26103.53,26086.53,26096.104", "2026-04-17 15:02,26103.78,26100.65,26103.78,26093.78,26096.120", "2026-04-17 15:03,26100.48,26092.72,26100.48,26090.58,26096.107", "2026-04-17 15:04,26093.22,26081.81,26093.55,26080.64,26096.055", "2026-04-17 15:05,26082.91,26086.72,26086.72,26077.74,26096.021", "2026-04-17 15:06,26088.14,26090.25,26090.90,26081.18,26096.000", "2026-04-17 15:07,26086.76,26087.30,26090.42,26082.31,26095.968", "2026-04-17 15:08,26085.29,26092.80,26094.39,26081.88,26095.956", "2026-04-17 15:09,26092.95,26093.75,26096.15,26086.24,26095.948", "2026-04-17 15:10,26092.32,26091.81,26099.93,26089.28,26095.933", "2026-04-17 15:11,26093.29,26096.67,26096.67,26090.05,26095.935", "2026-04-17 15:12,26096.50,26097.41,26097.41,26090.28,26095.940", "2026-04-17 15:13,26098.50,26102.08,26105.88,26094.41,26095.961", "2026-04-17 15:14,26100.09,26112.17,26115.33,26100.09,26096.017", "2026-04-17 15:15,26116.33,26118.66,26120.14,26111.40,26096.096", "2026-04-17 15:16,26118.36,26118.30,26121.57,26115.83,26096.173", "2026-04-17 15:17,26119.88,26122.01,26122.01,26112.41,26096.262", "2026-04-17 15:18,26118.61,26111.87,26121.10,26108.54,26096.316", "2026-04-17 15:19,26109.98,26104.16,26112.64,26103.49,26096.343", "2026-04-17 15:20,26107.80,26108.04,26110.64,26102.69,26096.383", "2026-04-17 15:21,26110.25,26105.96,26111.87,26100.30,26096.415", "2026-04-17 15:22,26103.56,26103.06,26105.43,26097.91,26096.437", "2026-04-17 15:23,26104.69,26109.55,26111.11,26100.56,26096.481", "2026-04-17 15:24,26110.41,26121.44,26121.85,26108.37,26096.565", "2026-04-17 15:25,26122.70,26119.84,26123.91,26117.52,26096.643", "2026-04-17 15:26,26119.54,26121.43,26123.59,26116.28,26096.726", "2026-04-17 15:27,26120.43,26129.63,26131.26,26120.43,26096.836", "2026-04-17 15:28,26129.04,26124.95,26129.82,26122.53,26096.930", "2026-04-17 15:29,26126.70,26121.32,26129.89,26117.64,26097.011", "2026-04-17 15:30,26120.39,26115.63,26123.08,26112.08,26097.072", "2026-04-17 15:31,26118.11,26117.82,26118.11,26111.27,26097.140", "2026-04-17 15:32,26113.76,26109.04,26117.96,26108.24,26097.179", "2026-04-17 15:33,26108.43,26108.86,26115.03,26108.25,26097.217", "2026-04-17 15:34,26108.91,26111.15,26112.68,26107.16,26097.262", "2026-04-17 15:35,26110.34,26116.19,26118.12,26110.34,26097.323", "2026-04-17 15:36,26116.12,26116.22,26120.46,26113.55,26097.384", "2026-04-17 15:37,26117.11,26116.89,26119.63,26112.81,26097.447", "2026-04-17 15:38,26117.10,26112.85,26118.12,26109.21,26097.496", "2026-04-17 15:39,26114.86,26115.86,26116.99,26110.62,26097.555", "2026-04-17 15:40,26115.85,26114.18,26115.85,26108.61,26097.608", "2026-04-17 15:41,26111.44,26107.43,26113.09,26105.34,26097.639", "2026-04-17 15:42,26106.99,26104.86,26106.99,26100.18,26097.662", "2026-04-17 15:43,26108.44,26105.25,26108.44,26100.84,26097.686", "2026-04-17 15:44,26104.62,26100.64,26106.09,26097.55,26097.695", "2026-04-17 15:45,26103.86,26109.05,26111.73,26099.67,26097.730", "2026-04-17 15:46,26106.18,26108.45,26111.64,26102.72,26097.763", "2026-04-17 15:47,26105.17,26104.14,26108.65,26100.66,26097.783", "2026-04-17 15:48,26104.75,26102.20,26110.74,26100.70,26097.796", "2026-04-17 15:49,26104.87,26109.50,26111.87,26100.51,26097.832", "2026-04-17 15:50,26108.17,26111.09,26111.94,26105.26,26097.873", "2026-04-17 15:51,26111.59,26110.79,26115.46,26105.63,26097.913", "2026-04-17 15:52,26117.01,26118.57,26122.49,26116.48,26097.976", "2026-04-17 15:53,26117.71,26122.23,26124.04,26116.19,26098.050", "2026-04-17 15:54,26120.24,26126.11,26129.23,26117.53,26098.136", "2026-04-17 15:55,26130.54,26132.88,26133.63,26121.61,26098.242", "2026-04-17 15:56,26131.51,26132.41,26135.08,26128.21,26098.346", "2026-04-17 15:57,26131.26,26137.06,26140.47,26127.94,26098.464", "2026-04-17 15:58,26136.10,26131.48,26137.44,26129.35,26098.564", "2026-04-17 15:59,26134.33,26133.89,26136.64,26127.37,26098.671", "2026-04-17 16:00,26130.22,26160.33,26160.33,26130.22,26098.857"]
+    }
+});</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=100.HSI&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp246</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取港股国企指数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>miniquotechart_jp248({
+    "rc": 0,
+    "rt": 10,
+    "svr": 183124161,
+    "lt": 1,
+    "full": 1,
+    "dlmkts": "",
+    "data": {
+        "code": "HSCEI",
+        "market": 100,
+        "type": 0,
+        "status": 0,
+        "name": "国企指数",
+        "decimal": 2,
+        "preSettlement": 8905.11,
+        "preClose": 8905.11,
+        "beticks": "32400|34200|57600|34200|43200|46800|57600",
+        "trendsTotal": 331,
+        "time": 1776413320,
+        "kind": 2,
+        "prePrice": 8905.11,
+        "tradePeriods": {
+            "pre": null,
+            "after": null,
+            "periods": [{
+                "b": 202604170930,
+                "e": 202604171200
+            }, {
+                "b": 202604171300,
+                "e": 202604171600
+            }]
+        },
+        "hisPrePrices": [{
+            "date": 20260417,
+            "prePrice": 8905.11
+        }],
+        "trends": ["2026-04-17 09:30,8840.57,8840.57,8840.57,8840.57,0.000", "2026-04-17 09:31,8848.84,8864.14,8868.29,8848.84,8864.140", "2026-04-17 09:32,8863.73,8866.28,8870.86,8858.84,8864.853", "2026-04-17 09:33,8865.97,8870.85,8870.85,8860.87,8866.352", "2026-04-17 09:34,8869.40,8861.56,8874.29,8861.56,8865.393", "2026-04-17 09:35,8861.44,8860.67,8863.42,8859.42,8864.605", "2026-04-17 09:36,8860.76,8864.47,8865.57,8857.83,8864.585", "2026-04-17 09:37,8863.75,8867.76,8868.33,8863.75,8864.981", "2026-04-17 09:38,8867.60,8862.28,8869.37,8860.96,8864.680", "2026-04-17 09:39,8861.98,8860.35,8863.14,8858.18,8864.247", "2026-04-17 09:40,8860.08,8847.63,8860.08,8847.63,8862.736", "2026-04-17 09:41,8848.07,8850.49,8855.12,8848.07,8861.715", "2026-04-17 09:42,8850.35,8843.75,8851.09,8843.06,8860.333", "2026-04-17 09:43,8842.82,8844.36,8846.96,8842.32,8859.192", "2026-04-17 09:44,8844.85,8839.51,8844.85,8839.51,8857.879", "2026-04-17 09:45,8839.74,8843.18,8843.75,8838.13,8856.960", "2026-04-17 09:46,8841.95,8838.94,8845.97,8838.20,8855.900", "2026-04-17 09:47,8839.14,8836.84,8840.04,8832.75,8854.841", "2026-04-17 09:48,8837.41,8846.85,8849.05,8837.41,8854.420", "2026-04-17 09:49,8845.66,8845.30,8845.90,8840.54,8853.964", "2026-04-17 09:50,8844.94,8847.09,8848.16,8843.64,8853.636", "2026-04-17 09:51,8848.07,8839.48,8848.92,8839.48,8852.992", "2026-04-17 09:52,8839.88,8835.01,8843.10,8835.01,8852.210", "2026-04-17 09:53,8834.71,8838.78,8839.70,8834.71,8851.650", "2026-04-17 09:54,8839.53,8839.14,8842.58,8836.67,8851.149", "2026-04-17 09:55,8839.93,8837.17,8839.94,8835.67,8850.611", "2026-04-17 09:56,8837.09,8840.44,8842.95,8837.09,8850.234", "2026-04-17 09:57,8840.27,8833.18,8840.27,8832.27,8849.624", "2026-04-17 09:58,8832.47,8833.16,8834.38,8830.49,8849.056", "2026-04-17 09:59,8832.49,8825.78,8834.00,8825.78,8848.280", "2026-04-17 10:00,8823.37,8830.93,8831.69,8823.37,8847.720", "2026-04-17 10:01,8830.53,8829.71,8832.99,8828.88,8847.157", "2026-04-17 10:02,8829.40,8831.87,8833.33,8829.22,8846.693", "2026-04-17 10:03,8831.70,8829.48,8832.72,8827.44,8846.186", "2026-04-17 10:04,8829.54,8831.12,8833.00,8828.83,8845.755", "2026-04-17 10:05,8832.55,8827.53,8832.84,8826.47,8845.248", "2026-04-17 10:06,8827.27,8831.33,8831.82,8827.27,8844.871", "2026-04-17 10:07,8829.69,8832.10,8832.10,8827.97,8844.534", "2026-04-17 10:08,8831.11,8830.53,8833.18,8829.09,8844.174", "2026-04-17 10:09,8830.86,8829.75,8831.60,8828.69,8843.813", "2026-04-17 10:10,8828.06,8824.82,8829.58,8824.77,8843.349", "2026-04-17 10:11,8823.67,8823.71,8826.53,8820.99,8842.881", "2026-04-17 10:12,8825.04,8821.56,8825.04,8820.25,8842.385", "2026-04-17 10:13,8819.94,8825.25,8826.07,8819.94,8841.995", "2026-04-17 10:14,8826.49,8826.25,8827.67,8825.16,8841.645", "2026-04-17 10:15,8826.86,8820.96,8826.86,8820.66,8841.195", "2026-04-17 10:16,8821.15,8823.33,8824.01,8820.86,8840.814", "2026-04-17 10:17,8822.68,8824.10,8825.98,8822.53,8840.465", "2026-04-17 10:18,8824.59,8823.12,8825.16,8820.53,8840.111", "2026-04-17 10:19,8823.12,8825.23,8826.88,8822.30,8839.813", "2026-04-17 10:20,8825.47,8821.88,8825.47,8821.88,8839.461", "2026-04-17 10:21,8820.80,8826.60,8827.76,8818.96,8839.213", "2026-04-17 10:22,8828.10,8831.32,8831.87,8827.02,8839.064", "2026-04-17 10:23,8831.11,8832.87,8834.88,8830.52,8838.949", "2026-04-17 10:24,8833.01,8830.77,8833.49,8829.39,8838.800", "2026-04-17 10:25,8830.46,8825.34,8831.73,8825.34,8838.559", "2026-04-17 10:26,8825.71,8828.22,8829.20,8825.22,8838.377", "2026-04-17 10:27,8828.04,8826.14,8829.64,8825.64,8838.166", "2026-04-17 10:28,8826.49,8824.59,8828.33,8824.01,8837.935", "2026-04-17 10:29,8823.74,8822.04,8824.27,8821.12,8837.670", "2026-04-17 10:30,8824.18,8825.16,8827.12,8822.06,8837.464", "2026-04-17 10:31,8824.26,8822.57,8825.88,8822.01,8837.223", "2026-04-17 10:32,8822.27,8825.60,8826.42,8820.73,8837.038", "2026-04-17 10:33,8826.13,8829.09,8829.59,8826.00,8836.913", "2026-04-17 10:34,8829.51,8827.96,8831.62,8827.69,8836.775", "2026-04-17 10:35,8828.42,8828.81,8830.87,8827.16,8836.654", "2026-04-17 10:36,8828.51,8816.64,8828.51,8816.39,8836.355", "2026-04-17 10:37,8816.62,8818.19,8819.33,8816.33,8836.087", "2026-04-17 10:38,8817.62,8820.34,8821.28,8817.10,8835.858", "2026-04-17 10:39,8820.95,8818.60,8821.94,8818.60,8835.611", "2026-04-17 10:40,8818.77,8819.71,8821.13,8818.50,8835.387", "2026-04-17 10:41,8818.77,8819.14,8821.87,8818.54,8835.161", "2026-04-17 10:42,8820.05,8820.17,8822.16,8818.86,8834.955", "2026-04-17 10:43,8820.34,8819.12,8821.85,8819.12,8834.741", "2026-04-17 10:44,8819.00,8820.18,8821.71,8818.39,8834.546", "2026-04-17 10:45,8820.50,8819.49,8821.48,8818.27,8834.347", "2026-04-17 10:46,8820.44,8825.46,8825.46,8817.40,8834.231", "2026-04-17 10:47,8826.25,8825.34,8826.90,8824.35,8834.117", "2026-04-17 10:48,8825.46,8825.70,8826.50,8823.82,8834.010", "2026-04-17 10:49,8825.69,8818.72,8825.69,8817.62,8833.818", "2026-04-17 10:50,8818.88,8818.35,8819.71,8816.91,8833.627", "2026-04-17 10:51,8819.74,8810.45,8819.74,8809.00,8833.344", "2026-04-17 10:52,8809.99,8810.41,8811.90,8809.66,8833.067", "2026-04-17 10:53,8809.98,8810.46,8811.28,8806.92,8832.797", "2026-04-17 10:54,8810.35,8810.29,8812.72,8809.42,8832.532", "2026-04-17 10:55,8810.70,8808.40,8811.71,8807.64,8832.251", "2026-04-17 10:56,8808.10,8807.05,8809.13,8806.04,8831.961", "2026-04-17 10:57,8806.49,8804.04,8806.65,8803.51,8831.643", "2026-04-17 10:58,8803.64,8805.08,8805.98,8802.68,8831.344", "2026-04-17 10:59,8805.04,8804.40,8806.31,8803.61,8831.044", "2026-04-17 11:00,8803.92,8799.35,8805.06,8799.35,8830.695", "2026-04-17 11:01,8799.42,8801.12,8803.44,8799.42,8830.373", "2026-04-17 11:02,8800.63,8798.95,8801.81,8798.03,8830.035", "2026-04-17 11:03,8800.71,8797.95,8800.71,8797.73,8829.693", "2026-04-17 11:04,8798.09,8799.33,8800.37,8797.25,8829.373", "2026-04-17 11:05,8798.86,8796.36,8799.43,8795.42,8829.029", "2026-04-17 11:06,8796.50,8796.55,8798.84,8794.46,8828.694", "2026-04-17 11:07,8794.21,8794.24,8796.49,8792.81,8828.342", "2026-04-17 11:08,8794.66,8792.53,8794.66,8792.01,8827.980", "2026-04-17 11:09,8792.08,8794.89,8796.76,8791.75,8827.649", "2026-04-17 11:10,8796.12,8792.19,8796.12,8792.19,8827.297", "2026-04-17 11:11,8791.18,8791.97,8792.11,8788.50,8826.950", "2026-04-17 11:12,8792.95,8791.64,8794.02,8790.58,8826.607", "2026-04-17 11:13,8789.48,8794.02,8794.02,8789.48,8826.293", "2026-04-17 11:14,8792.30,8788.74,8794.23,8788.74,8825.935", "2026-04-17 11:15,8790.38,8792.91,8793.24,8789.89,8825.623", "2026-04-17 11:16,8791.97,8792.91,8795.11,8790.66,8825.317", "2026-04-17 11:17,8791.59,8793.66,8794.18,8789.29,8825.023", "2026-04-17 11:18,8793.88,8794.01,8796.71,8792.69,8824.738", "2026-04-17 11:19,8792.38,8793.94,8795.46,8791.70,8824.458", "2026-04-17 11:20,8792.66,8792.60,8796.02,8792.60,8824.170", "2026-04-17 11:21,8793.11,8790.74,8794.41,8789.84,8823.871", "2026-04-17 11:22,8791.40,8792.42,8794.32,8791.40,8823.592", "2026-04-17 11:23,8791.83,8790.89,8792.90,8789.38,8823.305", "2026-04-17 11:24,8791.63,8788.54,8791.63,8787.96,8823.002", "2026-04-17 11:25,8789.60,8790.42,8791.90,8788.36,8822.721", "2026-04-17 11:26,8788.91,8789.15,8791.15,8788.12,8822.434", "2026-04-17 11:27,8789.53,8787.79,8789.73,8787.12,8822.140", "2026-04-17 11:28,8787.53,8787.35,8788.07,8785.09,8821.847", "2026-04-17 11:29,8785.25,8787.91,8789.72,8784.92,8821.564", "2026-04-17 11:30,8787.91,8791.32,8791.88,8787.91,8821.314", "2026-04-17 11:31,8790.47,8790.03,8792.52,8788.99,8821.057", "2026-04-17 11:32,8790.19,8791.23,8792.18,8788.29,8820.814", "2026-04-17 11:33,8790.85,8789.82,8792.11,8789.79,8820.564", "2026-04-17 11:34,8790.64,8791.16,8791.27,8788.25,8820.328", "2026-04-17 11:35,8790.91,8788.28,8791.72,8787.69,8820.073", "2026-04-17 11:36,8789.01,8787.67,8789.76,8786.22,8819.817", "2026-04-17 11:37,8786.68,8784.96,8787.90,8783.27,8819.544", "2026-04-17 11:38,8784.31,8784.99,8786.36,8783.34,8819.276", "2026-04-17 11:39,8786.59,8786.45,8786.59,8783.44,8819.023", "2026-04-17 11:40,8785.99,8784.04,8786.68,8784.04,8818.755", "2026-04-17 11:41,8784.39,8783.67,8784.55,8781.97,8818.489", "2026-04-17 11:42,8783.78,8783.31,8784.20,8780.28,8818.224", "2026-04-17 11:43,8783.05,8782.85,8784.93,8782.24,8817.960", "2026-04-17 11:44,8783.46,8783.01,8783.65,8781.93,8817.701", "2026-04-17 11:45,8782.75,8782.07,8784.12,8781.86,8817.439", "2026-04-17 11:46,8781.87,8785.97,8785.97,8781.79,8817.209", "2026-04-17 11:47,8785.50,8788.48,8788.88,8785.47,8817.000", "2026-04-17 11:48,8788.36,8786.18,8788.95,8785.40,8816.778", "2026-04-17 11:49,8786.23,8785.66,8786.91,8784.99,8816.555", "2026-04-17 11:50,8786.90,8785.92,8787.43,8784.38,8816.337", "2026-04-17 11:51,8785.48,8785.43,8786.79,8785.12,8816.119", "2026-04-17 11:52,8785.81,8784.55,8786.51,8784.11,8815.898", "2026-04-17 11:53,8784.16,8785.43,8785.63,8783.07,8815.686", "2026-04-17 11:54,8783.90,8786.11,8786.89,8783.90,8815.482", "2026-04-17 11:55,8785.13,8786.80,8788.05,8784.28,8815.285", "2026-04-17 11:56,8787.73,8787.91,8790.15,8787.16,8815.098", "2026-04-17 11:57,8788.72,8791.06,8791.06,8787.79,8814.935", "2026-04-17 11:58,8790.47,8791.00,8791.37,8788.29,8814.774", "2026-04-17 11:59,8791.14,8788.68,8791.14,8787.91,8814.600", "2026-04-17 12:00,8789.66,8790.68,8791.01,8788.13,8814.441", "2026-04-17 13:01,8790.71,8794.21,8797.52,8790.71,8814.307", "2026-04-17 13:02,8793.87,8794.50,8797.41,8793.49,8814.177", "2026-04-17 13:03,8795.31,8794.59,8796.03,8793.70,8814.049", "2026-04-17 13:04,8793.65,8791.72,8793.65,8790.68,8813.904", "2026-04-17 13:05,8791.89,8792.20,8792.68,8790.30,8813.764", "2026-04-17 13:06,8791.56,8795.79,8795.79,8790.40,8813.649", "2026-04-17 13:07,8794.71,8794.10,8795.98,8792.49,8813.525", "2026-04-17 13:08,8794.75,8791.77,8795.41,8791.02,8813.388", "2026-04-17 13:09,8792.19,8795.93,8795.93,8791.49,8813.278", "2026-04-17 13:10,8795.39,8795.09,8795.53,8792.79,8813.165", "2026-04-17 13:11,8795.04,8796.41,8796.58,8794.32,8813.061", "2026-04-17 13:12,8795.89,8793.84,8796.02,8793.02,8812.943", "2026-04-17 13:13,8794.14,8793.77,8795.90,8791.71,8812.826", "2026-04-17 13:14,8793.94,8795.87,8796.66,8793.94,8812.723", "2026-04-17 13:15,8795.91,8796.97,8798.08,8794.40,8812.628", "2026-04-17 13:16,8795.87,8796.75,8797.35,8794.64,8812.532", "2026-04-17 13:17,8797.20,8798.00,8798.51,8796.32,8812.445", "2026-04-17 13:18,8798.47,8797.40,8798.47,8794.43,8812.355", "2026-04-17 13:19,8795.94,8789.74,8796.42,8788.60,8812.221", "2026-04-17 13:20,8790.14,8791.30,8791.30,8789.44,8812.098", "2026-04-17 13:21,8791.60,8792.24,8792.64,8790.47,8811.982", "2026-04-17 13:22,8791.79,8790.21,8792.73,8790.10,8811.856", "2026-04-17 13:23,8790.10,8792.02,8793.60,8789.54,8811.742", "2026-04-17 13:24,8792.91,8791.71,8794.15,8791.61,8811.627", "2026-04-17 13:25,8791.90,8796.80,8798.37,8791.56,8811.542", "2026-04-17 13:26,8796.51,8795.79,8797.17,8795.56,8811.453", "2026-04-17 13:27,8795.63,8795.77,8796.94,8793.49,8811.364", "2026-04-17 13:28,8795.54,8795.41,8797.21,8793.68,8811.274", "2026-04-17 13:29,8795.33,8795.62,8797.90,8794.78,8811.187", "2026-04-17 13:30,8795.73,8796.91,8797.17,8795.18,8811.108", "2026-04-17 13:31,8796.53,8796.71,8797.56,8795.98,8811.028", "2026-04-17 13:32,8796.12,8789.91,8797.25,8789.31,8810.912", "2026-04-17 13:33,8790.51,8791.38,8792.09,8789.01,8810.805", "2026-04-17 13:34,8791.24,8789.34,8791.47,8788.23,8810.688", "2026-04-17 13:35,8789.28,8790.33,8790.78,8788.32,8810.578", "2026-04-17 13:36,8790.18,8791.58,8791.78,8788.72,8810.476", "2026-04-17 13:37,8792.06,8793.35,8793.64,8790.68,8810.384", "2026-04-17 13:38,8793.21,8799.34,8799.34,8792.58,8810.325", "2026-04-17 13:39,8798.83,8800.20,8802.08,8798.27,8810.271", "2026-04-17 13:40,8798.33,8797.44,8799.70,8797.35,8810.203", "2026-04-17 13:41,8797.99,8797.09,8798.30,8795.44,8810.134", "2026-04-17 13:42,8797.01,8798.25,8800.09,8797.01,8810.072", "2026-04-17 13:43,8798.23,8797.85,8799.67,8796.61,8810.009", "2026-04-17 13:44,8797.48,8797.12,8799.34,8796.60,8809.942", "2026-04-17 13:45,8798.18,8800.34,8800.62,8797.31,8809.893", "2026-04-17 13:46,8800.30,8801.54,8802.49,8798.18,8809.850", "2026-04-17 13:47,8801.22,8802.85,8804.46,8800.99,8809.814", "2026-04-17 13:48,8802.21,8803.43,8804.24,8801.16,8809.781", "2026-04-17 13:49,8803.44,8806.42,8806.42,8803.44,8809.764", "2026-04-17 13:50,8806.56,8805.99,8808.09,8805.45,8809.745", "2026-04-17 13:51,8806.75,8806.75,8807.25,8804.95,8809.730", "2026-04-17 13:52,8807.25,8807.28,8809.31,8806.77,8809.717", "2026-04-17 13:53,8807.70,8811.88,8813.24,8807.58,8809.727", "2026-04-17 13:54,8813.99,8813.84,8814.65,8810.81,8809.747", "2026-04-17 13:55,8814.71,8816.11,8816.80,8812.91,8809.777", "2026-04-17 13:56,8816.37,8822.82,8822.82,8816.37,8809.840", "2026-04-17 13:57,8823.38,8821.55,8824.41,8821.06,8809.896", "2026-04-17 13:58,8821.43,8817.25,8821.43,8816.60,8809.931", "2026-04-17 13:59,8818.11,8816.51,8818.11,8815.50,8809.962", "2026-04-17 14:00,8817.32,8815.34,8817.32,8814.02,8809.987", "2026-04-17 14:01,8815.04,8815.49,8817.63,8814.16,8810.012", "2026-04-17 14:02,8815.74,8814.97,8817.04,8814.41,8810.035", "2026-04-17 14:03,8816.24,8816.55,8818.03,8815.66,8810.065", "2026-04-17 14:04,8815.63,8818.59,8820.32,8815.63,8810.104", "2026-04-17 14:05,8819.83,8817.36,8819.84,8816.29,8810.137", "2026-04-17 14:06,8817.12,8819.97,8820.62,8816.93,8810.182", "2026-04-17 14:07,8818.96,8820.38,8822.80,8818.45,8810.228", "2026-04-17 14:08,8821.74,8822.82,8823.21,8820.68,8810.285", "2026-04-17 14:09,8823.52,8817.50,8823.52,8817.09,8810.317", "2026-04-17 14:10,8816.95,8810.22,8816.95,8809.53,8810.316", "2026-04-17 14:11,8810.14,8809.26,8811.64,8808.13,8810.311", "2026-04-17 14:12,8810.96,8807.58,8811.50,8807.52,8810.298", "2026-04-17 14:13,8807.28,8808.09,8810.73,8807.28,8810.288", "2026-04-17 14:14,8807.63,8808.77,8811.65,8807.36,8810.281", "2026-04-17 14:15,8809.87,8810.49,8811.54,8808.33,8810.281", "2026-04-17 14:16,8810.12,8811.32,8812.20,8808.48,8810.285", "2026-04-17 14:17,8810.06,8810.84,8812.48,8809.84,8810.287", "2026-04-17 14:18,8810.51,8811.85,8813.52,8810.51,8810.293", "2026-04-17 14:19,8811.56,8810.86,8811.82,8808.64,8810.295", "2026-04-17 14:20,8810.57,8809.94,8811.09,8808.57,8810.293", "2026-04-17 14:21,8809.38,8808.35,8809.90,8808.17,8810.284", "2026-04-17 14:22,8807.23,8803.50,8808.48,8802.13,8810.254", "2026-04-17 14:23,8803.28,8802.75,8805.19,8802.28,8810.221", "2026-04-17 14:24,8802.72,8802.76,8805.69,8802.72,8810.189", "2026-04-17 14:25,8803.44,8806.40,8808.30,8803.44,8810.172", "2026-04-17 14:26,8807.39,8807.45,8808.13,8805.54,8810.160", "2026-04-17 14:27,8808.32,8805.93,8808.46,8804.36,8810.142", "2026-04-17 14:28,8806.25,8806.39,8807.12,8804.42,8810.126", "2026-04-17 14:29,8807.45,8806.14,8809.08,8805.22,8810.109", "2026-04-17 14:30,8805.88,8804.00,8806.71,8802.87,8810.083", "2026-04-17 14:31,8803.08,8801.81,8805.14,8800.99,8810.048", "2026-04-17 14:32,8803.17,8804.26,8804.26,8801.37,8810.024", "2026-04-17 14:33,8803.52,8803.60,8805.10,8801.69,8809.997", "2026-04-17 14:34,8802.97,8805.32,8806.54,8802.87,8809.977", "2026-04-17 14:35,8805.40,8805.94,8807.99,8805.18,8809.960", "2026-04-17 14:36,8806.74,8807.44,8808.03,8805.71,8809.949", "2026-04-17 14:37,8807.86,8807.63,8808.60,8805.84,8809.939", "2026-04-17 14:38,8807.18,8808.09,8809.31,8805.70,8809.931", "2026-04-17 14:39,8808.26,8810.19,8810.65,8806.50,8809.932", "2026-04-17 14:40,8808.35,8808.71,8810.26,8807.06,8809.927", "2026-04-17 14:41,8808.55,8810.83,8812.23,8808.55,8809.930", "2026-04-17 14:42,8811.15,8810.74,8812.05,8809.69,8809.933", "2026-04-17 14:43,8809.92,8811.45,8812.20,8809.18,8809.938", "2026-04-17 14:44,8810.94,8811.42,8811.90,8809.21,8809.943", "2026-04-17 14:45,8810.71,8812.64,8812.65,8809.42,8809.953", "2026-04-17 14:46,8812.93,8811.93,8813.75,8811.53,8809.960", "2026-04-17 14:47,8811.66,8813.58,8814.59,8811.61,8809.974", "2026-04-17 14:48,8813.26,8813.75,8815.70,8813.26,8809.988", "2026-04-17 14:49,8814.15,8814.78,8815.20,8812.39,8810.006", "2026-04-17 14:50,8815.46,8815.18,8816.37,8813.74,8810.025", "2026-04-17 14:51,8814.87,8818.14,8818.60,8814.87,8810.055", "2026-04-17 14:52,8818.69,8817.14,8820.11,8816.37,8810.081", "2026-04-17 14:53,8818.04,8817.57,8819.44,8816.86,8810.109", "2026-04-17 14:54,8818.58,8815.47,8819.39,8814.88,8810.129", "2026-04-17 14:55,8815.64,8814.04,8815.65,8813.03,8810.143", "2026-04-17 14:56,8813.85,8812.53,8815.26,8810.92,8810.151", "2026-04-17 14:57,8811.86,8812.53,8813.01,8810.66,8810.159", "2026-04-17 14:58,8812.63,8814.94,8816.27,8812.63,8810.176", "2026-04-17 14:59,8815.34,8816.21,8817.60,8814.40,8810.198", "2026-04-17 15:00,8816.59,8816.33,8816.89,8813.45,8810.220", "2026-04-17 15:01,8816.21,8820.56,8820.96,8816.21,8810.258", "2026-04-17 15:02,8820.84,8819.81,8820.84,8817.23,8810.292", "2026-04-17 15:03,8819.75,8816.42,8820.54,8815.21,8810.314", "2026-04-17 15:04,8816.50,8812.62,8817.18,8811.93,8810.322", "2026-04-17 15:05,8812.78,8813.73,8813.73,8809.83,8810.334", "2026-04-17 15:06,8813.99,8814.78,8814.96,8811.31,8810.350", "2026-04-17 15:07,8813.42,8814.22,8814.79,8811.87,8810.363", "2026-04-17 15:08,8813.50,8816.88,8817.46,8812.14,8810.386", "2026-04-17 15:09,8817.36,8817.53,8818.12,8814.42,8810.411", "2026-04-17 15:10,8816.99,8817.38,8819.85,8816.27,8810.435", "2026-04-17 15:11,8817.77,8819.77,8819.77,8816.47,8810.468", "2026-04-17 15:12,8819.67,8820.96,8820.96,8816.87,8810.505", "2026-04-17 15:13,8821.72,8823.73,8825.15,8819.99,8810.551", "2026-04-17 15:14,8822.68,8828.05,8829.00,8822.68,8810.612", "2026-04-17 15:15,8828.69,8830.42,8830.73,8826.79,8810.681", "2026-04-17 15:16,8830.17,8830.09,8832.04,8828.63,8810.748", "2026-04-17 15:17,8830.71,8831.02,8831.09,8827.52,8810.818", "2026-04-17 15:18,8829.77,8827.71,8830.77,8826.11,8810.876", "2026-04-17 15:19,8827.00,8825.19,8827.69,8824.55,8810.925", "2026-04-17 15:20,8826.37,8825.93,8826.76,8824.47,8810.976", "2026-04-17 15:21,8826.89,8825.03,8827.20,8823.24,8811.024", "2026-04-17 15:22,8823.66,8824.96,8825.58,8822.66,8811.071", "2026-04-17 15:23,8825.68,8827.78,8828.09,8823.56,8811.127", "2026-04-17 15:24,8828.22,8832.57,8832.57,8826.71,8811.199", "2026-04-17 15:25,8832.44,8831.50,8832.97,8830.61,8811.267", "2026-04-17 15:26,8831.38,8831.90,8832.89,8830.18,8811.336", "2026-04-17 15:27,8831.36,8834.70,8834.70,8831.36,8811.414", "2026-04-17 15:28,8834.35,8832.57,8834.69,8831.64,8811.484", "2026-04-17 15:29,8833.63,8831.89,8834.57,8830.23,8811.552", "2026-04-17 15:30,8831.68,8829.82,8831.75,8828.26,8811.612", "2026-04-17 15:31,8830.62,8831.17,8831.17,8827.40,8811.676", "2026-04-17 15:32,8829.42,8827.46,8831.04,8826.56,8811.728", "2026-04-17 15:33,8827.24,8827.28,8829.84,8826.80,8811.779", "2026-04-17 15:34,8827.27,8829.38,8829.58,8826.63,8811.836", "2026-04-17 15:35,8829.32,8830.06,8831.31,8828.85,8811.895", "2026-04-17 15:36,8829.78,8829.70,8832.00,8828.73,8811.952", "2026-04-17 15:37,8829.91,8828.72,8830.69,8827.06,8812.006", "2026-04-17 15:38,8829.08,8828.01,8830.01,8826.18,8812.057", "2026-04-17 15:39,8828.32,8829.27,8829.37,8826.39,8812.112", "2026-04-17 15:40,8829.08,8828.38,8829.52,8826.38,8812.164", "2026-04-17 15:41,8827.66,8826.49,8827.91,8825.09,8812.209", "2026-04-17 15:42,8825.78,8825.49,8826.12,8823.63,8812.251", "2026-04-17 15:43,8826.69,8825.95,8826.92,8823.13,8812.294", "2026-04-17 15:44,8826.01,8824.15,8826.01,8823.42,8812.331", "2026-04-17 15:45,8825.85,8827.23,8828.38,8823.93,8812.378", "2026-04-17 15:46,8826.65,8826.82,8827.88,8825.04,8812.423", "2026-04-17 15:47,8826.46,8825.99,8827.93,8825.08,8812.465", "2026-04-17 15:48,8826.17,8825.64,8828.44,8824.53,8812.506", "2026-04-17 15:49,8826.26,8828.45,8828.91,8824.81,8812.555", "2026-04-17 15:50,8827.50,8827.90,8828.90,8824.89,8812.602", "2026-04-17 15:51,8827.30,8827.19,8828.64,8825.62,8812.647", "2026-04-17 15:52,8828.85,8831.13,8832.41,8828.85,8812.704", "2026-04-17 15:53,8830.60,8832.14,8833.04,8830.15,8812.763", "2026-04-17 15:54,8830.93,8833.24,8834.81,8829.93,8812.826", "2026-04-17 15:55,8835.67,8835.08,8835.67,8831.18,8812.894", "2026-04-17 15:56,8834.72,8836.03,8837.23,8834.13,8812.964", "2026-04-17 15:57,8835.15,8837.07,8838.60,8834.41,8813.037", "2026-04-17 15:58,8837.18,8835.85,8837.46,8834.01,8813.106", "2026-04-17 15:59,8836.82,8836.30,8837.10,8832.96,8813.176", "2026-04-17 16:00,8835.52,8845.02,8845.02,8835.52,8813.272"]
+    }
+});</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=100.HSCEI&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp248</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取港股红筹指数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=124.HSCCI&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>miniquotechart_jp250({
+    "rc": 0,
+    "rt": 10,
+    "svr": 183124161,
+    "lt": 1,
+    "full": 1,
+    "dlmkts": "",
+    "data": {
+        "code": "HSCCI",
+        "market": 124,
+        "type": 4,
+        "status": 0,
+        "name": "红筹指数",
+        "decimal": 2,
+        "preSettlement": 4347.41,
+        "preClose": 4347.41,
+        "beticks": "34200|34200|57600|34200|43200|46800|57600",
+        "trendsTotal": 331,
+        "time": 1776413320,
+        "kind": 2,
+        "prePrice": 4347.41,
+        "tradePeriods": {
+            "pre": null,
+            "after": null,
+            "periods": [{
+                "b": 202604170930,
+                "e": 202604171200
+            }, {
+                "b": 202604171300,
+                "e": 202604171600
+            }]
+        },
+        "hisPrePrices": [{
+            "date": 20260417,
+            "prePrice": 4347.41
+        }],
+        "trends": ["2026-04-17 09:30,4344.36,4344.36,4344.36,4344.36,0.000", "2026-04-17 09:31,4343.66,4340.88,4348.60,4340.78,4340.880", "2026-04-17 09:32,4341.25,4338.05,4341.25,4336.89,4339.936", "2026-04-17 09:33,4337.10,4334.73,4337.10,4332.00,4338.634", "2026-04-17 09:34,4333.59,4327.40,4334.50,4327.40,4336.387", "2026-04-17 09:35,4327.40,4326.78,4328.21,4326.06,4334.785", "2026-04-17 09:36,4326.31,4330.05,4330.36,4326.31,4334.108", "2026-04-17 09:37,4330.04,4332.82,4333.26,4330.04,4333.947", "2026-04-17 09:38,4332.54,4329.30,4332.74,4329.30,4333.430", "2026-04-17 09:39,4329.85,4329.70,4331.85,4329.26,4333.057", "2026-04-17 09:40,4329.79,4328.22,4330.65,4328.22,4332.617", "2026-04-17 09:41,4328.77,4331.40,4332.12,4328.77,4332.515", "2026-04-17 09:42,4330.41,4326.06,4330.52,4326.06,4332.018", "2026-04-17 09:43,4325.74,4322.78,4325.93,4322.35,4331.358", "2026-04-17 09:44,4322.52,4323.82,4323.82,4321.39,4330.855", "2026-04-17 09:45,4323.76,4324.16,4325.31,4323.41,4330.436", "2026-04-17 09:46,4324.22,4328.33,4329.18,4324.22,4330.312", "2026-04-17 09:47,4328.64,4325.45,4328.90,4325.00,4330.041", "2026-04-17 09:48,4325.73,4330.32,4330.59,4325.73,4330.055", "2026-04-17 09:49,4329.86,4327.74,4329.86,4327.26,4329.939", "2026-04-17 09:50,4327.74,4327.13,4328.10,4326.30,4329.805", "2026-04-17 09:51,4327.41,4322.23,4327.41,4322.23,4329.460", "2026-04-17 09:52,4323.22,4321.17,4324.37,4321.17,4329.099", "2026-04-17 09:53,4321.17,4321.98,4322.46,4321.17,4328.802", "2026-04-17 09:54,4321.69,4320.42,4321.82,4320.01,4328.466", "2026-04-17 09:55,4319.74,4319.36,4320.22,4318.81,4328.115", "2026-04-17 09:56,4319.04,4318.19,4319.61,4317.65,4327.747", "2026-04-17 09:57,4317.69,4315.74,4317.69,4315.16,4327.318", "2026-04-17 09:58,4315.42,4314.04,4315.63,4314.04,4326.860", "2026-04-17 09:59,4314.61,4311.74,4315.14,4311.70,4326.356", "2026-04-17 10:00,4312.35,4314.07,4314.42,4311.32,4325.959", "2026-04-17 10:01,4314.11,4313.25,4315.17,4313.07,4325.561", "2026-04-17 10:02,4312.71,4315.02,4315.55,4312.71,4325.241", "2026-04-17 10:03,4315.23,4315.77,4316.31,4314.70,4324.962", "2026-04-17 10:04,4315.56,4316.73,4317.07,4315.48,4324.726", "2026-04-17 10:05,4316.75,4315.89,4316.75,4315.25,4324.480", "2026-04-17 10:06,4316.49,4319.38,4319.38,4316.25,4324.342", "2026-04-17 10:07,4319.38,4319.13,4319.38,4317.40,4324.204", "2026-04-17 10:08,4319.20,4318.94,4320.10,4318.06,4324.069", "2026-04-17 10:09,4319.07,4317.01,4319.37,4316.67,4323.892", "2026-04-17 10:10,4317.04,4315.79,4318.32,4315.79,4323.694", "2026-04-17 10:11,4315.38,4314.60,4315.57,4313.37,4323.477", "2026-04-17 10:12,4314.52,4315.26,4316.59,4314.43,4323.285", "2026-04-17 10:13,4315.26,4316.76,4316.76,4315.08,4323.136", "2026-04-17 10:14,4316.89,4320.09,4320.65,4316.89,4323.068", "2026-04-17 10:15,4320.36,4318.46,4321.19,4318.32,4322.967", "2026-04-17 10:16,4318.36,4317.93,4318.72,4317.57,4322.859", "2026-04-17 10:17,4317.44,4318.19,4319.15,4317.44,4322.761", "2026-04-17 10:18,4318.13,4315.65,4318.13,4315.36,4322.615", "2026-04-17 10:19,4316.24,4317.37,4318.79,4316.10,4322.510", "2026-04-17 10:20,4317.81,4318.32,4318.44,4317.39,4322.427", "2026-04-17 10:21,4317.67,4318.58,4319.67,4316.85,4322.353", "2026-04-17 10:22,4318.65,4319.84,4320.38,4317.85,4322.305", "2026-04-17 10:23,4319.76,4320.51,4320.82,4318.93,4322.271", "2026-04-17 10:24,4320.13,4320.67,4321.41,4319.82,4322.241", "2026-04-17 10:25,4321.01,4320.99,4321.30,4319.67,4322.218", "2026-04-17 10:26,4320.93,4319.42,4321.12,4319.10,4322.168", "2026-04-17 10:27,4319.42,4318.79,4320.61,4318.79,4322.109", "2026-04-17 10:28,4318.79,4322.39,4322.60,4318.79,4322.113", "2026-04-17 10:29,4322.65,4321.65,4322.65,4320.69,4322.105", "2026-04-17 10:30,4321.43,4322.18,4322.94,4321.43,4322.106", "2026-04-17 10:31,4322.18,4324.44,4324.44,4321.95,4322.143", "2026-04-17 10:32,4324.43,4324.60,4325.49,4324.01,4322.182", "2026-04-17 10:33,4325.82,4327.56,4327.63,4324.68,4322.266", "2026-04-17 10:34,4327.37,4328.40,4329.44,4327.35,4322.360", "2026-04-17 10:35,4327.89,4329.04,4330.81,4327.89,4322.461", "2026-04-17 10:36,4329.72,4329.96,4330.76,4328.52,4322.572", "2026-04-17 10:37,4329.94,4329.85,4330.24,4328.82,4322.679", "2026-04-17 10:38,4330.00,4329.67,4330.26,4328.28,4322.780", "2026-04-17 10:39,4329.18,4329.27,4330.54,4329.07,4322.872", "2026-04-17 10:40,4328.99,4328.89,4329.80,4328.62,4322.956", "2026-04-17 10:41,4329.00,4328.93,4330.10,4328.29,4323.038", "2026-04-17 10:42,4328.93,4329.85,4330.42,4328.37,4323.131", "2026-04-17 10:43,4329.88,4326.30,4329.88,4326.24,4323.173", "2026-04-17 10:44,4326.77,4325.96,4327.31,4325.27,4323.210", "2026-04-17 10:45,4326.20,4326.84,4328.17,4325.48,4323.257", "2026-04-17 10:46,4327.36,4328.44,4328.75,4327.10,4323.324", "2026-04-17 10:47,4328.31,4328.38,4329.13,4327.58,4323.388", "2026-04-17 10:48,4328.07,4325.52,4328.07,4325.52,4323.414", "2026-04-17 10:49,4325.84,4325.00,4326.31,4324.10,4323.433", "2026-04-17 10:50,4324.27,4322.98,4324.27,4321.97,4323.427", "2026-04-17 10:51,4322.69,4319.97,4323.87,4319.84,4323.384", "2026-04-17 10:52,4319.70,4319.61,4320.98,4319.61,4323.338", "2026-04-17 10:53,4319.88,4318.76,4320.41,4318.69,4323.283", "2026-04-17 10:54,4318.76,4319.73,4321.12,4318.48,4323.241", "2026-04-17 10:55,4319.98,4320.33,4321.10,4319.79,4323.207", "2026-04-17 10:56,4320.61,4320.68,4321.29,4319.77,4323.177", "2026-04-17 10:57,4320.83,4320.27,4321.77,4319.86,4323.143", "2026-04-17 10:58,4320.14,4318.80,4320.50,4318.80,4323.094", "2026-04-17 10:59,4318.87,4319.64,4319.75,4318.59,4323.055", "2026-04-17 11:00,4319.96,4315.64,4320.09,4315.64,4322.973", "2026-04-17 11:01,4315.51,4315.06,4316.00,4313.81,4322.886", "2026-04-17 11:02,4315.35,4316.13,4316.13,4314.47,4322.813", "2026-04-17 11:03,4316.13,4315.80,4316.93,4315.80,4322.738", "2026-04-17 11:04,4315.07,4315.52,4315.84,4314.84,4322.662", "2026-04-17 11:05,4315.24,4315.45,4315.74,4315.11,4322.586", "2026-04-17 11:06,4315.45,4313.88,4316.42,4313.77,4322.496", "2026-04-17 11:07,4313.54,4311.93,4314.04,4311.61,4322.388", "2026-04-17 11:08,4311.40,4311.67,4312.87,4310.95,4322.279", "2026-04-17 11:09,4311.63,4313.08,4313.08,4311.27,4322.187", "2026-04-17 11:10,4312.54,4313.77,4315.32,4312.28,4322.103", "2026-04-17 11:11,4314.01,4313.80,4314.67,4312.97,4322.021", "2026-04-17 11:12,4314.02,4315.56,4316.17,4313.82,4321.958", "2026-04-17 11:13,4315.84,4315.10,4316.24,4315.03,4321.892", "2026-04-17 11:14,4314.71,4312.59,4315.55,4312.59,4321.803", "2026-04-17 11:15,4313.18,4313.74,4314.35,4312.74,4321.726", "2026-04-17 11:16,4314.15,4312.82,4314.37,4312.76,4321.642", "2026-04-17 11:17,4313.15,4313.20,4313.49,4312.09,4321.563", "2026-04-17 11:18,4312.84,4312.78,4313.73,4312.33,4321.482", "2026-04-17 11:19,4312.25,4313.46,4313.48,4311.86,4321.409", "2026-04-17 11:20,4313.58,4312.87,4314.05,4312.84,4321.332", "2026-04-17 11:21,4312.94,4311.48,4313.03,4311.14,4321.244", "2026-04-17 11:22,4311.75,4312.14,4312.82,4311.35,4321.163", "2026-04-17 11:23,4312.14,4311.95,4312.14,4311.24,4321.082", "2026-04-17 11:24,4311.95,4310.92,4311.95,4310.36,4320.993", "2026-04-17 11:25,4311.15,4310.72,4311.84,4310.10,4320.904", "2026-04-17 11:26,4310.44,4310.96,4312.09,4310.44,4320.819", "2026-04-17 11:27,4311.41,4311.05,4311.67,4310.24,4320.736", "2026-04-17 11:28,4311.12,4310.81,4311.39,4310.60,4320.652", "2026-04-17 11:29,4311.07,4310.32,4311.15,4309.94,4320.565", "2026-04-17 11:30,4310.32,4308.92,4310.32,4308.92,4320.468", "2026-04-17 11:31,4309.24,4308.93,4310.11,4308.93,4320.373", "2026-04-17 11:32,4309.13,4309.02,4309.82,4308.20,4320.280", "2026-04-17 11:33,4309.02,4308.18,4309.12,4308.18,4320.182", "2026-04-17 11:34,4308.18,4308.96,4308.96,4307.66,4320.092", "2026-04-17 11:35,4308.88,4306.62,4309.20,4305.82,4319.985", "2026-04-17 11:36,4306.45,4306.25,4307.39,4306.25,4319.876", "2026-04-17 11:37,4306.25,4306.51,4307.20,4305.57,4319.771", "2026-04-17 11:38,4306.51,4305.02,4306.83,4305.02,4319.656", "2026-04-17 11:39,4305.57,4305.43,4306.04,4304.78,4319.546", "2026-04-17 11:40,4305.75,4305.69,4306.25,4305.23,4319.440", "2026-04-17 11:41,4306.00,4306.41,4306.65,4305.44,4319.341", "2026-04-17 11:42,4306.41,4306.68,4306.68,4305.38,4319.245", "2026-04-17 11:43,4306.75,4306.04,4307.00,4305.81,4319.146", "2026-04-17 11:44,4306.04,4306.74,4306.74,4306.04,4319.054", "2026-04-17 11:45,4306.74,4307.66,4307.66,4306.63,4318.970", "2026-04-17 11:46,4307.35,4306.71,4307.54,4306.59,4318.880", "2026-04-17 11:47,4307.23,4309.04,4309.31,4307.19,4318.808", "2026-04-17 11:48,4309.04,4309.20,4309.45,4308.27,4318.738", "2026-04-17 11:49,4309.20,4309.69,4310.23,4308.39,4318.673", "2026-04-17 11:50,4310.40,4310.56,4310.73,4309.61,4318.615", "2026-04-17 11:51,4310.56,4310.00,4311.00,4309.84,4318.554", "2026-04-17 11:52,4310.23,4311.47,4311.47,4310.23,4318.504", "2026-04-17 11:53,4311.19,4310.68,4311.53,4310.52,4318.449", "2026-04-17 11:54,4310.68,4310.97,4311.41,4310.68,4318.397", "2026-04-17 11:55,4310.77,4311.85,4311.92,4310.28,4318.352", "2026-04-17 11:56,4311.77,4311.27,4312.10,4310.74,4318.303", "2026-04-17 11:57,4311.27,4313.13,4313.17,4311.24,4318.268", "2026-04-17 11:58,4313.13,4312.78,4313.45,4312.46,4318.231", "2026-04-17 11:59,4312.78,4312.47,4312.90,4311.90,4318.192", "2026-04-17 12:00,4312.75,4313.19,4313.24,4311.65,4318.158", "2026-04-17 13:01,4313.49,4312.75,4316.20,4312.75,4318.122", "2026-04-17 13:02,4312.44,4312.31,4313.24,4311.80,4318.084", "2026-04-17 13:03,4312.85,4312.71,4313.44,4312.38,4318.049", "2026-04-17 13:04,4312.33,4311.99,4312.33,4311.36,4318.009", "2026-04-17 13:05,4311.94,4312.29,4312.56,4311.39,4317.972", "2026-04-17 13:06,4311.97,4311.73,4312.74,4311.40,4317.932", "2026-04-17 13:07,4311.62,4311.25,4312.07,4310.36,4317.889", "2026-04-17 13:08,4311.25,4310.80,4311.53,4310.32,4317.844", "2026-04-17 13:09,4310.76,4311.14,4311.14,4310.49,4317.802", "2026-04-17 13:10,4310.82,4310.10,4311.21,4310.02,4317.754", "2026-04-17 13:11,4310.37,4310.32,4310.52,4309.61,4317.708", "2026-04-17 13:12,4310.32,4309.12,4310.32,4308.81,4317.655", "2026-04-17 13:13,4309.00,4308.82,4309.40,4308.14,4317.601", "2026-04-17 13:14,4308.65,4309.71,4309.80,4308.55,4317.553", "2026-04-17 13:15,4309.71,4310.29,4310.38,4309.50,4317.509", "2026-04-17 13:16,4310.29,4311.72,4311.72,4310.21,4317.474", "2026-04-17 13:17,4311.59,4311.27,4311.83,4310.46,4317.437", "2026-04-17 13:18,4311.24,4310.58,4311.44,4310.31,4317.396", "2026-04-17 13:19,4311.13,4309.75,4311.13,4308.77,4317.351", "2026-04-17 13:20,4310.07,4309.88,4310.71,4309.88,4317.307", "2026-04-17 13:21,4310.15,4310.58,4311.41,4309.93,4317.267", "2026-04-17 13:22,4310.58,4311.89,4311.89,4309.89,4317.235", "2026-04-17 13:23,4312.04,4312.29,4312.47,4310.71,4317.206", "2026-04-17 13:24,4312.46,4310.58,4312.46,4310.30,4317.168", "2026-04-17 13:25,4310.12,4311.54,4312.15,4310.12,4317.136", "2026-04-17 13:26,4311.54,4311.65,4311.65,4310.74,4317.105", "2026-04-17 13:27,4311.81,4309.91,4311.81,4309.45,4317.064", "2026-04-17 13:28,4309.60,4309.56,4310.29,4309.22,4317.022", "2026-04-17 13:29,4309.88,4308.81,4310.53,4308.81,4316.976", "2026-04-17 13:30,4308.81,4308.87,4309.39,4308.38,4316.931", "2026-04-17 13:31,4308.94,4308.21,4309.37,4307.96,4316.883", "2026-04-17 13:32,4308.21,4304.93,4308.52,4304.93,4316.817", "2026-04-17 13:33,4304.93,4305.19,4305.74,4304.51,4316.753", "2026-04-17 13:34,4305.44,4303.58,4305.44,4303.58,4316.681", "2026-04-17 13:35,4303.69,4304.36,4304.70,4303.48,4316.614", "2026-04-17 13:36,4304.36,4304.76,4305.01,4303.37,4316.550", "2026-04-17 13:37,4304.83,4304.21,4305.69,4303.89,4316.484", "2026-04-17 13:38,4304.36,4305.83,4306.62,4304.36,4316.427", "2026-04-17 13:39,4306.17,4307.49,4307.49,4305.89,4316.379", "2026-04-17 13:40,4306.93,4307.49,4307.60,4306.18,4316.332", "2026-04-17 13:41,4307.77,4307.05,4307.93,4306.17,4316.283", "2026-04-17 13:42,4307.05,4306.77,4308.41,4306.77,4316.233", "2026-04-17 13:43,4307.05,4307.93,4309.25,4306.77,4316.190", "2026-04-17 13:44,4307.93,4308.97,4308.98,4307.41,4316.152", "2026-04-17 13:45,4308.66,4308.21,4308.92,4306.55,4316.111", "2026-04-17 13:46,4308.21,4308.58,4308.58,4307.28,4316.072", "2026-04-17 13:47,4308.58,4309.27,4309.85,4308.02,4316.037", "2026-04-17 13:48,4308.59,4308.44,4309.11,4308.02,4315.998", "2026-04-17 13:49,4308.60,4308.47,4309.25,4308.03,4315.960", "2026-04-17 13:50,4308.47,4307.57,4309.48,4307.57,4315.918", "2026-04-17 13:51,4307.57,4308.43,4308.98,4307.57,4315.880", "2026-04-17 13:52,4308.92,4308.30,4309.18,4308.17,4315.842", "2026-04-17 13:53,4308.94,4309.06,4309.52,4308.51,4315.808", "2026-04-17 13:54,4309.27,4310.01,4310.01,4308.27,4315.779", "2026-04-17 13:55,4310.78,4310.59,4311.19,4310.13,4315.753", "2026-04-17 13:56,4310.91,4313.27,4313.27,4310.83,4315.741", "2026-04-17 13:57,4313.08,4311.28,4313.40,4311.08,4315.719", "2026-04-17 13:58,4311.35,4310.49,4312.13,4310.07,4315.693", "2026-04-17 13:59,4310.45,4309.31,4310.86,4309.31,4315.662", "2026-04-17 14:00,4309.79,4309.78,4310.39,4309.03,4315.634", "2026-04-17 14:01,4310.22,4309.49,4310.49,4309.07,4315.605", "2026-04-17 14:02,4309.49,4309.20,4309.64,4308.73,4315.574", "2026-04-17 14:03,4309.16,4309.27,4310.05,4308.29,4315.544", "2026-04-17 14:04,4309.55,4310.57,4311.00,4308.58,4315.520", "2026-04-17 14:05,4310.43,4310.40,4311.04,4309.58,4315.496", "2026-04-17 14:06,4310.68,4311.02,4311.34,4310.08,4315.475", "2026-04-17 14:07,4311.02,4310.83,4312.08,4310.69,4315.453", "2026-04-17 14:08,4310.55,4310.52,4311.14,4309.85,4315.430", "2026-04-17 14:09,4310.83,4310.34,4311.29,4309.98,4315.406", "2026-04-17 14:10,4310.19,4307.70,4310.19,4307.38,4315.371", "2026-04-17 14:11,4307.75,4308.29,4308.71,4307.75,4315.339", "2026-04-17 14:12,4308.61,4308.54,4309.20,4307.49,4315.308", "2026-04-17 14:13,4307.86,4308.51,4308.99,4307.86,4315.277", "2026-04-17 14:14,4308.46,4309.29,4310.34,4308.21,4315.250", "2026-04-17 14:15,4309.29,4309.94,4309.94,4308.91,4315.226", "2026-04-17 14:16,4309.89,4309.16,4310.01,4308.97,4315.199", "2026-04-17 14:17,4309.16,4309.00,4310.05,4308.73,4315.171", "2026-04-17 14:18,4309.60,4311.07,4311.07,4309.57,4315.153", "2026-04-17 14:19,4311.17,4311.27,4311.63,4310.32,4315.136", "2026-04-17 14:20,4310.95,4311.73,4311.97,4310.57,4315.121", "2026-04-17 14:21,4312.04,4312.62,4312.62,4310.93,4315.110", "2026-04-17 14:22,4312.59,4311.83,4312.61,4311.54,4315.095", "2026-04-17 14:23,4311.96,4312.44,4312.64,4311.07,4315.083", "2026-04-17 14:24,4312.65,4312.88,4313.01,4312.37,4315.073", "2026-04-17 14:25,4312.53,4312.45,4312.53,4311.10,4315.061", "2026-04-17 14:26,4312.13,4312.49,4312.77,4311.90,4315.050", "2026-04-17 14:27,4312.49,4312.95,4312.95,4311.92,4315.041", "2026-04-17 14:28,4312.96,4312.74,4313.55,4312.11,4315.031", "2026-04-17 14:29,4312.68,4312.76,4313.85,4312.67,4315.021", "2026-04-17 14:30,4313.07,4312.54,4314.12,4312.37,4315.010", "2026-04-17 14:31,4312.76,4311.70,4313.82,4310.69,4314.996", "2026-04-17 14:32,4311.38,4311.53,4311.92,4310.42,4314.981", "2026-04-17 14:33,4311.38,4312.47,4312.95,4311.07,4314.970", "2026-04-17 14:34,4313.04,4312.93,4313.93,4312.68,4314.961", "2026-04-17 14:35,4313.03,4312.55,4313.61,4311.90,4314.951", "2026-04-17 14:36,4313.27,4313.38,4313.48,4312.75,4314.944", "2026-04-17 14:37,4313.38,4313.67,4314.47,4312.68,4314.938", "2026-04-17 14:38,4313.67,4312.80,4314.20,4312.71,4314.929", "2026-04-17 14:39,4312.80,4313.67,4314.36,4312.68,4314.923", "2026-04-17 14:40,4313.99,4313.84,4314.04,4313.03,4314.918", "2026-04-17 14:41,4313.84,4314.21,4315.27,4313.69,4314.915", "2026-04-17 14:42,4313.82,4314.46,4315.32,4313.82,4314.913", "2026-04-17 14:43,4314.46,4315.67,4316.09,4314.39,4314.915", "2026-04-17 14:44,4315.72,4316.64,4317.08,4315.24,4314.921", "2026-04-17 14:45,4316.27,4317.54,4317.85,4316.12,4314.931", "2026-04-17 14:46,4317.82,4316.78,4317.84,4316.13,4314.938", "2026-04-17 14:47,4317.42,4318.25,4318.96,4317.02,4314.950", "2026-04-17 14:48,4318.40,4319.34,4320.22,4318.27,4314.966", "2026-04-17 14:49,4319.62,4319.73,4320.42,4319.41,4314.984", "2026-04-17 14:50,4320.37,4320.38,4320.75,4319.65,4315.004", "2026-04-17 14:51,4320.07,4322.15,4322.34,4320.00,4315.031", "2026-04-17 14:52,4322.78,4321.44,4322.79,4320.74,4315.055", "2026-04-17 14:53,4321.69,4320.89,4322.05,4320.85,4315.077", "2026-04-17 14:54,4321.21,4321.45,4321.79,4320.48,4315.101", "2026-04-17 14:55,4321.45,4320.54,4321.88,4319.67,4315.121", "2026-04-17 14:56,4320.85,4320.39,4321.88,4319.91,4315.140", "2026-04-17 14:57,4320.39,4319.40,4321.50,4319.22,4315.155", "2026-04-17 14:58,4319.40,4320.15,4320.85,4319.27,4315.173", "2026-04-17 14:59,4320.14,4320.63,4321.23,4319.63,4315.193", "2026-04-17 15:00,4320.63,4321.07,4321.39,4320.41,4315.214", "2026-04-17 15:01,4321.22,4322.50,4322.50,4320.88,4315.240", "2026-04-17 15:02,4322.50,4321.68,4322.78,4320.87,4315.263", "2026-04-17 15:03,4320.75,4320.59,4321.86,4320.26,4315.282", "2026-04-17 15:04,4320.59,4320.68,4321.89,4320.24,4315.301", "2026-04-17 15:05,4320.68,4318.77,4321.05,4318.77,4315.313", "2026-04-17 15:06,4318.85,4319.38,4320.09,4318.85,4315.327", "2026-04-17 15:07,4319.61,4319.74,4320.46,4319.13,4315.342", "2026-04-17 15:08,4319.84,4320.37,4320.38,4319.38,4315.360", "2026-04-17 15:09,4320.37,4320.35,4320.91,4317.88,4315.377", "2026-04-17 15:10,4320.48,4320.72,4322.02,4320.34,4315.396", "2026-04-17 15:11,4320.82,4320.48,4321.30,4319.84,4315.414", "2026-04-17 15:12,4320.91,4320.99,4321.58,4320.24,4315.433", "2026-04-17 15:13,4321.10,4321.99,4321.99,4320.86,4315.456", "2026-04-17 15:14,4322.37,4322.67,4323.12,4321.25,4315.481", "2026-04-17 15:15,4322.36,4323.21,4323.68,4322.33,4315.508", "2026-04-17 15:16,4323.48,4323.22,4323.54,4322.31,4315.534", "2026-04-17 15:17,4323.49,4324.16,4324.32,4323.00,4315.563", "2026-04-17 15:18,4324.07,4321.48,4324.07,4321.48,4315.583", "2026-04-17 15:19,4321.29,4322.27,4322.27,4321.21,4315.606", "2026-04-17 15:20,4322.15,4321.43,4322.55,4321.43,4315.626", "2026-04-17 15:21,4321.60,4320.71,4322.15,4319.76,4315.643", "2026-04-17 15:22,4320.38,4321.68,4322.34,4320.38,4315.663", "2026-04-17 15:23,4321.37,4323.04,4323.19,4321.37,4315.688", "2026-04-17 15:24,4323.95,4323.65,4324.16,4323.08,4315.714", "2026-04-17 15:25,4323.38,4324.20,4325.16,4323.38,4315.742", "2026-04-17 15:26,4323.88,4324.10,4324.70,4323.71,4315.770", "2026-04-17 15:27,4323.82,4323.09,4325.14,4322.92,4315.794", "2026-04-17 15:28,4323.33,4322.95,4323.57,4322.67,4315.817", "2026-04-17 15:29,4322.95,4323.19,4323.19,4322.08,4315.841", "2026-04-17 15:30,4323.19,4322.19,4323.48,4321.29,4315.862", "2026-04-17 15:31,4321.62,4321.85,4321.89,4320.73,4315.881", "2026-04-17 15:32,4321.66,4320.91,4322.00,4320.80,4315.897", "2026-04-17 15:33,4321.23,4322.40,4322.50,4320.93,4315.918", "2026-04-17 15:34,4322.21,4321.84,4323.04,4321.29,4315.937", "2026-04-17 15:35,4321.84,4323.11,4323.11,4321.46,4315.960", "2026-04-17 15:36,4322.72,4323.44,4323.47,4322.48,4315.984", "2026-04-17 15:37,4323.24,4322.60,4323.47,4322.33,4316.005", "2026-04-17 15:38,4322.24,4322.85,4323.32,4322.21,4316.027", "2026-04-17 15:39,4323.04,4323.94,4324.62,4323.04,4316.052", "2026-04-17 15:40,4323.41,4324.32,4324.71,4322.11,4316.078", "2026-04-17 15:41,4324.60,4325.24,4325.60,4324.18,4316.107", "2026-04-17 15:42,4325.21,4324.55,4325.21,4324.47,4316.133", "2026-04-17 15:43,4324.76,4324.20,4325.24,4323.84,4316.158", "2026-04-17 15:44,4324.36,4324.83,4325.37,4324.18,4316.185", "2026-04-17 15:45,4324.76,4325.58,4325.58,4324.30,4316.214", "2026-04-17 15:46,4325.58,4325.52,4326.19,4324.80,4316.243", "2026-04-17 15:47,4325.71,4324.92,4326.26,4324.26,4316.270", "2026-04-17 15:48,4324.99,4324.20,4325.36,4322.26,4316.294", "2026-04-17 15:49,4323.75,4324.36,4324.56,4323.01,4316.319", "2026-04-17 15:50,4323.91,4324.72,4324.95,4323.90,4316.345", "2026-04-17 15:51,4324.56,4323.73,4324.73,4323.45,4316.367", "2026-04-17 15:52,4323.62,4323.82,4323.93,4322.00,4316.390", "2026-04-17 15:53,4323.52,4324.44,4325.00,4323.02,4316.414", "2026-04-17 15:54,4324.65,4324.10,4324.65,4323.07,4316.437", "2026-04-17 15:55,4324.16,4322.29,4324.16,4321.76,4316.454", "2026-04-17 15:56,4322.54,4323.23,4323.42,4322.18,4316.474", "2026-04-17 15:57,4323.50,4323.42,4323.50,4322.12,4316.495", "2026-04-17 15:58,4323.71,4324.08,4324.47,4322.39,4316.518", "2026-04-17 15:59,4324.31,4325.14,4325.14,4322.24,4316.544", "2026-04-17 16:00,4324.67,4325.72,4325.72,4323.68,4316.571"]
+    }
+});</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取亚洲股市行情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://push2.eastmoney.com/api/qt/clist/get?np=1&amp;fltt=1&amp;invt=2&amp;cb=jQuery37106678942551489491_1776569949905&amp;fs=i%3A1.000001%2Ci%3A0.399001%2Ci%3A0.399005%2Ci%3A0.399006%2Ci%3A1.000300%2Ci%3A100.HSI%2Ci%3A100.HSCEI%2Ci%3A124.HSCCI%2Ci%3A100.TWII%2Ci%3A100.N225%2Ci%3A100.KOSPI200%2Ci%3A100.KS11%2Ci%3A100.STI%2Ci%3A100.SENSEX%2Ci%3A100.KLSE%2Ci%3A100.SET%2Ci%3A100.PSI%2Ci%3A100.KSE100%2Ci%3A100.VNINDEX%2Ci%3A100.JKSE%2Ci%3A100.CSEALL&amp;fields=f12%2Cf13%2Cf14%2Cf292%2Cf1%2Cf2%2Cf4%2Cf3%2Cf152&amp;fid=&amp;pn=1&amp;pz=100&amp;po=1&amp;ut=fa5fd1943c7b386f172d6893dbfba10b&amp;dect=1&amp;wbp2u=%7C0%7C0%7C0%7Cweb&amp;_=1776569949906</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jQuery37106678942551489491_1776569949905({
+    "rc": 0,
+    "rt": 6,
+    "svr": 183637960,
+    "lt": 1,
+    "full": 1,
+    "dlmkts": "",
+    "data": {
+        "total": 21,
+        "diff": [{
+            "f1": 2,
+            "f2": 405143,
+            "f3": -10,
+            "f4": -412,
+            "f12": "000001",
+            "f13": 1,
+            "f14": "上证指数",
+            "f152": 2,
+            "f292": 13
+        }, {
+            "f1": 2,
+            "f2": 1488542,
+            "f3": 60,
+            "f4": 8909,
+            "f12": "399001",
+            "f13": 0,
+            "f14": "深证成指",
+            "f152": 2,
+            "f292": 13
+        }, {
+            "f1": 2,
+            "f2": 902786,
+            "f3": 12,
+            "f4": 1061,
+            "f12": "399005",
+            "f13": 0,
+            "f14": "中小100",
+            "f152": 2,
+            "f292": 13
+        }, {
+            "f1": 2,
+            "f2": 367829,
+            "f3": 143,
+            "f4": 5202,
+            "f12": "399006",
+            "f13": 0,
+            "f14": "创业板指",
+            "f152": 2,
+            "f292": 13
+        }, {
+            "f1": 2,
+            "f2": 472867,
+            "f3": -17,
+            "f4": -794,
+            "f12": "000300",
+            "f13": 1,
+            "f14": "沪深300",
+            "f152": 2,
+            "f292": 13
+        }, {
+            "f1": 2,
+            "f2": 2616033,
+            "f3": -89,
+            "f4": -23393,
+            "f12": "HSI",
+            "f13": 100,
+            "f14": "恒生指数",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 884502,
+            "f3": -67,
+            "f4": -6009,
+            "f12": "HSCEI",
+            "f13": 100,
+            "f14": "国企指数",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 432572,
+            "f3": -50,
+            "f4": -2169,
+            "f12": "HSCCI",
+            "f13": 124,
+            "f14": "红筹指数",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 3680434,
+            "f3": -88,
+            "f4": -32768,
+            "f12": "TWII",
+            "f13": 100,
+            "f14": "台湾加权",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 5847590,
+            "f3": -175,
+            "f4": -104244,
+            "f12": "N225",
+            "f13": 100,
+            "f14": "日经225",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 93141,
+            "f3": -69,
+            "f4": -646,
+            "f12": "KOSPI200",
+            "f13": 100,
+            "f14": "韩国KOSPI200",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 619192,
+            "f3": -55,
+            "f4": -3413,
+            "f12": "KS11",
+            "f13": 100,
+            "f14": "韩国KOSPI",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 499793,
+            "f3": -20,
+            "f4": -990,
+            "f12": "STI",
+            "f13": 100,
+            "f14": "富时新加坡海峡时报",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 7849354,
+            "f3": 65,
+            "f4": 50486,
+            "f12": "SENSEX",
+            "f13": 100,
+            "f14": "印度孟买SENSEX",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 169521,
+            "f3": 33,
+            "f4": 550,
+            "f12": "KLSE",
+            "f13": 100,
+            "f14": "富时马来西亚KLCI",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 148245,
+            "f3": -49,
+            "f4": -728,
+            "f12": "SET",
+            "f13": 100,
+            "f14": "泰国SET",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 599913,
+            "f3": -106,
+            "f4": -6456,
+            "f12": "PSI",
+            "f13": 100,
+            "f14": "菲律宾马尼拉",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 17276071,
+            "f3": 132,
+            "f4": 225141,
+            "f12": "KSE100",
+            "f13": 100,
+            "f14": "巴基斯坦卡拉奇",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 181717,
+            "f3": -15,
+            "f4": -266,
+            "f12": "VNINDEX",
+            "f13": 100,
+            "f14": "越南胡志明",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 763400,
+            "f3": 17,
+            "f4": 1262,
+            "f12": "JKSE",
+            "f13": 100,
+            "f14": "印尼雅加达综合",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 2277329,
+            "f3": 82,
+            "f4": 18432,
+            "f12": "CSEALL",
+            "f13": 100,
+            "f14": "斯里兰卡科伦坡",
+            "f152": 2,
+            "f292": 5
+        }]
+    }
+});</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取美洲股市行情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+https://push2.eastmoney.com/api/qt/clist/get?np=1&amp;fltt=1&amp;invt=2&amp;cb=jQuery37106678942551489491_1776569949909&amp;fs=i%3A100.DJIA%2Ci%3A100.SPX%2Ci%3A100.NDX%2Ci%3A100.TSX%2Ci%3A100.BVSP%2Ci%3A100.MXX&amp;fields=f12%2Cf13%2Cf14%2Cf292%2Cf1%2Cf2%2Cf4%2Cf3%2Cf152&amp;fid=&amp;pn=1&amp;pz=100&amp;po=1&amp;ut=fa5fd1943c7b386f172d6893dbfba10b&amp;dect=1&amp;wbp2u=%7C0%7C0%7C0%7Cweb&amp;_=1776569949910</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jQuery37106678942551489491_1776569949909({
+    "rc": 0,
+    "rt": 6,
+    "svr": 183636839,
+    "lt": 1,
+    "full": 1,
+    "dlmkts": "",
+    "data": {
+        "total": 6,
+        "diff": [{
+            "f1": 2,
+            "f2": 4944743,
+            "f3": 179,
+            "f4": 86871,
+            "f12": "DJIA",
+            "f13": 100,
+            "f14": "道琼斯",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 712606,
+            "f3": 120,
+            "f4": 8478,
+            "f12": "SPX",
+            "f13": 100,
+            "f14": "标普500",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 2446848,
+            "f3": 152,
+            "f4": 36578,
+            "f12": "NDX",
+            "f13": 100,
+            "f14": "纳斯达克",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 3434629,
+            "f3": 86,
+            "f4": 29406,
+            "f12": "TSX",
+            "f13": 100,
+            "f14": "加拿大S&amp;P/TSX",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 19573400,
+            "f3": -55,
+            "f4": -108500,
+            "f12": "BVSP",
+            "f13": 100,
+            "f14": "巴西BOVESPA",
+            "f152": 2,
+            "f292": 5
+        }, {
+            "f1": 2,
+            "f2": 6982594,
+            "f3": 106,
+            "f4": 73092,
+            "f12": "MXX",
+            "f13": 100,
+            "f14": "墨西哥BOLSA",
+            "f152": 2,
+            "f292": 5
+        }]
+    }
+});</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1344,7 +2014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756FAFE1-58E3-4702-9EE8-9320214AB644}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -1488,8 +2158,131 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C8" s="2"/>
+    <row r="8" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1500,6 +2293,10 @@
     <hyperlink ref="C5" r:id="rId4" xr:uid="{65A696E3-DC0D-41D5-BEF2-5F556A0DFD08}"/>
     <hyperlink ref="C6" r:id="rId5" xr:uid="{4CE6E835-A307-4EC6-94A1-7077A14AD1D1}"/>
     <hyperlink ref="C7" r:id="rId6" xr:uid="{F70AB97F-1DF4-41E6-89EB-9DE1813B8336}"/>
+    <hyperlink ref="C8" r:id="rId7" display="https://push2.eastmoney.com/api/qt/clist/get?np=1&amp;fltt=1&amp;invt=2&amp;cb=jQuery37103879588047371354_1776568216882&amp;fs=b%3AMK0010&amp;fields=f12%2Cf13%2Cf14%2Cf1%2Cf2%2Cf4%2Cf3%2Cf152%2Cf5%2Cf6%2Cf18%2Cf17%2Cf15%2Cf16&amp;fid=&amp;pn=1&amp;pz=50&amp;po=1&amp;ut=fa5fd1943c7b386f172d6893dbfba10b&amp;dect=1&amp;wbp2u=%7C0%7C0%7C0%7Cweb&amp;_=1776568216883" xr:uid="{AED338C9-D95A-48FB-99EC-D694CC813656}"/>
+    <hyperlink ref="C11" r:id="rId8" display="https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=100.DJIA&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp152" xr:uid="{18F47342-9A41-47AC-A7DD-1F5487D4AEB2}"/>
+    <hyperlink ref="C13" r:id="rId9" display="https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=100.HSCEI&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp248" xr:uid="{36FC8E56-4897-4C0B-A7F3-540876EE494B}"/>
+    <hyperlink ref="C14" r:id="rId10" display="https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=124.HSCCI&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp250" xr:uid="{F0EC10B8-513A-4B2E-A66E-991476046EFD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/fund_api.xlsx
+++ b/fund_api.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lzfdd\backups\MyProjects\python_test\fundweb\JJBond\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FBFA8B-72D1-4F87-B0AE-1AD1AEE2ACFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D432A900-507D-4E49-AFAE-6212DE177D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7068C037-8E11-473D-BF09-92FC6201B4E7}"/>
+    <workbookView xWindow="2352" yWindow="3768" windowWidth="17280" windowHeight="13236" xr2:uid="{7068C037-8E11-473D-BF09-92FC6201B4E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
   <si>
     <t>接口</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1623,6 +1623,127 @@
 });</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>获取主题基金列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+https://api.fund.eastmoney.com/ZTJJ/GetBKRelTopicFundNew?callback=jQuery18306304851841656735_1776918973918&amp;sort=undefined&amp;sorttype=DESC&amp;pageindex=1&amp;pagesize=10&amp;tp=BK000096&amp;isbuy=1&amp;_=1776940130680</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jQuery18306304851841656735_1776918973918({
+    "Data": [
+        {
+            "CORR_1Y": 69.0725,
+            "FCODE": "501008",
+            "RELATETYPE": "1",
+            "SYRQ": "2026-04-22",
+            "SOURCERATE": "0.00%",
+            "DWJZ": 0.9074,
+            "RZDF": 1.14,
+            "RATE": "0.00%",
+            "ISBUY": "1",
+            "MINSG": 10.0,
+            "SHORTNAME": "汇添富中证互联网医疗指数(LOF)C",
+            "SYL_Z": 1.43,
+            "SYL_Y": 0.99,
+            "SYL_3Y": -9.25,
+            "SYL_6Y": -1.47,
+            "SYL_1N": 1.52,
+            "SYL_2N": 12.37,
+            "SYL_3N": -18.94,
+            "SYL_JN": 0.31,
+            "SYL_LN": -9.26,
+            "ISSALES": "1",
+            "FTYPE": "指数型-股票",
+            "RELATION": 69.0725
+        },
+        {
+            "CORR_1Y": 69.0725,
+            "FCODE": "501007",
+            "RELATETYPE": "1",
+            "SYRQ": "2026-04-22",
+            "SOURCERATE": "0.80%",
+            "DWJZ": 0.9375,
+            "RZDF": 1.13,
+            "RATE": "0.08%",
+            "ISBUY": "1",
+            "MINSG": 10.0,
+            "SHORTNAME": "汇添富中证互联网医疗指数(LOF)A",
+            "SYL_Z": 1.44,
+            "SYL_Y": 1.02,
+            "SYL_3Y": -9.17,
+            "SYL_6Y": -1.27,
+            "SYL_1N": 1.94,
+            "SYL_2N": 13.27,
+            "SYL_3N": -17.96,
+            "SYL_JN": 0.43,
+            "SYL_LN": -6.25,
+            "ISSALES": "1",
+            "FTYPE": "指数型-股票",
+            "RELATION": 69.0725
+        },
+    ],
+    "ErrCode": 0,
+    "ErrMsg": null,
+    "TotalCount": 62,
+    "Expansion": null,
+    "PageSize": 10,
+    "PageIndex": 1
+})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tp参数从 获取行业板块涨跌情况接口获取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取板块主题详情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://api.fund.eastmoney.com/ZTJJ/GetBKDetailInfoNew?callback=jQuery18306304851841656735_1776918973918&amp;tp=BK000197&amp;_=1776943829756</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jQuery18306304851841656735_1776918973918({
+    "Data": {
+        "M": -4.0300,
+        "MSC": 184.0,
+        "Q": 17.2200,
+        "QSC": 184.0,
+        "RANKM": 183.0,
+        "RANKQ": 17.0,
+        "RANKSY": 56.0,
+        "RANKW": 63.0,
+        "RANKY": 98.0,
+        "SEC_CODE": "BK000197",
+        "SEC_NAME": "能源",
+        "SYSC": 184.0,
+        "W": 2.0100,
+        "WSC": 185.0,
+        "Y": 44.9200,
+        "YSC": 184.0,
+        "INDEXNAME": "能源",
+        "INDEXCODE": "BK000197",
+        "D": 2.785084,
+        "SY": 17.2300
+    },
+    "ErrCode": 0,
+    "ErrMsg": null,
+    "TotalCount": 0,
+    "Expansion": null,
+    "PageSize": 0,
+    "PageIndex": 0
+})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>响应参数中，"D"为日涨幅，"W" 为近一周涨幅，"M"为近一月，"Q"为近三月，"Y"为近一年，“SY”为今年来涨幅。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2014,7 +2135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756FAFE1-58E3-4702-9EE8-9320214AB644}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -2284,6 +2405,34 @@
         <v>62</v>
       </c>
     </row>
+    <row r="17" spans="2:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -2297,6 +2446,7 @@
     <hyperlink ref="C11" r:id="rId8" display="https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=100.DJIA&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp152" xr:uid="{18F47342-9A41-47AC-A7DD-1F5487D4AEB2}"/>
     <hyperlink ref="C13" r:id="rId9" display="https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=100.HSCEI&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp248" xr:uid="{36FC8E56-4897-4C0B-A7F3-540876EE494B}"/>
     <hyperlink ref="C14" r:id="rId10" display="https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=124.HSCCI&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp250" xr:uid="{F0EC10B8-513A-4B2E-A66E-991476046EFD}"/>
+    <hyperlink ref="C17" r:id="rId11" xr:uid="{A628F64C-A7D6-4A1F-89ED-5FBC668A5C95}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/fund_api.xlsx
+++ b/fund_api.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lzfdd\backups\MyProjects\python_test\fundweb\JJBond\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D432A900-507D-4E49-AFAE-6212DE177D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7469B191-2FEA-47A5-93F6-EE8BA5582781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2352" yWindow="3768" windowWidth="17280" windowHeight="13236" xr2:uid="{7068C037-8E11-473D-BF09-92FC6201B4E7}"/>
+    <workbookView xWindow="4536" yWindow="444" windowWidth="17280" windowHeight="13236" xr2:uid="{7068C037-8E11-473D-BF09-92FC6201B4E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="81">
   <si>
     <t>接口</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1744,6 +1744,123 @@
     <t>响应参数中，"D"为日涨幅，"W" 为近一周涨幅，"M"为近一月，"Q"为近三月，"Y"为近一年，“SY”为今年来涨幅。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>获取基金历史净值(东方财富)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取基金历史净值图表(东方财富)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取基金历史净值(新浪财经)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+https://stock.finance.sina.com.cn/fundInfo/api/openapi.php/CaihuiFundInfoService.getNav?callback=jQuery1112002027799582723_1784127647303&amp;symbol=003096&amp;datefrom=&amp;dateto=&amp;page=1&amp;_=1784127647319</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从 https://finance.sina.com.cn/ 跳转</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/*&lt;script&gt;location.href='//sina.com';&lt;/script&gt;*/
+jQuery1112002027799582723_1784127647303({
+    "result": {
+        "status": {
+            "code": 0
+        },
+        "data": {
+            "data": [{
+                "fbrq": "2026-07-15 00:00:00",
+                "jjjz": "2.0058",
+                "ljjz": "2.2378"
+            }, {
+                "fbrq": "2026-07-14 00:00:00",
+                "jjjz": "1.9017",
+                "ljjz": "2.1337"
+            }],
+            "total_num": "2371"
+        }
+    }
+})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://api.fund.eastmoney.com/f10/lsjz?callback=jQuery18303837326938161737_1784126811022&amp;fundCode=003096&amp;pageIndex=1&amp;pageSize=20&amp;startDate=&amp;endDate=&amp;_=1784126811236</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jQuery18303837326938161737_1784126811022({
+    "Data": {
+        "LSJZList": [
+            {
+                "FSRQ": "2026-07-15",
+                "DWJZ": "2.0058",
+                "LJJZ": "2.2378",
+                "SDATE": null,
+                "ACTUALSYI": "",
+                "NAVTYPE": "1",
+                "JZZZL": "5.47",
+                "SGZT": "限制大额申购",
+                "SHZT": "开放赎回",
+                "FHFCZ": "",
+                "FHFCBZ": "",
+                "DTYPE": null,
+                "FHSP": ""
+            },
+            {
+                "FSRQ": "2026-07-14",
+                "DWJZ": "1.9017",
+                "LJJZ": "2.1337",
+                "SDATE": null,
+                "ACTUALSYI": "",
+                "NAVTYPE": "1",
+                "JZZZL": "3.84",
+                "SGZT": "限制大额申购",
+                "SHZT": "开放赎回",
+                "FHFCZ": "",
+                "FHFCBZ": "",
+                "DTYPE": null,
+                "FHSP": ""
+            }],
+        "FundType": "002",
+        "SYType": null,
+        "isNewType": false,
+        "Feature": "211"
+    },
+    "ErrCode": 0,
+    "ErrMsg": null,
+    "TotalCount": 2371,
+    "Expansion": null,
+    "PageSize": 20,
+    "PageIndex": 1
+})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://api.fund.eastmoney.com/f10/LSJZChart?callback=jQuery18303837326938161737_1784126811023&amp;type=0&amp;fundCode=003096&amp;pageIndex=1&amp;pageSize=400&amp;startDate=2025-07-15&amp;endDate=2026-07-15&amp;_=1784126811236</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jQuery18303837326938161737_1784126811023({
+    "Data": [
+        [
+            1752537600000.0,
+            1.7462
+        ],
+        [
+            1752624000000.0,
+            1.7459
+        ]],
+            "total_num": "2371"
+        }
+    }
+})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2135,7 +2252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756FAFE1-58E3-4702-9EE8-9320214AB644}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -2433,6 +2550,51 @@
         <v>66</v>
       </c>
     </row>
+    <row r="19" spans="2:7" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="276" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -2447,6 +2609,8 @@
     <hyperlink ref="C13" r:id="rId9" display="https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=100.HSCEI&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp248" xr:uid="{36FC8E56-4897-4C0B-A7F3-540876EE494B}"/>
     <hyperlink ref="C14" r:id="rId10" display="https://push2.eastmoney.com/api/qt/stock/trends2/get?fields1=f1,f2,f3,f4,f5,f6,f7,f8,f9,f10,f11,f12,f13,f14,f17&amp;fields2=f51,f52,f53,f54,f55,f58&amp;dect=1&amp;mpi=1000&amp;ut=bd1d9ddb04089700cf9c27f6f7426281&amp;secid=124.HSCCI&amp;ndays=1&amp;iscr=0&amp;iscca=0&amp;wbp2u=1849325530509956|0|1|0|web&amp;cb=miniquotechart_jp250" xr:uid="{F0EC10B8-513A-4B2E-A66E-991476046EFD}"/>
     <hyperlink ref="C17" r:id="rId11" xr:uid="{A628F64C-A7D6-4A1F-89ED-5FBC668A5C95}"/>
+    <hyperlink ref="C19" r:id="rId12" xr:uid="{D3745AF9-8509-4E9E-92E3-9D32DCBCCCCD}"/>
+    <hyperlink ref="C20" r:id="rId13" xr:uid="{1B3704EF-1D9C-4562-BEB4-B79F12D05420}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
